--- a/Development/Common/GameData/Enum/GameEnum.xlsx
+++ b/Development/Common/GameData/Enum/GameEnum.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\project\MMOGameServerProject\Common\GameData\Enum\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\project\MMOGameServerProject\Development\Common\GameData\Enum\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B12E5532-5884-4D38-88EF-7037F4398715}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C85D651-C285-4E75-821A-B1D17C6D98D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6705" yWindow="2775" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Enum" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="53">
   <si>
     <t>MonsterGrade</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -184,6 +184,58 @@
   </si>
   <si>
     <t>공격력추가</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ObjectType</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prop</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>프랍</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Drop</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>드롭아이템</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>System</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>시스템</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>캐릭터 선택창 등의 시스템 스테이지</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ResultCode</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Success</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>성공</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>실패</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Fail</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -551,7 +603,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18.5" style="1" customWidth="1"/>
@@ -738,13 +790,13 @@
         <v>1</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
@@ -758,13 +810,13 @@
         <v>2</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
@@ -778,27 +830,33 @@
         <v>3</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="C14" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
@@ -809,13 +867,10 @@
         <v>33</v>
       </c>
       <c r="C15" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
@@ -826,13 +881,13 @@
         <v>33</v>
       </c>
       <c r="C16" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
@@ -843,13 +898,160 @@
         <v>33</v>
       </c>
       <c r="C17" s="1">
+        <v>2</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C18" s="1">
         <v>3</v>
       </c>
-      <c r="D17" s="1" t="s">
+      <c r="D18" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="E17" s="1" t="s">
+      <c r="E18" s="1" t="s">
         <v>39</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C19" s="1">
+        <v>0</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A20" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20" s="1">
+        <v>1</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A21" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C21" s="1">
+        <v>2</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A22" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C22" s="1">
+        <v>3</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A23" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C23" s="1">
+        <v>4</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A24" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C24" s="1">
+        <v>0</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A25" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C25" s="1">
+        <v>1</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A26" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C26" s="1">
+        <v>2</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>51</v>
       </c>
     </row>
   </sheetData>

--- a/Development/Common/GameData/Enum/GameEnum.xlsx
+++ b/Development/Common/GameData/Enum/GameEnum.xlsx
@@ -8,24 +8,35 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\project\MMOGameServerProject\Development\Common\GameData\Enum\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C85D651-C285-4E75-821A-B1D17C6D98D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D863DB4-BC46-4220-9E54-69006D3DE503}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Enum" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="335" uniqueCount="169">
   <si>
     <t>MonsterGrade</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -163,30 +174,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>AddHP</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>AddMP</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>AddAtk</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>HP추가</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>MP추가</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>공격력추가</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>ObjectType</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -237,6 +224,398 @@
   <si>
     <t>Fail</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>StatOp</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Add</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>AddPct</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Amp</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Reduce</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Total</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>필수</t>
+  </si>
+  <si>
+    <t>합연산 (힘+)</t>
+  </si>
+  <si>
+    <t>합연산% (힘+%)</t>
+  </si>
+  <si>
+    <t>곱연산 (힘증폭)</t>
+  </si>
+  <si>
+    <t>점감곱연산 (힘감폭)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>총합</t>
+  </si>
+  <si>
+    <t>StatGroup</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Str</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Int</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Hp</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Mp</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PDef</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MDef</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MoveSpd</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AtkSpd</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CritRate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>힘</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>지능</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>HP</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MP</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>물리방어력</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>마법방어력</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이동속도</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>공격속도</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>크리티컬확률</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>StrAdd</t>
+  </si>
+  <si>
+    <t>IntAdd</t>
+  </si>
+  <si>
+    <t>HpAdd</t>
+  </si>
+  <si>
+    <t>MpAdd</t>
+  </si>
+  <si>
+    <t>PDefAdd</t>
+  </si>
+  <si>
+    <t>MDefAdd</t>
+  </si>
+  <si>
+    <t>MoveSpdAdd</t>
+  </si>
+  <si>
+    <t>AtkSpdAdd</t>
+  </si>
+  <si>
+    <t>CritRateAdd</t>
+  </si>
+  <si>
+    <t>StrAddPct</t>
+  </si>
+  <si>
+    <t>IntAddPct</t>
+  </si>
+  <si>
+    <t>HpAddPct</t>
+  </si>
+  <si>
+    <t>MpAddPct</t>
+  </si>
+  <si>
+    <t>PDefAddPct</t>
+  </si>
+  <si>
+    <t>MDefAddPct</t>
+  </si>
+  <si>
+    <t>MoveSpdAddPct</t>
+  </si>
+  <si>
+    <t>AtkSpdAddPct</t>
+  </si>
+  <si>
+    <t>CritRateAddPct</t>
+  </si>
+  <si>
+    <t>StrAmp</t>
+  </si>
+  <si>
+    <t>IntAmp</t>
+  </si>
+  <si>
+    <t>HpAmp</t>
+  </si>
+  <si>
+    <t>MpAmp</t>
+  </si>
+  <si>
+    <t>PDefAmp</t>
+  </si>
+  <si>
+    <t>MDefAmp</t>
+  </si>
+  <si>
+    <t>MoveSpdAmp</t>
+  </si>
+  <si>
+    <t>AtkSpdAmp</t>
+  </si>
+  <si>
+    <t>CritRateAmp</t>
+  </si>
+  <si>
+    <t>StrReduce</t>
+  </si>
+  <si>
+    <t>IntReduce</t>
+  </si>
+  <si>
+    <t>HpReduce</t>
+  </si>
+  <si>
+    <t>MpReduce</t>
+  </si>
+  <si>
+    <t>PDefReduce</t>
+  </si>
+  <si>
+    <t>MDefReduce</t>
+  </si>
+  <si>
+    <t>MoveSpdReduce</t>
+  </si>
+  <si>
+    <t>AtkSpdReduce</t>
+  </si>
+  <si>
+    <t>CritRateReduce</t>
+  </si>
+  <si>
+    <t>StrTotal</t>
+  </si>
+  <si>
+    <t>IntTotal</t>
+  </si>
+  <si>
+    <t>HpTotal</t>
+  </si>
+  <si>
+    <t>MpTotal</t>
+  </si>
+  <si>
+    <t>PDefTotal</t>
+  </si>
+  <si>
+    <t>MDefTotal</t>
+  </si>
+  <si>
+    <t>MoveSpdTotal</t>
+  </si>
+  <si>
+    <t>AtkSpdTotal</t>
+  </si>
+  <si>
+    <t>CritRateTotal</t>
+  </si>
+  <si>
+    <t>힘+</t>
+  </si>
+  <si>
+    <t>힘+%</t>
+  </si>
+  <si>
+    <t>힘증폭</t>
+  </si>
+  <si>
+    <t>힘감폭</t>
+  </si>
+  <si>
+    <t>힘총합</t>
+  </si>
+  <si>
+    <t>지능+</t>
+  </si>
+  <si>
+    <t>지능+%</t>
+  </si>
+  <si>
+    <t>지능증폭</t>
+  </si>
+  <si>
+    <t>지능감폭</t>
+  </si>
+  <si>
+    <t>지능총합</t>
+  </si>
+  <si>
+    <t>HP+</t>
+  </si>
+  <si>
+    <t>HP+%</t>
+  </si>
+  <si>
+    <t>HP증폭</t>
+  </si>
+  <si>
+    <t>HP감폭</t>
+  </si>
+  <si>
+    <t>HP총합</t>
+  </si>
+  <si>
+    <t>MP+</t>
+  </si>
+  <si>
+    <t>MP+%</t>
+  </si>
+  <si>
+    <t>MP증폭</t>
+  </si>
+  <si>
+    <t>MP감폭</t>
+  </si>
+  <si>
+    <t>MP총합</t>
+  </si>
+  <si>
+    <t>물리방어력+</t>
+  </si>
+  <si>
+    <t>물리방어력+%</t>
+  </si>
+  <si>
+    <t>물리방어력증폭</t>
+  </si>
+  <si>
+    <t>물리방어력감폭</t>
+  </si>
+  <si>
+    <t>물리방어력총합</t>
+  </si>
+  <si>
+    <t>마법방어력+</t>
+  </si>
+  <si>
+    <t>마법방어력+%</t>
+  </si>
+  <si>
+    <t>마법방어력증폭</t>
+  </si>
+  <si>
+    <t>마법방어력감폭</t>
+  </si>
+  <si>
+    <t>마법방어력총합</t>
+  </si>
+  <si>
+    <t>이동속도+</t>
+  </si>
+  <si>
+    <t>이동속도+%</t>
+  </si>
+  <si>
+    <t>이동속도증폭</t>
+  </si>
+  <si>
+    <t>이동속도감폭</t>
+  </si>
+  <si>
+    <t>이동속도총합</t>
+  </si>
+  <si>
+    <t>공격속도+</t>
+  </si>
+  <si>
+    <t>공격속도+%</t>
+  </si>
+  <si>
+    <t>공격속도증폭</t>
+  </si>
+  <si>
+    <t>공격속도감폭</t>
+  </si>
+  <si>
+    <t>공격속도총합</t>
+  </si>
+  <si>
+    <t>치명타확률+</t>
+  </si>
+  <si>
+    <t>치명타확률+%</t>
+  </si>
+  <si>
+    <t>치명타확률증폭</t>
+  </si>
+  <si>
+    <t>치명타확률감폭</t>
+  </si>
+  <si>
+    <t>치명타확률총합</t>
   </si>
 </sst>
 </file>
@@ -312,7 +691,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -322,6 +701,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -603,7 +985,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:F84"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18.5" style="1" customWidth="1"/>
@@ -790,13 +1172,13 @@
         <v>1</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
@@ -861,10 +1243,10 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="C15" s="1">
         <v>0</v>
@@ -875,183 +1257,1175 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="C16" s="1">
         <v>1</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>37</v>
+        <v>13</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="C17" s="1">
         <v>2</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>38</v>
+        <v>14</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="C18" s="1">
         <v>3</v>
       </c>
       <c r="D18" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E18" s="1" t="s">
         <v>36</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C19" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>30</v>
+        <v>37</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C20" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C21" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>8</v>
+        <v>43</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>14</v>
+        <v>44</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C22" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="C23" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>44</v>
+        <v>30</v>
+      </c>
+      <c r="E23" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C24" s="1">
+        <v>1</v>
+      </c>
+      <c r="D24" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="B24" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C24" s="1">
-        <v>0</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>30</v>
+      <c r="E24" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="C25" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="E25" s="1" t="s">
         <v>50</v>
+      </c>
+      <c r="E25" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B26" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C26" s="1">
+        <v>3</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="E26" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A27" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C27" s="1">
+        <v>4</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E27" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A28" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C28" s="1">
+        <v>5</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="E28" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A29" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C29" s="1">
+        <v>0</v>
+      </c>
+      <c r="D29" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A30" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C30" s="1">
+        <v>1</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A31" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C31" s="1">
+        <v>2</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A32" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C32" s="1">
+        <v>3</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A33" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C33" s="1">
+        <v>4</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A34" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C34" s="1">
+        <v>5</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A35" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C35" s="1">
         <v>6</v>
       </c>
-      <c r="C26" s="1">
+      <c r="D35" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A36" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C36" s="1">
+        <v>7</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A37" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C37" s="1">
+        <v>8</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A38" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C38" s="1">
+        <v>9</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A39" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C39" s="1">
+        <v>0</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A40" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C40" s="1">
+        <v>1</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A41" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C41" s="1">
         <v>2</v>
       </c>
-      <c r="D26" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="E26" s="1" t="s">
-        <v>51</v>
+      <c r="D41" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="F41" s="4"/>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A42" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C42" s="1">
+        <v>3</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A43" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C43" s="1">
+        <v>4</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A44" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C44" s="1">
+        <v>5</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A45" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C45" s="1">
+        <v>6</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="E45" s="1" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A46" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C46" s="1">
+        <v>7</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="E46" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="F46" s="4"/>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A47" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C47" s="1">
+        <v>8</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="E47" s="1" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A48" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C48" s="1">
+        <v>9</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="E48" s="1" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A49" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C49" s="1">
+        <v>10</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="E49" s="1" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A50" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C50" s="1">
+        <v>11</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="E50" s="1" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A51" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C51" s="1">
+        <v>12</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="E51" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="F51" s="4"/>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A52" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C52" s="1">
+        <v>13</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="E52" s="1" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A53" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C53" s="1">
+        <v>14</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="E53" s="1" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A54" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C54" s="1">
+        <v>15</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="E54" s="1" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A55" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C55" s="1">
+        <v>16</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E55" s="1" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A56" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C56" s="1">
+        <v>17</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="E56" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="F56" s="4"/>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A57" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C57" s="1">
+        <v>18</v>
+      </c>
+      <c r="D57" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="E57" s="1" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A58" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C58" s="1">
+        <v>19</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="E58" s="1" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A59" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C59" s="1">
+        <v>20</v>
+      </c>
+      <c r="D59" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="E59" s="1" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A60" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C60" s="1">
+        <v>21</v>
+      </c>
+      <c r="D60" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E60" s="1" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A61" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C61" s="1">
+        <v>22</v>
+      </c>
+      <c r="D61" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="E61" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="F61" s="4"/>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A62" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C62" s="1">
+        <v>23</v>
+      </c>
+      <c r="D62" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="E62" s="1" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A63" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C63" s="1">
+        <v>24</v>
+      </c>
+      <c r="D63" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="E63" s="1" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A64" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C64" s="1">
+        <v>25</v>
+      </c>
+      <c r="D64" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="E64" s="1" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A65" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C65" s="1">
+        <v>26</v>
+      </c>
+      <c r="D65" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="E65" s="1" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A66" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C66" s="1">
+        <v>27</v>
+      </c>
+      <c r="D66" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="E66" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="F66" s="4"/>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A67" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C67" s="1">
+        <v>28</v>
+      </c>
+      <c r="D67" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="E67" s="1" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A68" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C68" s="1">
+        <v>29</v>
+      </c>
+      <c r="D68" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="E68" s="1" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A69" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C69" s="1">
+        <v>30</v>
+      </c>
+      <c r="D69" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="E69" s="1" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A70" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C70" s="1">
+        <v>31</v>
+      </c>
+      <c r="D70" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="E70" s="1" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A71" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C71" s="1">
+        <v>32</v>
+      </c>
+      <c r="D71" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="E71" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="F71" s="4"/>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A72" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C72" s="1">
+        <v>33</v>
+      </c>
+      <c r="D72" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="E72" s="1" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A73" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C73" s="1">
+        <v>34</v>
+      </c>
+      <c r="D73" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="E73" s="1" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A74" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C74" s="1">
+        <v>35</v>
+      </c>
+      <c r="D74" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="E74" s="1" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A75" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C75" s="1">
+        <v>36</v>
+      </c>
+      <c r="D75" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="E75" s="1" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A76" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C76" s="1">
+        <v>37</v>
+      </c>
+      <c r="D76" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="E76" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="F76" s="4"/>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A77" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C77" s="1">
+        <v>38</v>
+      </c>
+      <c r="D77" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="E77" s="1" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A78" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C78" s="1">
+        <v>39</v>
+      </c>
+      <c r="D78" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="E78" s="1" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A79" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C79" s="1">
+        <v>40</v>
+      </c>
+      <c r="D79" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="E79" s="1" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A80" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C80" s="1">
+        <v>41</v>
+      </c>
+      <c r="D80" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="E80" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A81" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C81" s="1">
+        <v>42</v>
+      </c>
+      <c r="D81" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="E81" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="F81" s="4"/>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A82" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C82" s="1">
+        <v>43</v>
+      </c>
+      <c r="D82" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="E82" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A83" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B83" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C83" s="1">
+        <v>44</v>
+      </c>
+      <c r="D83" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="E83" s="1" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A84" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B84" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C84" s="1">
+        <v>45</v>
+      </c>
+      <c r="D84" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="E84" s="1" t="s">
+        <v>168</v>
       </c>
     </row>
   </sheetData>

--- a/Development/Common/GameData/Enum/GameEnum.xlsx
+++ b/Development/Common/GameData/Enum/GameEnum.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\project\MMOGameServerProject\Development\Common\GameData\Enum\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D863DB4-BC46-4220-9E54-69006D3DE503}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2067F61D-4F70-4193-B249-3A6185584174}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="335" uniqueCount="169">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="346" uniqueCount="174">
   <si>
     <t>MonsterGrade</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -616,6 +616,26 @@
   </si>
   <si>
     <t>치명타확률총합</t>
+  </si>
+  <si>
+    <t>Job</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Wizard</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Warrior</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>마법사</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>전사</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -985,7 +1005,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F84"/>
+  <dimension ref="A1:F87"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18.5" style="1" customWidth="1"/>
@@ -1067,10 +1087,10 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>0</v>
+        <v>169</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C5" s="1">
         <v>0</v>
@@ -1081,36 +1101,36 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>0</v>
+        <v>169</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C6" s="1">
         <v>1</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>1</v>
+        <v>170</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>16</v>
+        <v>172</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>0</v>
+        <v>169</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C7" s="1">
         <v>2</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>15</v>
+        <v>171</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>17</v>
+        <v>173</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
@@ -1121,13 +1141,10 @@
         <v>8</v>
       </c>
       <c r="C8" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
@@ -1138,67 +1155,64 @@
         <v>8</v>
       </c>
       <c r="C9" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C10" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>30</v>
+        <v>15</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C11" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>39</v>
+        <v>3</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>41</v>
+        <v>18</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C12" s="1">
+        <v>4</v>
+      </c>
+      <c r="D12" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D12" s="1" t="s">
-        <v>21</v>
-      </c>
       <c r="E12" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
@@ -1209,16 +1223,10 @@
         <v>9</v>
       </c>
       <c r="C13" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
@@ -1229,67 +1237,79 @@
         <v>9</v>
       </c>
       <c r="C14" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C15" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>30</v>
+        <v>21</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C16" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+        <v>25</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C17" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+        <v>26</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
         <v>34</v>
       </c>
@@ -1297,16 +1317,13 @@
         <v>6</v>
       </c>
       <c r="C18" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
         <v>34</v>
       </c>
@@ -1314,69 +1331,72 @@
         <v>6</v>
       </c>
       <c r="C19" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>37</v>
+        <v>12</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C20" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C21" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C22" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="C23" s="1">
         <v>0</v>
@@ -1384,45 +1404,42 @@
       <c r="D23" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="E23" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="C24" s="1">
         <v>1</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="E24" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+        <v>43</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="C25" s="1">
         <v>2</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="E25" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+        <v>46</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
         <v>47</v>
       </c>
@@ -1430,16 +1447,16 @@
         <v>33</v>
       </c>
       <c r="C26" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>51</v>
+        <v>30</v>
       </c>
       <c r="E26" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
         <v>47</v>
       </c>
@@ -1447,16 +1464,16 @@
         <v>33</v>
       </c>
       <c r="C27" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="E27" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
         <v>47</v>
       </c>
@@ -1464,64 +1481,67 @@
         <v>33</v>
       </c>
       <c r="C28" s="1">
+        <v>2</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E28" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A29" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C29" s="1">
+        <v>3</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="E29" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A30" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C30" s="1">
+        <v>4</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E30" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A31" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C31" s="1">
         <v>5</v>
       </c>
-      <c r="D28" s="1" t="s">
+      <c r="D31" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="E28" t="s">
+      <c r="E31" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A29" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C29" s="1">
-        <v>0</v>
-      </c>
-      <c r="D29" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A30" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C30" s="1">
-        <v>1</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="E30" s="1" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A31" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C31" s="1">
-        <v>2</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="E31" s="1" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
         <v>60</v>
       </c>
@@ -1529,13 +1549,10 @@
         <v>33</v>
       </c>
       <c r="C32" s="1">
-        <v>3</v>
-      </c>
-      <c r="D32" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="E32" s="1" t="s">
-        <v>72</v>
+        <v>0</v>
+      </c>
+      <c r="D32" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
@@ -1546,13 +1563,13 @@
         <v>33</v>
       </c>
       <c r="C33" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
@@ -1563,13 +1580,13 @@
         <v>33</v>
       </c>
       <c r="C34" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
@@ -1580,13 +1597,13 @@
         <v>33</v>
       </c>
       <c r="C35" s="1">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
@@ -1597,13 +1614,13 @@
         <v>33</v>
       </c>
       <c r="C36" s="1">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
@@ -1614,13 +1631,13 @@
         <v>33</v>
       </c>
       <c r="C37" s="1">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
@@ -1631,63 +1648,65 @@
         <v>33</v>
       </c>
       <c r="C38" s="1">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
-        <v>33</v>
+        <v>60</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>33</v>
       </c>
       <c r="C39" s="1">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>30</v>
+        <v>67</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
-        <v>33</v>
+        <v>60</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>33</v>
       </c>
       <c r="C40" s="1">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>124</v>
+        <v>77</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
-        <v>33</v>
+        <v>60</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>33</v>
       </c>
       <c r="C41" s="1">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>88</v>
+        <v>69</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="F41" s="4"/>
+        <v>78</v>
+      </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
@@ -1697,13 +1716,10 @@
         <v>33</v>
       </c>
       <c r="C42" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="E42" s="1" t="s">
-        <v>126</v>
+        <v>30</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
@@ -1714,13 +1730,13 @@
         <v>33</v>
       </c>
       <c r="C43" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>106</v>
+        <v>79</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.3">
@@ -1731,14 +1747,15 @@
         <v>33</v>
       </c>
       <c r="C44" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>115</v>
+        <v>88</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>128</v>
-      </c>
+        <v>125</v>
+      </c>
+      <c r="F44" s="4"/>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
@@ -1748,13 +1765,13 @@
         <v>33</v>
       </c>
       <c r="C45" s="1">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>80</v>
+        <v>97</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
@@ -1765,15 +1782,14 @@
         <v>33</v>
       </c>
       <c r="C46" s="1">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>89</v>
+        <v>106</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="F46" s="4"/>
+        <v>127</v>
+      </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="s">
@@ -1783,13 +1799,13 @@
         <v>33</v>
       </c>
       <c r="C47" s="1">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>98</v>
+        <v>115</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.3">
@@ -1800,13 +1816,13 @@
         <v>33</v>
       </c>
       <c r="C48" s="1">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>107</v>
+        <v>80</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.3">
@@ -1817,14 +1833,15 @@
         <v>33</v>
       </c>
       <c r="C49" s="1">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>116</v>
+        <v>89</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>133</v>
-      </c>
+        <v>130</v>
+      </c>
+      <c r="F49" s="4"/>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="s">
@@ -1834,13 +1851,13 @@
         <v>33</v>
       </c>
       <c r="C50" s="1">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>81</v>
+        <v>98</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.3">
@@ -1851,15 +1868,14 @@
         <v>33</v>
       </c>
       <c r="C51" s="1">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>90</v>
+        <v>107</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="F51" s="4"/>
+        <v>132</v>
+      </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
@@ -1869,13 +1885,13 @@
         <v>33</v>
       </c>
       <c r="C52" s="1">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.3">
@@ -1886,13 +1902,13 @@
         <v>33</v>
       </c>
       <c r="C53" s="1">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>108</v>
+        <v>81</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.3">
@@ -1903,14 +1919,15 @@
         <v>33</v>
       </c>
       <c r="C54" s="1">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>117</v>
+        <v>90</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>138</v>
-      </c>
+        <v>135</v>
+      </c>
+      <c r="F54" s="4"/>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
@@ -1920,13 +1937,13 @@
         <v>33</v>
       </c>
       <c r="C55" s="1">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>82</v>
+        <v>99</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.3">
@@ -1937,15 +1954,14 @@
         <v>33</v>
       </c>
       <c r="C56" s="1">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>91</v>
+        <v>108</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="F56" s="4"/>
+        <v>137</v>
+      </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
@@ -1955,13 +1971,13 @@
         <v>33</v>
       </c>
       <c r="C57" s="1">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>100</v>
+        <v>117</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.3">
@@ -1972,13 +1988,13 @@
         <v>33</v>
       </c>
       <c r="C58" s="1">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>109</v>
+        <v>82</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.3">
@@ -1989,14 +2005,15 @@
         <v>33</v>
       </c>
       <c r="C59" s="1">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>118</v>
+        <v>91</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>143</v>
-      </c>
+        <v>140</v>
+      </c>
+      <c r="F59" s="4"/>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
@@ -2006,13 +2023,13 @@
         <v>33</v>
       </c>
       <c r="C60" s="1">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>83</v>
+        <v>100</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.3">
@@ -2023,15 +2040,14 @@
         <v>33</v>
       </c>
       <c r="C61" s="1">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>92</v>
+        <v>109</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="F61" s="4"/>
+        <v>142</v>
+      </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A62" s="1" t="s">
@@ -2041,13 +2057,13 @@
         <v>33</v>
       </c>
       <c r="C62" s="1">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.3">
@@ -2058,13 +2074,13 @@
         <v>33</v>
       </c>
       <c r="C63" s="1">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>110</v>
+        <v>83</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.3">
@@ -2075,14 +2091,15 @@
         <v>33</v>
       </c>
       <c r="C64" s="1">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>119</v>
+        <v>92</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>148</v>
-      </c>
+        <v>145</v>
+      </c>
+      <c r="F64" s="4"/>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A65" s="1" t="s">
@@ -2092,13 +2109,13 @@
         <v>33</v>
       </c>
       <c r="C65" s="1">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>84</v>
+        <v>101</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.3">
@@ -2109,15 +2126,14 @@
         <v>33</v>
       </c>
       <c r="C66" s="1">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>93</v>
+        <v>110</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="F66" s="4"/>
+        <v>147</v>
+      </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A67" s="1" t="s">
@@ -2127,13 +2143,13 @@
         <v>33</v>
       </c>
       <c r="C67" s="1">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.3">
@@ -2144,13 +2160,13 @@
         <v>33</v>
       </c>
       <c r="C68" s="1">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>111</v>
+        <v>84</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.3">
@@ -2161,14 +2177,15 @@
         <v>33</v>
       </c>
       <c r="C69" s="1">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>120</v>
+        <v>93</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>153</v>
-      </c>
+        <v>150</v>
+      </c>
+      <c r="F69" s="4"/>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A70" s="1" t="s">
@@ -2178,13 +2195,13 @@
         <v>33</v>
       </c>
       <c r="C70" s="1">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.3">
@@ -2195,15 +2212,14 @@
         <v>33</v>
       </c>
       <c r="C71" s="1">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>94</v>
+        <v>111</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="F71" s="4"/>
+        <v>152</v>
+      </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A72" s="1" t="s">
@@ -2213,13 +2229,13 @@
         <v>33</v>
       </c>
       <c r="C72" s="1">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>103</v>
+        <v>120</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.3">
@@ -2230,13 +2246,13 @@
         <v>33</v>
       </c>
       <c r="C73" s="1">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>112</v>
+        <v>85</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.3">
@@ -2247,14 +2263,15 @@
         <v>33</v>
       </c>
       <c r="C74" s="1">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>121</v>
+        <v>94</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>158</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="F74" s="4"/>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A75" s="1" t="s">
@@ -2264,13 +2281,13 @@
         <v>33</v>
       </c>
       <c r="C75" s="1">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>86</v>
+        <v>103</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.3">
@@ -2281,15 +2298,14 @@
         <v>33</v>
       </c>
       <c r="C76" s="1">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>95</v>
+        <v>112</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="F76" s="4"/>
+        <v>157</v>
+      </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A77" s="1" t="s">
@@ -2299,13 +2315,13 @@
         <v>33</v>
       </c>
       <c r="C77" s="1">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>104</v>
+        <v>121</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.3">
@@ -2316,13 +2332,13 @@
         <v>33</v>
       </c>
       <c r="C78" s="1">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>113</v>
+        <v>86</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.3">
@@ -2333,14 +2349,15 @@
         <v>33</v>
       </c>
       <c r="C79" s="1">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>122</v>
+        <v>95</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>163</v>
-      </c>
+        <v>160</v>
+      </c>
+      <c r="F79" s="4"/>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A80" s="1" t="s">
@@ -2350,13 +2367,13 @@
         <v>33</v>
       </c>
       <c r="C80" s="1">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>87</v>
+        <v>104</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.3">
@@ -2367,15 +2384,14 @@
         <v>33</v>
       </c>
       <c r="C81" s="1">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>96</v>
+        <v>113</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="F81" s="4"/>
+        <v>162</v>
+      </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A82" s="1" t="s">
@@ -2385,13 +2401,13 @@
         <v>33</v>
       </c>
       <c r="C82" s="1">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.3">
@@ -2402,13 +2418,13 @@
         <v>33</v>
       </c>
       <c r="C83" s="1">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>114</v>
+        <v>87</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.3">
@@ -2419,12 +2435,64 @@
         <v>33</v>
       </c>
       <c r="C84" s="1">
+        <v>42</v>
+      </c>
+      <c r="D84" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="E84" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="F84" s="4"/>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A85" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B85" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C85" s="1">
+        <v>43</v>
+      </c>
+      <c r="D85" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="E85" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A86" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B86" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C86" s="1">
+        <v>44</v>
+      </c>
+      <c r="D86" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="E86" s="1" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A87" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B87" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C87" s="1">
         <v>45</v>
       </c>
-      <c r="D84" s="1" t="s">
+      <c r="D87" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="E84" s="1" t="s">
+      <c r="E87" s="1" t="s">
         <v>168</v>
       </c>
     </row>

--- a/Development/Common/GameData/Enum/GameEnum.xlsx
+++ b/Development/Common/GameData/Enum/GameEnum.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\project\MMOGameServerProject\Development\Common\GameData\Enum\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2067F61D-4F70-4193-B249-3A6185584174}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{204534C3-EBD9-4A37-B28D-BCCBF65ADB88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38280" yWindow="5355" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Enum" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="346" uniqueCount="174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="424" uniqueCount="214">
   <si>
     <t>MonsterGrade</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -622,10 +622,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Wizard</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Warrior</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -635,6 +631,139 @@
   </si>
   <si>
     <t>전사</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Mage</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SkillCategory</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>StationaryCast</t>
+  </si>
+  <si>
+    <t>제자리시전</t>
+  </si>
+  <si>
+    <t>MobileCast</t>
+  </si>
+  <si>
+    <t>이동시전</t>
+  </si>
+  <si>
+    <t>Movement</t>
+  </si>
+  <si>
+    <t>이동기</t>
+  </si>
+  <si>
+    <t>Skill</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>스킬 사용중 움직일 수 없음</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>스킬 사용중 움직일 수 있음</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이동전용 스킬</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>EffectType</t>
+  </si>
+  <si>
+    <t>Projectile</t>
+  </si>
+  <si>
+    <t>InstantDamage</t>
+  </si>
+  <si>
+    <t>TickDamageArea</t>
+  </si>
+  <si>
+    <t>Buff</t>
+  </si>
+  <si>
+    <t>VFX</t>
+  </si>
+  <si>
+    <t>강제이동</t>
+  </si>
+  <si>
+    <t>투사체</t>
+  </si>
+  <si>
+    <t>즉시타격</t>
+  </si>
+  <si>
+    <t>지속타격영역</t>
+  </si>
+  <si>
+    <t>버프</t>
+  </si>
+  <si>
+    <t>시각효과</t>
+  </si>
+  <si>
+    <t>스킬 이펙트 종류를 나타낸다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RangeShape</t>
+  </si>
+  <si>
+    <t>Circle</t>
+  </si>
+  <si>
+    <t>Rectangle</t>
+  </si>
+  <si>
+    <t>Sector</t>
+  </si>
+  <si>
+    <t>원형</t>
+  </si>
+  <si>
+    <t>사각형</t>
+  </si>
+  <si>
+    <t>부채꼴</t>
+  </si>
+  <si>
+    <t>스킬 범위의 모양</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>OriginType</t>
+  </si>
+  <si>
+    <t>CasterCenter</t>
+  </si>
+  <si>
+    <t>TargetCenter</t>
+  </si>
+  <si>
+    <t>CasterForward</t>
+  </si>
+  <si>
+    <t>캐릭터 위치 중심</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>타겟 위치 중심</t>
+  </si>
+  <si>
+    <t>캐릭터 위치에서 전방으로 뻗음</t>
+  </si>
+  <si>
+    <t>효과의 발생 기준 위치</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1005,7 +1134,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F87"/>
+  <dimension ref="A1:F106"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18.5" style="1" customWidth="1"/>
@@ -1110,10 +1239,10 @@
         <v>1</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
@@ -1127,10 +1256,10 @@
         <v>2</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
@@ -2494,6 +2623,336 @@
       </c>
       <c r="E87" s="1" t="s">
         <v>168</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A88" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="B88" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="C88" s="1">
+        <v>0</v>
+      </c>
+      <c r="D88" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A89" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="B89" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="C89" s="1">
+        <v>1</v>
+      </c>
+      <c r="D89" t="s">
+        <v>175</v>
+      </c>
+      <c r="E89" t="s">
+        <v>176</v>
+      </c>
+      <c r="F89" s="1" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A90" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="B90" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="C90" s="1">
+        <v>2</v>
+      </c>
+      <c r="D90" t="s">
+        <v>177</v>
+      </c>
+      <c r="E90" t="s">
+        <v>178</v>
+      </c>
+      <c r="F90" s="1" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A91" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="B91" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="C91" s="1">
+        <v>3</v>
+      </c>
+      <c r="D91" t="s">
+        <v>179</v>
+      </c>
+      <c r="E91" t="s">
+        <v>180</v>
+      </c>
+      <c r="F91" s="1" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A92" t="s">
+        <v>185</v>
+      </c>
+      <c r="B92" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="C92" s="1">
+        <v>0</v>
+      </c>
+      <c r="D92" t="s">
+        <v>49</v>
+      </c>
+      <c r="E92"/>
+      <c r="F92" s="1" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A93" t="s">
+        <v>185</v>
+      </c>
+      <c r="B93" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="C93" s="1">
+        <v>1</v>
+      </c>
+      <c r="D93" t="s">
+        <v>179</v>
+      </c>
+      <c r="E93" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A94" t="s">
+        <v>185</v>
+      </c>
+      <c r="B94" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="C94" s="1">
+        <v>2</v>
+      </c>
+      <c r="D94" t="s">
+        <v>186</v>
+      </c>
+      <c r="E94" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A95" t="s">
+        <v>185</v>
+      </c>
+      <c r="B95" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="C95" s="1">
+        <v>3</v>
+      </c>
+      <c r="D95" t="s">
+        <v>187</v>
+      </c>
+      <c r="E95" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A96" t="s">
+        <v>185</v>
+      </c>
+      <c r="B96" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="C96" s="1">
+        <v>4</v>
+      </c>
+      <c r="D96" t="s">
+        <v>188</v>
+      </c>
+      <c r="E96" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A97" t="s">
+        <v>185</v>
+      </c>
+      <c r="B97" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="C97" s="1">
+        <v>5</v>
+      </c>
+      <c r="D97" t="s">
+        <v>189</v>
+      </c>
+      <c r="E97" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A98" t="s">
+        <v>185</v>
+      </c>
+      <c r="B98" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="C98" s="1">
+        <v>6</v>
+      </c>
+      <c r="D98" t="s">
+        <v>190</v>
+      </c>
+      <c r="E98" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A99" t="s">
+        <v>198</v>
+      </c>
+      <c r="B99" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="C99" s="1">
+        <v>0</v>
+      </c>
+      <c r="D99" t="s">
+        <v>30</v>
+      </c>
+      <c r="F99" s="1" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A100" t="s">
+        <v>198</v>
+      </c>
+      <c r="B100" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="C100" s="1">
+        <v>1</v>
+      </c>
+      <c r="D100" t="s">
+        <v>199</v>
+      </c>
+      <c r="E100" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A101" t="s">
+        <v>198</v>
+      </c>
+      <c r="B101" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="C101" s="1">
+        <v>2</v>
+      </c>
+      <c r="D101" t="s">
+        <v>200</v>
+      </c>
+      <c r="E101" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A102" t="s">
+        <v>198</v>
+      </c>
+      <c r="B102" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="C102" s="1">
+        <v>3</v>
+      </c>
+      <c r="D102" t="s">
+        <v>201</v>
+      </c>
+      <c r="E102" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A103" t="s">
+        <v>206</v>
+      </c>
+      <c r="B103" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="C103" s="1">
+        <v>0</v>
+      </c>
+      <c r="D103" t="s">
+        <v>30</v>
+      </c>
+      <c r="F103" s="1" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A104" t="s">
+        <v>206</v>
+      </c>
+      <c r="B104" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="C104" s="1">
+        <v>1</v>
+      </c>
+      <c r="D104" t="s">
+        <v>207</v>
+      </c>
+      <c r="E104" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A105" t="s">
+        <v>206</v>
+      </c>
+      <c r="B105" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="C105" s="1">
+        <v>2</v>
+      </c>
+      <c r="D105" t="s">
+        <v>208</v>
+      </c>
+      <c r="E105" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A106" t="s">
+        <v>206</v>
+      </c>
+      <c r="B106" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="C106" s="1">
+        <v>3</v>
+      </c>
+      <c r="D106" t="s">
+        <v>209</v>
+      </c>
+      <c r="E106" t="s">
+        <v>212</v>
       </c>
     </row>
   </sheetData>

--- a/Development/Common/GameData/Enum/GameEnum.xlsx
+++ b/Development/Common/GameData/Enum/GameEnum.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\project\MMOGameServerProject\Development\Common\GameData\Enum\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{204534C3-EBD9-4A37-B28D-BCCBF65ADB88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B93583AB-17EE-4503-AF0D-F870ED581CA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="5355" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38865" yWindow="5910" windowWidth="27360" windowHeight="14340" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Enum" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="424" uniqueCount="214">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="468" uniqueCount="239">
   <si>
     <t>MonsterGrade</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -765,6 +765,83 @@
   <si>
     <t>효과의 발생 기준 위치</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BuffCategory</t>
+  </si>
+  <si>
+    <t>BuffCategory</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Buff</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BuffStackPolicy</t>
+  </si>
+  <si>
+    <t>PeriodicEffect</t>
+  </si>
+  <si>
+    <t>Debuff</t>
+  </si>
+  <si>
+    <t>Refresh</t>
+  </si>
+  <si>
+    <t>Stack</t>
+  </si>
+  <si>
+    <t>Ignore</t>
+  </si>
+  <si>
+    <t>DamageHp</t>
+  </si>
+  <si>
+    <t>HealHp</t>
+  </si>
+  <si>
+    <t>이로운효과</t>
+  </si>
+  <si>
+    <t>해로운효과</t>
+  </si>
+  <si>
+    <t>디스펠 대상</t>
+  </si>
+  <si>
+    <t>시간갱신</t>
+  </si>
+  <si>
+    <t>재적용 시 지속시간만 리셋</t>
+  </si>
+  <si>
+    <t>스택증가</t>
+  </si>
+  <si>
+    <t>재적용 시 스택+1 (MaxStack까지)</t>
+  </si>
+  <si>
+    <t>무시</t>
+  </si>
+  <si>
+    <t>이미 있으면 무시</t>
+  </si>
+  <si>
+    <t>주기효과 없음</t>
+  </si>
+  <si>
+    <t>HP감소</t>
+  </si>
+  <si>
+    <t>DoT</t>
+  </si>
+  <si>
+    <t>HP회복</t>
+  </si>
+  <si>
+    <t>HoT</t>
   </si>
 </sst>
 </file>
@@ -1134,7 +1211,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F106"/>
+  <dimension ref="A1:F116"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18.5" style="1" customWidth="1"/>
@@ -2955,6 +3032,188 @@
         <v>212</v>
       </c>
     </row>
+    <row r="107" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A107" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="B107" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="C107" s="1">
+        <v>0</v>
+      </c>
+      <c r="D107" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="E107" s="1" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A108" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="B108" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="C108" s="1">
+        <v>1</v>
+      </c>
+      <c r="D108" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="E108" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="F108" s="1" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A109" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="B109" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="C109" s="1">
+        <v>2</v>
+      </c>
+      <c r="D109" s="1" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A110" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="B110" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="C110" s="1">
+        <v>0</v>
+      </c>
+      <c r="D110" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A111" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="B111" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="C111" s="1">
+        <v>1</v>
+      </c>
+      <c r="D111" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="E111" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="F111" s="1" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A112" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="B112" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="C112" s="1">
+        <v>2</v>
+      </c>
+      <c r="D112" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="E112" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="F112" s="1" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A113" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="B113" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="C113" s="1">
+        <v>3</v>
+      </c>
+      <c r="D113" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="E113" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="F113" s="1" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A114" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="B114" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="C114" s="1">
+        <v>0</v>
+      </c>
+      <c r="D114" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="E114" s="1" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="115" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A115" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="B115" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="C115" s="1">
+        <v>1</v>
+      </c>
+      <c r="D115" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="E115" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="F115" s="1" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A116" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="B116" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="C116" s="1">
+        <v>2</v>
+      </c>
+      <c r="D116" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="E116" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="F116" s="1" t="s">
+        <v>238</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Development/Common/GameData/Enum/GameEnum.xlsx
+++ b/Development/Common/GameData/Enum/GameEnum.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\project\MMOGameServerProject\Development\Common\GameData\Enum\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B93583AB-17EE-4503-AF0D-F870ED581CA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F1A06FA-7B22-4C10-A01A-AA4727B2D29A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38865" yWindow="5910" windowWidth="27360" windowHeight="14340" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Enum" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="468" uniqueCount="239">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="484" uniqueCount="249">
   <si>
     <t>MonsterGrade</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -638,25 +638,12 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>SkillCategory</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>StationaryCast</t>
-  </si>
-  <si>
     <t>제자리시전</t>
   </si>
   <si>
-    <t>MobileCast</t>
-  </si>
-  <si>
     <t>이동시전</t>
   </si>
   <si>
-    <t>Movement</t>
-  </si>
-  <si>
     <t>이동기</t>
   </si>
   <si>
@@ -676,97 +663,12 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>EffectType</t>
-  </si>
-  <si>
-    <t>Projectile</t>
-  </si>
-  <si>
-    <t>InstantDamage</t>
-  </si>
-  <si>
-    <t>TickDamageArea</t>
-  </si>
-  <si>
     <t>Buff</t>
   </si>
   <si>
-    <t>VFX</t>
-  </si>
-  <si>
-    <t>강제이동</t>
-  </si>
-  <si>
-    <t>투사체</t>
-  </si>
-  <si>
-    <t>즉시타격</t>
-  </si>
-  <si>
-    <t>지속타격영역</t>
-  </si>
-  <si>
-    <t>버프</t>
-  </si>
-  <si>
-    <t>시각효과</t>
-  </si>
-  <si>
-    <t>스킬 이펙트 종류를 나타낸다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>RangeShape</t>
-  </si>
-  <si>
     <t>Circle</t>
   </si>
   <si>
-    <t>Rectangle</t>
-  </si>
-  <si>
-    <t>Sector</t>
-  </si>
-  <si>
-    <t>원형</t>
-  </si>
-  <si>
-    <t>사각형</t>
-  </si>
-  <si>
-    <t>부채꼴</t>
-  </si>
-  <si>
-    <t>스킬 범위의 모양</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>OriginType</t>
-  </si>
-  <si>
-    <t>CasterCenter</t>
-  </si>
-  <si>
-    <t>TargetCenter</t>
-  </si>
-  <si>
-    <t>CasterForward</t>
-  </si>
-  <si>
-    <t>캐릭터 위치 중심</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>타겟 위치 중심</t>
-  </si>
-  <si>
-    <t>캐릭터 위치에서 전방으로 뻗음</t>
-  </si>
-  <si>
-    <t>효과의 발생 기준 위치</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>BuffCategory</t>
   </si>
   <si>
@@ -842,13 +744,163 @@
   </si>
   <si>
     <t>HoT</t>
+  </si>
+  <si>
+    <t>Stationary</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Mobile</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Mobility</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>다음페이즈 스킬이 트리거되는 기준 위치</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>다음페이즈 스킬이 트리거되는 타이밍</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>OnStart</t>
+  </si>
+  <si>
+    <t>AfterEnd</t>
+  </si>
+  <si>
+    <t>AfterDelay</t>
+  </si>
+  <si>
+    <t>이전 스킬 lifetime 종료 직후</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이전 스킬 발동과 동시</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이전 스킬 litetime 종료 + NextTriggerDelayMs</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>캐스터 현재 위치</t>
+  </si>
+  <si>
+    <t>CasterPos</t>
+  </si>
+  <si>
+    <t>CasterFront</t>
+  </si>
+  <si>
+    <t>PrevCenter</t>
+  </si>
+  <si>
+    <t>캐스터 정면 + CasterFrontDistance</t>
+  </si>
+  <si>
+    <t>이전 페이즈 중심</t>
+  </si>
+  <si>
+    <t>PrevEnd</t>
+  </si>
+  <si>
+    <t>이전 페이즈 종료 위치</t>
+  </si>
+  <si>
+    <t>Static</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Linear</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ContactHit</t>
+  </si>
+  <si>
+    <t>Area</t>
+  </si>
+  <si>
+    <t>Obb</t>
+  </si>
+  <si>
+    <t>스킬 효과의 위치가 시간에 따라 어떻게 변하는지 결정</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>고정 (얼음지대, 화염지대, 전격방출, 메테오 착탄 등)</t>
+  </si>
+  <si>
+    <t>직선 등속 (이동하는 장판 = 하이브리드)</t>
+  </si>
+  <si>
+    <t>스킬 대미지를 어떻게 주는지 결정</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>투사체 접촉 시 1회. 클라 hit 보고 기반 → ProjectileGroup</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>서버 주도 범위 틱 → AreaEffect. 틱 횟수/간격이 instant(1회)/periodic(N회) 을 결정.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>EffectShape — 스킬/효과의 범위 모양 (X-Z 평면)
+범위 판정은 모두 X-Z 평면에서 한다 (높이 Y 는 무시). 게임이 쿼터뷰 평면 기반이라 대미지 범위는 평면 모양으로 충분하다.
+중심 좌표(center)는 모양에 넣지 않는다. 이동하는 효과는 매 tick center 가 달라지므로 center 는 판정 시점에 인자로 받고, 모양 자체(반지름/크기/방향)만 보관한다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>원 (전격방출, 메테오 착탄, 파이어볼 폭발 등)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>방향이 있는 직사각형, Oriented Bounding Box (얼음지대, 블레이즈)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SkillCastClass</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>NextSkillOrigin</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>NextSkillTiming</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SkillEffectMotion</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SkillEffectDamage</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SkillEffectShape</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Unique</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>유니크</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -876,6 +928,20 @@
       <b/>
       <sz val="11"/>
       <color theme="0"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial Unicode MS"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="맑은 고딕"/>
       <family val="3"/>
       <charset val="129"/>
@@ -917,7 +983,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -930,6 +996,11 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1211,10 +1282,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F116"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:F120"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="18.5" style="1" customWidth="1"/>
+    <col min="1" max="1" width="22.75" style="1" customWidth="1"/>
     <col min="2" max="2" width="30.25" style="1" customWidth="1"/>
     <col min="3" max="3" width="26.125" style="1" customWidth="1"/>
     <col min="4" max="4" width="29.125" style="1" customWidth="1"/>
@@ -1223,7 +1294,7 @@
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="3" customFormat="1" ht="33" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" s="3" customFormat="1" ht="33">
       <c r="A1" s="2" t="s">
         <v>4</v>
       </c>
@@ -1243,7 +1314,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6">
       <c r="A2" s="1" t="s">
         <v>10</v>
       </c>
@@ -1257,7 +1328,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6">
       <c r="A3" s="1" t="s">
         <v>10</v>
       </c>
@@ -1274,7 +1345,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6">
       <c r="A4" s="1" t="s">
         <v>10</v>
       </c>
@@ -1291,7 +1362,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6">
       <c r="A5" s="1" t="s">
         <v>169</v>
       </c>
@@ -1305,7 +1376,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6">
       <c r="A6" s="1" t="s">
         <v>169</v>
       </c>
@@ -1322,7 +1393,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6">
       <c r="A7" s="1" t="s">
         <v>169</v>
       </c>
@@ -1339,7 +1410,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6">
       <c r="A8" s="1" t="s">
         <v>0</v>
       </c>
@@ -1353,7 +1424,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6">
       <c r="A9" s="1" t="s">
         <v>0</v>
       </c>
@@ -1370,7 +1441,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6">
       <c r="A10" s="1" t="s">
         <v>0</v>
       </c>
@@ -1387,7 +1458,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6">
       <c r="A11" s="1" t="s">
         <v>0</v>
       </c>
@@ -1404,7 +1475,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6">
       <c r="A12" s="1" t="s">
         <v>0</v>
       </c>
@@ -1415,27 +1486,30 @@
         <v>4</v>
       </c>
       <c r="D12" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13" s="1">
+        <v>5</v>
+      </c>
+      <c r="D13" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E12" s="1" t="s">
+      <c r="E13" s="1" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A13" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="1">
-        <v>0</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6">
       <c r="A14" s="1" t="s">
         <v>20</v>
       </c>
@@ -1443,19 +1517,13 @@
         <v>9</v>
       </c>
       <c r="C14" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
       <c r="A15" s="1" t="s">
         <v>20</v>
       </c>
@@ -1463,19 +1531,19 @@
         <v>9</v>
       </c>
       <c r="C15" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
       <c r="A16" s="1" t="s">
         <v>20</v>
       </c>
@@ -1483,19 +1551,19 @@
         <v>9</v>
       </c>
       <c r="C16" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
       <c r="A17" s="1" t="s">
         <v>20</v>
       </c>
@@ -1503,33 +1571,39 @@
         <v>9</v>
       </c>
       <c r="C17" s="1">
+        <v>3</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C18" s="1">
         <v>4</v>
       </c>
-      <c r="D17" s="1" t="s">
+      <c r="D18" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="E17" s="1" t="s">
+      <c r="E18" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="F17" s="1" t="s">
+      <c r="F18" s="1" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C18" s="1">
-        <v>0</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6">
       <c r="A19" s="1" t="s">
         <v>34</v>
       </c>
@@ -1537,16 +1611,13 @@
         <v>6</v>
       </c>
       <c r="C19" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6">
       <c r="A20" s="1" t="s">
         <v>34</v>
       </c>
@@ -1554,16 +1625,16 @@
         <v>6</v>
       </c>
       <c r="C20" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6">
       <c r="A21" s="1" t="s">
         <v>34</v>
       </c>
@@ -1571,16 +1642,16 @@
         <v>6</v>
       </c>
       <c r="C21" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6">
       <c r="A22" s="1" t="s">
         <v>34</v>
       </c>
@@ -1588,30 +1659,33 @@
         <v>6</v>
       </c>
       <c r="C22" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6">
       <c r="A23" s="1" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C23" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+        <v>37</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6">
       <c r="A24" s="1" t="s">
         <v>42</v>
       </c>
@@ -1619,16 +1693,13 @@
         <v>6</v>
       </c>
       <c r="C24" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="E24" s="1" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6">
       <c r="A25" s="1" t="s">
         <v>42</v>
       </c>
@@ -1636,33 +1707,33 @@
         <v>6</v>
       </c>
       <c r="C25" s="1">
+        <v>1</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6">
+      <c r="A26" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C26" s="1">
         <v>2</v>
       </c>
-      <c r="D25" s="1" t="s">
+      <c r="D26" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="E25" s="1" t="s">
+      <c r="E26" s="1" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A26" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C26" s="1">
-        <v>0</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="E26" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:6">
       <c r="A27" s="1" t="s">
         <v>47</v>
       </c>
@@ -1670,16 +1741,16 @@
         <v>33</v>
       </c>
       <c r="C27" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="E27" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6">
       <c r="A28" s="1" t="s">
         <v>47</v>
       </c>
@@ -1687,16 +1758,16 @@
         <v>33</v>
       </c>
       <c r="C28" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E28" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6">
       <c r="A29" s="1" t="s">
         <v>47</v>
       </c>
@@ -1704,16 +1775,16 @@
         <v>33</v>
       </c>
       <c r="C29" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E29" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6">
       <c r="A30" s="1" t="s">
         <v>47</v>
       </c>
@@ -1721,16 +1792,16 @@
         <v>33</v>
       </c>
       <c r="C30" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E30" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6">
       <c r="A31" s="1" t="s">
         <v>47</v>
       </c>
@@ -1738,30 +1809,33 @@
         <v>33</v>
       </c>
       <c r="C31" s="1">
+        <v>4</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E31" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6">
+      <c r="A32" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C32" s="1">
         <v>5</v>
       </c>
-      <c r="D31" s="1" t="s">
+      <c r="D32" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="E31" t="s">
+      <c r="E32" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A32" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C32" s="1">
-        <v>0</v>
-      </c>
-      <c r="D32" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:6">
       <c r="A33" s="1" t="s">
         <v>60</v>
       </c>
@@ -1769,16 +1843,13 @@
         <v>33</v>
       </c>
       <c r="C33" s="1">
-        <v>1</v>
-      </c>
-      <c r="D33" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="E33" s="1" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="D33" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6">
       <c r="A34" s="1" t="s">
         <v>60</v>
       </c>
@@ -1786,16 +1857,16 @@
         <v>33</v>
       </c>
       <c r="C34" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6">
       <c r="A35" s="1" t="s">
         <v>60</v>
       </c>
@@ -1803,16 +1874,16 @@
         <v>33</v>
       </c>
       <c r="C35" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6">
       <c r="A36" s="1" t="s">
         <v>60</v>
       </c>
@@ -1820,16 +1891,16 @@
         <v>33</v>
       </c>
       <c r="C36" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6">
       <c r="A37" s="1" t="s">
         <v>60</v>
       </c>
@@ -1837,16 +1908,16 @@
         <v>33</v>
       </c>
       <c r="C37" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6">
       <c r="A38" s="1" t="s">
         <v>60</v>
       </c>
@@ -1854,16 +1925,16 @@
         <v>33</v>
       </c>
       <c r="C38" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6">
       <c r="A39" s="1" t="s">
         <v>60</v>
       </c>
@@ -1871,16 +1942,16 @@
         <v>33</v>
       </c>
       <c r="C39" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6">
       <c r="A40" s="1" t="s">
         <v>60</v>
       </c>
@@ -1888,16 +1959,16 @@
         <v>33</v>
       </c>
       <c r="C40" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6">
       <c r="A41" s="1" t="s">
         <v>60</v>
       </c>
@@ -1905,1264 +1976,1261 @@
         <v>33</v>
       </c>
       <c r="C41" s="1">
+        <v>8</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6">
+      <c r="A42" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C42" s="1">
         <v>9</v>
       </c>
-      <c r="D41" s="1" t="s">
+      <c r="D42" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="E41" s="1" t="s">
+      <c r="E42" s="1" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A42" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C42" s="1">
+    <row r="43" spans="1:6">
+      <c r="A43" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C43" s="1">
         <v>0</v>
       </c>
-      <c r="D42" s="1" t="s">
+      <c r="D43" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A43" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C43" s="1">
+    <row r="44" spans="1:6">
+      <c r="A44" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C44" s="1">
         <v>1</v>
       </c>
-      <c r="D43" s="1" t="s">
+      <c r="D44" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="E43" s="1" t="s">
+      <c r="E44" s="1" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A44" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B44" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C44" s="1">
+    <row r="45" spans="1:6">
+      <c r="A45" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C45" s="1">
         <v>2</v>
       </c>
-      <c r="D44" s="1" t="s">
+      <c r="D45" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="E44" s="1" t="s">
+      <c r="E45" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="F44" s="4"/>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A45" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C45" s="1">
+      <c r="F45" s="4"/>
+    </row>
+    <row r="46" spans="1:6">
+      <c r="A46" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C46" s="1">
         <v>3</v>
       </c>
-      <c r="D45" s="1" t="s">
+      <c r="D46" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="E45" s="1" t="s">
+      <c r="E46" s="1" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A46" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B46" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C46" s="1">
+    <row r="47" spans="1:6">
+      <c r="A47" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C47" s="1">
         <v>4</v>
       </c>
-      <c r="D46" s="1" t="s">
+      <c r="D47" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="E46" s="1" t="s">
+      <c r="E47" s="1" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A47" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C47" s="1">
+    <row r="48" spans="1:6">
+      <c r="A48" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C48" s="1">
         <v>5</v>
       </c>
-      <c r="D47" s="1" t="s">
+      <c r="D48" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="E47" s="1" t="s">
+      <c r="E48" s="1" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A48" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C48" s="1">
+    <row r="49" spans="1:6">
+      <c r="A49" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C49" s="1">
         <v>6</v>
       </c>
-      <c r="D48" s="1" t="s">
+      <c r="D49" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="E48" s="1" t="s">
+      <c r="E49" s="1" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A49" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C49" s="1">
+    <row r="50" spans="1:6">
+      <c r="A50" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C50" s="1">
         <v>7</v>
       </c>
-      <c r="D49" s="1" t="s">
+      <c r="D50" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="E49" s="1" t="s">
+      <c r="E50" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="F49" s="4"/>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A50" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C50" s="1">
+      <c r="F50" s="4"/>
+    </row>
+    <row r="51" spans="1:6">
+      <c r="A51" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C51" s="1">
         <v>8</v>
       </c>
-      <c r="D50" s="1" t="s">
+      <c r="D51" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="E50" s="1" t="s">
+      <c r="E51" s="1" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A51" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B51" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C51" s="1">
+    <row r="52" spans="1:6">
+      <c r="A52" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C52" s="1">
         <v>9</v>
       </c>
-      <c r="D51" s="1" t="s">
+      <c r="D52" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="E51" s="1" t="s">
+      <c r="E52" s="1" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A52" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B52" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C52" s="1">
+    <row r="53" spans="1:6">
+      <c r="A53" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C53" s="1">
         <v>10</v>
       </c>
-      <c r="D52" s="1" t="s">
+      <c r="D53" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="E52" s="1" t="s">
+      <c r="E53" s="1" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A53" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B53" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C53" s="1">
+    <row r="54" spans="1:6">
+      <c r="A54" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C54" s="1">
         <v>11</v>
       </c>
-      <c r="D53" s="1" t="s">
+      <c r="D54" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="E53" s="1" t="s">
+      <c r="E54" s="1" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A54" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B54" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C54" s="1">
+    <row r="55" spans="1:6">
+      <c r="A55" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C55" s="1">
         <v>12</v>
       </c>
-      <c r="D54" s="1" t="s">
+      <c r="D55" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="E54" s="1" t="s">
+      <c r="E55" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="F54" s="4"/>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A55" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B55" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C55" s="1">
+      <c r="F55" s="4"/>
+    </row>
+    <row r="56" spans="1:6">
+      <c r="A56" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C56" s="1">
         <v>13</v>
       </c>
-      <c r="D55" s="1" t="s">
+      <c r="D56" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="E55" s="1" t="s">
+      <c r="E56" s="1" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A56" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B56" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C56" s="1">
+    <row r="57" spans="1:6">
+      <c r="A57" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C57" s="1">
         <v>14</v>
       </c>
-      <c r="D56" s="1" t="s">
+      <c r="D57" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="E56" s="1" t="s">
+      <c r="E57" s="1" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A57" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B57" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C57" s="1">
+    <row r="58" spans="1:6">
+      <c r="A58" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C58" s="1">
         <v>15</v>
       </c>
-      <c r="D57" s="1" t="s">
+      <c r="D58" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="E57" s="1" t="s">
+      <c r="E58" s="1" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A58" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B58" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C58" s="1">
+    <row r="59" spans="1:6">
+      <c r="A59" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C59" s="1">
         <v>16</v>
       </c>
-      <c r="D58" s="1" t="s">
+      <c r="D59" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="E58" s="1" t="s">
+      <c r="E59" s="1" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A59" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B59" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C59" s="1">
+    <row r="60" spans="1:6">
+      <c r="A60" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C60" s="1">
         <v>17</v>
       </c>
-      <c r="D59" s="1" t="s">
+      <c r="D60" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="E59" s="1" t="s">
+      <c r="E60" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="F59" s="4"/>
-    </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A60" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B60" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C60" s="1">
+      <c r="F60" s="4"/>
+    </row>
+    <row r="61" spans="1:6">
+      <c r="A61" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C61" s="1">
         <v>18</v>
       </c>
-      <c r="D60" s="1" t="s">
+      <c r="D61" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="E60" s="1" t="s">
+      <c r="E61" s="1" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A61" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B61" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C61" s="1">
+    <row r="62" spans="1:6">
+      <c r="A62" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C62" s="1">
         <v>19</v>
       </c>
-      <c r="D61" s="1" t="s">
+      <c r="D62" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="E61" s="1" t="s">
+      <c r="E62" s="1" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A62" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B62" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C62" s="1">
+    <row r="63" spans="1:6">
+      <c r="A63" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C63" s="1">
         <v>20</v>
       </c>
-      <c r="D62" s="1" t="s">
+      <c r="D63" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="E62" s="1" t="s">
+      <c r="E63" s="1" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A63" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B63" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C63" s="1">
+    <row r="64" spans="1:6">
+      <c r="A64" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C64" s="1">
         <v>21</v>
       </c>
-      <c r="D63" s="1" t="s">
+      <c r="D64" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="E63" s="1" t="s">
+      <c r="E64" s="1" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A64" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B64" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C64" s="1">
+    <row r="65" spans="1:6">
+      <c r="A65" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C65" s="1">
         <v>22</v>
       </c>
-      <c r="D64" s="1" t="s">
+      <c r="D65" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="E64" s="1" t="s">
+      <c r="E65" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="F64" s="4"/>
-    </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A65" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B65" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C65" s="1">
+      <c r="F65" s="4"/>
+    </row>
+    <row r="66" spans="1:6">
+      <c r="A66" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C66" s="1">
         <v>23</v>
       </c>
-      <c r="D65" s="1" t="s">
+      <c r="D66" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="E65" s="1" t="s">
+      <c r="E66" s="1" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A66" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B66" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C66" s="1">
+    <row r="67" spans="1:6">
+      <c r="A67" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C67" s="1">
         <v>24</v>
       </c>
-      <c r="D66" s="1" t="s">
+      <c r="D67" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="E66" s="1" t="s">
+      <c r="E67" s="1" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A67" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B67" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C67" s="1">
+    <row r="68" spans="1:6">
+      <c r="A68" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C68" s="1">
         <v>25</v>
       </c>
-      <c r="D67" s="1" t="s">
+      <c r="D68" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="E67" s="1" t="s">
+      <c r="E68" s="1" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A68" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B68" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C68" s="1">
+    <row r="69" spans="1:6">
+      <c r="A69" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C69" s="1">
         <v>26</v>
       </c>
-      <c r="D68" s="1" t="s">
+      <c r="D69" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="E68" s="1" t="s">
+      <c r="E69" s="1" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A69" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B69" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C69" s="1">
+    <row r="70" spans="1:6">
+      <c r="A70" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C70" s="1">
         <v>27</v>
       </c>
-      <c r="D69" s="1" t="s">
+      <c r="D70" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="E69" s="1" t="s">
+      <c r="E70" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="F69" s="4"/>
-    </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A70" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B70" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C70" s="1">
+      <c r="F70" s="4"/>
+    </row>
+    <row r="71" spans="1:6">
+      <c r="A71" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C71" s="1">
         <v>28</v>
       </c>
-      <c r="D70" s="1" t="s">
+      <c r="D71" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="E70" s="1" t="s">
+      <c r="E71" s="1" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A71" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B71" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C71" s="1">
+    <row r="72" spans="1:6">
+      <c r="A72" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C72" s="1">
         <v>29</v>
       </c>
-      <c r="D71" s="1" t="s">
+      <c r="D72" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="E71" s="1" t="s">
+      <c r="E72" s="1" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A72" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B72" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C72" s="1">
+    <row r="73" spans="1:6">
+      <c r="A73" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C73" s="1">
         <v>30</v>
       </c>
-      <c r="D72" s="1" t="s">
+      <c r="D73" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="E72" s="1" t="s">
+      <c r="E73" s="1" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A73" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B73" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C73" s="1">
+    <row r="74" spans="1:6">
+      <c r="A74" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C74" s="1">
         <v>31</v>
       </c>
-      <c r="D73" s="1" t="s">
+      <c r="D74" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="E73" s="1" t="s">
+      <c r="E74" s="1" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A74" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B74" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C74" s="1">
+    <row r="75" spans="1:6">
+      <c r="A75" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C75" s="1">
         <v>32</v>
       </c>
-      <c r="D74" s="1" t="s">
+      <c r="D75" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="E74" s="1" t="s">
+      <c r="E75" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="F74" s="4"/>
-    </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A75" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B75" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C75" s="1">
-        <v>33</v>
-      </c>
-      <c r="D75" s="1" t="s">
+      <c r="F75" s="4"/>
+    </row>
+    <row r="76" spans="1:6">
+      <c r="A76" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C76" s="1">
+        <v>33</v>
+      </c>
+      <c r="D76" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="E75" s="1" t="s">
+      <c r="E76" s="1" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A76" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B76" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C76" s="1">
+    <row r="77" spans="1:6">
+      <c r="A77" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C77" s="1">
         <v>34</v>
       </c>
-      <c r="D76" s="1" t="s">
+      <c r="D77" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="E76" s="1" t="s">
+      <c r="E77" s="1" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A77" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B77" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C77" s="1">
+    <row r="78" spans="1:6">
+      <c r="A78" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C78" s="1">
         <v>35</v>
       </c>
-      <c r="D77" s="1" t="s">
+      <c r="D78" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="E77" s="1" t="s">
+      <c r="E78" s="1" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A78" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B78" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C78" s="1">
+    <row r="79" spans="1:6">
+      <c r="A79" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C79" s="1">
         <v>36</v>
       </c>
-      <c r="D78" s="1" t="s">
+      <c r="D79" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="E78" s="1" t="s">
+      <c r="E79" s="1" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A79" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B79" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C79" s="1">
+    <row r="80" spans="1:6">
+      <c r="A80" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C80" s="1">
         <v>37</v>
       </c>
-      <c r="D79" s="1" t="s">
+      <c r="D80" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="E79" s="1" t="s">
+      <c r="E80" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F79" s="4"/>
-    </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A80" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B80" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C80" s="1">
+      <c r="F80" s="4"/>
+    </row>
+    <row r="81" spans="1:6">
+      <c r="A81" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C81" s="1">
         <v>38</v>
       </c>
-      <c r="D80" s="1" t="s">
+      <c r="D81" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="E80" s="1" t="s">
+      <c r="E81" s="1" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A81" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B81" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C81" s="1">
+    <row r="82" spans="1:6">
+      <c r="A82" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C82" s="1">
         <v>39</v>
       </c>
-      <c r="D81" s="1" t="s">
+      <c r="D82" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="E81" s="1" t="s">
+      <c r="E82" s="1" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A82" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B82" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C82" s="1">
+    <row r="83" spans="1:6">
+      <c r="A83" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B83" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C83" s="1">
         <v>40</v>
       </c>
-      <c r="D82" s="1" t="s">
+      <c r="D83" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="E82" s="1" t="s">
+      <c r="E83" s="1" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A83" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B83" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C83" s="1">
+    <row r="84" spans="1:6">
+      <c r="A84" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B84" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C84" s="1">
         <v>41</v>
       </c>
-      <c r="D83" s="1" t="s">
+      <c r="D84" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="E83" s="1" t="s">
+      <c r="E84" s="1" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A84" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B84" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C84" s="1">
+    <row r="85" spans="1:6">
+      <c r="A85" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B85" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C85" s="1">
         <v>42</v>
       </c>
-      <c r="D84" s="1" t="s">
+      <c r="D85" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="E84" s="1" t="s">
+      <c r="E85" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="F84" s="4"/>
-    </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A85" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B85" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C85" s="1">
+      <c r="F85" s="4"/>
+    </row>
+    <row r="86" spans="1:6">
+      <c r="A86" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B86" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C86" s="1">
         <v>43</v>
       </c>
-      <c r="D85" s="1" t="s">
+      <c r="D86" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="E85" s="1" t="s">
+      <c r="E86" s="1" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A86" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B86" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C86" s="1">
+    <row r="87" spans="1:6">
+      <c r="A87" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B87" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C87" s="1">
         <v>44</v>
       </c>
-      <c r="D86" s="1" t="s">
+      <c r="D87" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="E86" s="1" t="s">
+      <c r="E87" s="1" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A87" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B87" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C87" s="1">
+    <row r="88" spans="1:6">
+      <c r="A88" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B88" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C88" s="1">
         <v>45</v>
       </c>
-      <c r="D87" s="1" t="s">
+      <c r="D88" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="E87" s="1" t="s">
+      <c r="E88" s="1" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A88" s="1" t="s">
+    <row r="89" spans="1:6">
+      <c r="A89" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="B89" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="C89" s="1">
+        <v>0</v>
+      </c>
+      <c r="D89" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6">
+      <c r="A90" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="B90" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="C90" s="1">
+        <v>1</v>
+      </c>
+      <c r="D90" t="s">
+        <v>208</v>
+      </c>
+      <c r="E90" t="s">
         <v>174</v>
       </c>
-      <c r="B88" s="1" t="s">
+      <c r="F90" s="1" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6">
+      <c r="A91" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="B91" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="C91" s="1">
+        <v>2</v>
+      </c>
+      <c r="D91" t="s">
+        <v>209</v>
+      </c>
+      <c r="E91" t="s">
+        <v>175</v>
+      </c>
+      <c r="F91" s="1" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6">
+      <c r="A92" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="B92" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="C92" s="1">
+        <v>3</v>
+      </c>
+      <c r="D92" t="s">
+        <v>210</v>
+      </c>
+      <c r="E92" t="s">
+        <v>176</v>
+      </c>
+      <c r="F92" s="1" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6">
+      <c r="A93" t="s">
+        <v>242</v>
+      </c>
+      <c r="B93" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="C93" s="1">
+        <v>0</v>
+      </c>
+      <c r="D93" t="s">
+        <v>30</v>
+      </c>
+      <c r="E93"/>
+      <c r="F93" s="1" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6">
+      <c r="A94" t="s">
+        <v>242</v>
+      </c>
+      <c r="B94" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="C94" s="1">
+        <v>1</v>
+      </c>
+      <c r="D94" t="s">
+        <v>220</v>
+      </c>
+      <c r="E94" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6">
+      <c r="A95" t="s">
+        <v>242</v>
+      </c>
+      <c r="B95" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="C95" s="1">
+        <v>2</v>
+      </c>
+      <c r="D95" t="s">
+        <v>221</v>
+      </c>
+      <c r="E95" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6">
+      <c r="A96" t="s">
+        <v>242</v>
+      </c>
+      <c r="B96" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="C96" s="1">
+        <v>3</v>
+      </c>
+      <c r="D96" t="s">
+        <v>222</v>
+      </c>
+      <c r="E96" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6">
+      <c r="A97" t="s">
+        <v>242</v>
+      </c>
+      <c r="B97" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="C97" s="1">
+        <v>4</v>
+      </c>
+      <c r="D97" t="s">
+        <v>225</v>
+      </c>
+      <c r="E97" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6">
+      <c r="A98" t="s">
+        <v>243</v>
+      </c>
+      <c r="B98" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="C98" s="1">
+        <v>0</v>
+      </c>
+      <c r="D98" t="s">
+        <v>30</v>
+      </c>
+      <c r="E98"/>
+      <c r="F98" s="1" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6">
+      <c r="A99" t="s">
+        <v>243</v>
+      </c>
+      <c r="B99" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="C99" s="1">
+        <v>1</v>
+      </c>
+      <c r="D99" t="s">
+        <v>213</v>
+      </c>
+      <c r="E99" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6">
+      <c r="A100" t="s">
+        <v>243</v>
+      </c>
+      <c r="B100" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="C100" s="1">
+        <v>2</v>
+      </c>
+      <c r="D100" t="s">
+        <v>214</v>
+      </c>
+      <c r="E100" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6">
+      <c r="A101" t="s">
+        <v>243</v>
+      </c>
+      <c r="B101" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="C101" s="1">
+        <v>3</v>
+      </c>
+      <c r="D101" t="s">
+        <v>215</v>
+      </c>
+      <c r="E101" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6">
+      <c r="A102" t="s">
+        <v>244</v>
+      </c>
+      <c r="B102" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="C102" s="1">
+        <v>0</v>
+      </c>
+      <c r="D102" t="s">
+        <v>30</v>
+      </c>
+      <c r="F102" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6">
+      <c r="A103" t="s">
+        <v>244</v>
+      </c>
+      <c r="B103" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="C103" s="1">
+        <v>1</v>
+      </c>
+      <c r="D103" t="s">
+        <v>227</v>
+      </c>
+      <c r="E103" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6">
+      <c r="A104" t="s">
+        <v>244</v>
+      </c>
+      <c r="B104" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="C104" s="1">
+        <v>2</v>
+      </c>
+      <c r="D104" t="s">
+        <v>228</v>
+      </c>
+      <c r="E104" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6">
+      <c r="A105" s="6" t="s">
+        <v>245</v>
+      </c>
+      <c r="B105" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="C105" s="1">
+        <v>0</v>
+      </c>
+      <c r="D105" t="s">
+        <v>49</v>
+      </c>
+      <c r="E105"/>
+      <c r="F105" s="1" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6">
+      <c r="A106" s="6" t="s">
+        <v>245</v>
+      </c>
+      <c r="B106" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="C106" s="1">
+        <v>1</v>
+      </c>
+      <c r="D106" t="s">
+        <v>229</v>
+      </c>
+      <c r="E106" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6">
+      <c r="A107" s="6" t="s">
+        <v>245</v>
+      </c>
+      <c r="B107" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="C107" s="1">
+        <v>2</v>
+      </c>
+      <c r="D107" s="5" t="s">
+        <v>230</v>
+      </c>
+      <c r="E107" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6" ht="148.5">
+      <c r="A108" s="6" t="s">
+        <v>246</v>
+      </c>
+      <c r="B108" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="C108" s="1">
+        <v>0</v>
+      </c>
+      <c r="D108" t="s">
+        <v>49</v>
+      </c>
+      <c r="E108"/>
+      <c r="F108" s="7" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6">
+      <c r="A109" s="6" t="s">
+        <v>246</v>
+      </c>
+      <c r="B109" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="C109" s="1">
+        <v>1</v>
+      </c>
+      <c r="D109" t="s">
+        <v>182</v>
+      </c>
+      <c r="E109" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6">
+      <c r="A110" s="6" t="s">
+        <v>246</v>
+      </c>
+      <c r="B110" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="C110" s="1">
+        <v>2</v>
+      </c>
+      <c r="D110" t="s">
+        <v>231</v>
+      </c>
+      <c r="E110" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6">
+      <c r="A111" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="B111" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="C111" s="1">
+        <v>0</v>
+      </c>
+      <c r="D111" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="E111" s="1" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6">
+      <c r="A112" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="B112" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="C112" s="1">
+        <v>1</v>
+      </c>
+      <c r="D112" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="C88" s="1">
-        <v>0</v>
-      </c>
-      <c r="D88" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A89" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="B89" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="C89" s="1">
-        <v>1</v>
-      </c>
-      <c r="D89" t="s">
-        <v>175</v>
-      </c>
-      <c r="E89" t="s">
-        <v>176</v>
-      </c>
-      <c r="F89" s="1" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A90" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="B90" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="C90" s="1">
+      <c r="E112" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="F112" s="1" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6">
+      <c r="A113" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="B113" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="C113" s="1">
         <v>2</v>
       </c>
-      <c r="D90" t="s">
-        <v>177</v>
-      </c>
-      <c r="E90" t="s">
-        <v>178</v>
-      </c>
-      <c r="F90" s="1" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A91" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="B91" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="C91" s="1">
-        <v>3</v>
-      </c>
-      <c r="D91" t="s">
-        <v>179</v>
-      </c>
-      <c r="E91" t="s">
-        <v>180</v>
-      </c>
-      <c r="F91" s="1" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A92" t="s">
+      <c r="D113" s="1" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6">
+      <c r="A114" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="B114" s="1" t="s">
         <v>185</v>
-      </c>
-      <c r="B92" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="C92" s="1">
-        <v>0</v>
-      </c>
-      <c r="D92" t="s">
-        <v>49</v>
-      </c>
-      <c r="E92"/>
-      <c r="F92" s="1" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A93" t="s">
-        <v>185</v>
-      </c>
-      <c r="B93" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="C93" s="1">
-        <v>1</v>
-      </c>
-      <c r="D93" t="s">
-        <v>179</v>
-      </c>
-      <c r="E93" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A94" t="s">
-        <v>185</v>
-      </c>
-      <c r="B94" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="C94" s="1">
-        <v>2</v>
-      </c>
-      <c r="D94" t="s">
-        <v>186</v>
-      </c>
-      <c r="E94" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A95" t="s">
-        <v>185</v>
-      </c>
-      <c r="B95" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="C95" s="1">
-        <v>3</v>
-      </c>
-      <c r="D95" t="s">
-        <v>187</v>
-      </c>
-      <c r="E95" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A96" t="s">
-        <v>185</v>
-      </c>
-      <c r="B96" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="C96" s="1">
-        <v>4</v>
-      </c>
-      <c r="D96" t="s">
-        <v>188</v>
-      </c>
-      <c r="E96" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A97" t="s">
-        <v>185</v>
-      </c>
-      <c r="B97" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="C97" s="1">
-        <v>5</v>
-      </c>
-      <c r="D97" t="s">
-        <v>189</v>
-      </c>
-      <c r="E97" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A98" t="s">
-        <v>185</v>
-      </c>
-      <c r="B98" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="C98" s="1">
-        <v>6</v>
-      </c>
-      <c r="D98" t="s">
-        <v>190</v>
-      </c>
-      <c r="E98" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A99" t="s">
-        <v>198</v>
-      </c>
-      <c r="B99" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="C99" s="1">
-        <v>0</v>
-      </c>
-      <c r="D99" t="s">
-        <v>30</v>
-      </c>
-      <c r="F99" s="1" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A100" t="s">
-        <v>198</v>
-      </c>
-      <c r="B100" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="C100" s="1">
-        <v>1</v>
-      </c>
-      <c r="D100" t="s">
-        <v>199</v>
-      </c>
-      <c r="E100" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A101" t="s">
-        <v>198</v>
-      </c>
-      <c r="B101" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="C101" s="1">
-        <v>2</v>
-      </c>
-      <c r="D101" t="s">
-        <v>200</v>
-      </c>
-      <c r="E101" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A102" t="s">
-        <v>198</v>
-      </c>
-      <c r="B102" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="C102" s="1">
-        <v>3</v>
-      </c>
-      <c r="D102" t="s">
-        <v>201</v>
-      </c>
-      <c r="E102" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A103" t="s">
-        <v>206</v>
-      </c>
-      <c r="B103" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="C103" s="1">
-        <v>0</v>
-      </c>
-      <c r="D103" t="s">
-        <v>30</v>
-      </c>
-      <c r="F103" s="1" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A104" t="s">
-        <v>206</v>
-      </c>
-      <c r="B104" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="C104" s="1">
-        <v>1</v>
-      </c>
-      <c r="D104" t="s">
-        <v>207</v>
-      </c>
-      <c r="E104" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A105" t="s">
-        <v>206</v>
-      </c>
-      <c r="B105" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="C105" s="1">
-        <v>2</v>
-      </c>
-      <c r="D105" t="s">
-        <v>208</v>
-      </c>
-      <c r="E105" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A106" t="s">
-        <v>206</v>
-      </c>
-      <c r="B106" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="C106" s="1">
-        <v>3</v>
-      </c>
-      <c r="D106" t="s">
-        <v>209</v>
-      </c>
-      <c r="E106" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A107" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="B107" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="C107" s="1">
-        <v>0</v>
-      </c>
-      <c r="D107" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="E107" s="1" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A108" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="B108" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="C108" s="1">
-        <v>1</v>
-      </c>
-      <c r="D108" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="E108" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="F108" s="1" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A109" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="B109" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="C109" s="1">
-        <v>2</v>
-      </c>
-      <c r="D109" s="1" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A110" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="B110" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="C110" s="1">
-        <v>0</v>
-      </c>
-      <c r="D110" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A111" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="B111" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="C111" s="1">
-        <v>1</v>
-      </c>
-      <c r="D111" s="1" t="s">
-        <v>220</v>
-      </c>
-      <c r="E111" s="1" t="s">
-        <v>228</v>
-      </c>
-      <c r="F111" s="1" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A112" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="B112" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="C112" s="1">
-        <v>2</v>
-      </c>
-      <c r="D112" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="E112" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="F112" s="1" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A113" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="B113" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="C113" s="1">
-        <v>3</v>
-      </c>
-      <c r="D113" s="1" t="s">
-        <v>222</v>
-      </c>
-      <c r="E113" s="1" t="s">
-        <v>232</v>
-      </c>
-      <c r="F113" s="1" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A114" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="B114" s="1" t="s">
-        <v>216</v>
       </c>
       <c r="C114" s="1">
         <v>0</v>
@@ -3170,48 +3238,122 @@
       <c r="D114" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="E114" s="1" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="115" spans="1:6">
       <c r="A115" s="1" t="s">
-        <v>218</v>
+        <v>186</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>216</v>
+        <v>185</v>
       </c>
       <c r="C115" s="1">
         <v>1</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>223</v>
+        <v>189</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>235</v>
+        <v>197</v>
       </c>
       <c r="F115" s="1" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.3">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6">
       <c r="A116" s="1" t="s">
-        <v>218</v>
+        <v>186</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>216</v>
+        <v>185</v>
       </c>
       <c r="C116" s="1">
         <v>2</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>224</v>
+        <v>190</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>237</v>
+        <v>199</v>
       </c>
       <c r="F116" s="1" t="s">
-        <v>238</v>
+        <v>200</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6">
+      <c r="A117" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="B117" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="C117" s="1">
+        <v>3</v>
+      </c>
+      <c r="D117" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="E117" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="F117" s="1" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="118" spans="1:6">
+      <c r="A118" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="B118" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="C118" s="1">
+        <v>0</v>
+      </c>
+      <c r="D118" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="E118" s="1" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6">
+      <c r="A119" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="B119" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="C119" s="1">
+        <v>1</v>
+      </c>
+      <c r="D119" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="E119" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="F119" s="1" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="120" spans="1:6">
+      <c r="A120" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="B120" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="C120" s="1">
+        <v>2</v>
+      </c>
+      <c r="D120" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="E120" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="F120" s="1" t="s">
+        <v>207</v>
       </c>
     </row>
   </sheetData>

--- a/Development/Common/GameData/Enum/GameEnum.xlsx
+++ b/Development/Common/GameData/Enum/GameEnum.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\project\MMOGameServerProject\Development\Common\GameData\Enum\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F1A06FA-7B22-4C10-A01A-AA4727B2D29A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{663F8EA7-9EF2-4678-B62A-27A7CDA66BAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="484" uniqueCount="249">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="512" uniqueCount="263">
   <si>
     <t>MonsterGrade</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -893,6 +893,62 @@
   </si>
   <si>
     <t>유니크</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>스킬의 타게팅 방식</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>가장 가까운 타겟</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>가장 등급이 높으면서 가장 가까운 타겟</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">TargetingMode </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Nearest</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>HighestGradeNearest</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SkillPlacement</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Caster</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Target</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Forward</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>캐스터 위치 (투사체 발사점 / 캐스터 중심 범위)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>타겟 위치에 OBB/Circle 생성</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>캐스터 전방에서 시작해 타겟 방향으로 OBB</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>스킬 효과의 위치를 어디에 둘지 정한다.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1282,7 +1338,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F120"/>
+  <dimension ref="A1:F127"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="22.75" style="1" customWidth="1"/>
@@ -3175,133 +3231,129 @@
       </c>
     </row>
     <row r="111" spans="1:6">
-      <c r="A111" s="1" t="s">
-        <v>184</v>
+      <c r="A111" s="6" t="s">
+        <v>252</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="C111" s="1">
         <v>0</v>
       </c>
-      <c r="D111" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="E111" s="1" t="s">
-        <v>194</v>
+      <c r="D111" t="s">
+        <v>30</v>
+      </c>
+      <c r="E111"/>
+      <c r="F111" s="1" t="s">
+        <v>249</v>
       </c>
     </row>
     <row r="112" spans="1:6">
-      <c r="A112" s="1" t="s">
-        <v>183</v>
+      <c r="A112" s="6" t="s">
+        <v>252</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="C112" s="1">
         <v>1</v>
       </c>
-      <c r="D112" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="E112" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="F112" s="1" t="s">
-        <v>196</v>
+      <c r="D112" t="s">
+        <v>253</v>
+      </c>
+      <c r="E112" t="s">
+        <v>250</v>
       </c>
     </row>
     <row r="113" spans="1:6">
-      <c r="A113" s="1" t="s">
-        <v>183</v>
+      <c r="A113" s="6" t="s">
+        <v>252</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="C113" s="1">
         <v>2</v>
       </c>
-      <c r="D113" s="1" t="s">
-        <v>188</v>
+      <c r="D113" t="s">
+        <v>254</v>
+      </c>
+      <c r="E113" t="s">
+        <v>251</v>
       </c>
     </row>
     <row r="114" spans="1:6">
-      <c r="A114" s="1" t="s">
-        <v>186</v>
+      <c r="A114" s="6" t="s">
+        <v>255</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="C114" s="1">
         <v>0</v>
       </c>
-      <c r="D114" s="1" t="s">
-        <v>49</v>
+      <c r="D114" t="s">
+        <v>30</v>
+      </c>
+      <c r="E114"/>
+      <c r="F114" s="1" t="s">
+        <v>262</v>
       </c>
     </row>
     <row r="115" spans="1:6">
-      <c r="A115" s="1" t="s">
-        <v>186</v>
+      <c r="A115" s="6" t="s">
+        <v>255</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="C115" s="1">
         <v>1</v>
       </c>
-      <c r="D115" s="1" t="s">
-        <v>189</v>
+      <c r="D115" t="s">
+        <v>256</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="F115" s="1" t="s">
-        <v>198</v>
+        <v>259</v>
       </c>
     </row>
     <row r="116" spans="1:6">
-      <c r="A116" s="1" t="s">
-        <v>186</v>
+      <c r="A116" s="6" t="s">
+        <v>255</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="C116" s="1">
         <v>2</v>
       </c>
-      <c r="D116" s="1" t="s">
-        <v>190</v>
+      <c r="D116" t="s">
+        <v>257</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="F116" s="1" t="s">
-        <v>200</v>
+        <v>260</v>
       </c>
     </row>
     <row r="117" spans="1:6">
-      <c r="A117" s="1" t="s">
-        <v>186</v>
+      <c r="A117" s="6" t="s">
+        <v>255</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="C117" s="1">
         <v>3</v>
       </c>
-      <c r="D117" s="1" t="s">
-        <v>191</v>
+      <c r="D117" t="s">
+        <v>258</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="F117" s="1" t="s">
-        <v>202</v>
+        <v>261</v>
       </c>
     </row>
     <row r="118" spans="1:6">
       <c r="A118" s="1" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="B118" s="1" t="s">
         <v>185</v>
@@ -3313,12 +3365,12 @@
         <v>49</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>203</v>
+        <v>194</v>
       </c>
     </row>
     <row r="119" spans="1:6">
       <c r="A119" s="1" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="B119" s="1" t="s">
         <v>185</v>
@@ -3327,18 +3379,18 @@
         <v>1</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>192</v>
+        <v>181</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="F119" s="1" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
     </row>
     <row r="120" spans="1:6">
       <c r="A120" s="1" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="B120" s="1" t="s">
         <v>185</v>
@@ -3347,12 +3399,137 @@
         <v>2</v>
       </c>
       <c r="D120" s="1" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6">
+      <c r="A121" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="B121" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="C121" s="1">
+        <v>0</v>
+      </c>
+      <c r="D121" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="122" spans="1:6">
+      <c r="A122" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="B122" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="C122" s="1">
+        <v>1</v>
+      </c>
+      <c r="D122" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="E122" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="F122" s="1" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="123" spans="1:6">
+      <c r="A123" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="B123" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="C123" s="1">
+        <v>2</v>
+      </c>
+      <c r="D123" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="E123" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="F123" s="1" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="124" spans="1:6">
+      <c r="A124" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="B124" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="C124" s="1">
+        <v>3</v>
+      </c>
+      <c r="D124" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="E124" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="F124" s="1" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="125" spans="1:6">
+      <c r="A125" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="B125" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="C125" s="1">
+        <v>0</v>
+      </c>
+      <c r="D125" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="E125" s="1" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="126" spans="1:6">
+      <c r="A126" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="B126" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="C126" s="1">
+        <v>1</v>
+      </c>
+      <c r="D126" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="E126" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="F126" s="1" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="127" spans="1:6">
+      <c r="A127" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="B127" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="C127" s="1">
+        <v>2</v>
+      </c>
+      <c r="D127" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="E120" s="1" t="s">
+      <c r="E127" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="F120" s="1" t="s">
+      <c r="F127" s="1" t="s">
         <v>207</v>
       </c>
     </row>

--- a/Development/Common/GameData/Enum/GameEnum.xlsx
+++ b/Development/Common/GameData/Enum/GameEnum.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\project\MMOGameServerProject\Development\Common\GameData\Enum\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7713EA7-E465-4085-9D6D-7B342544E61B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D949E5D-813E-4DA0-9EE1-7E73EA4D8B0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2070" yWindow="2190" windowWidth="31605" windowHeight="17295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Enum" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="476" uniqueCount="277">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="487" uniqueCount="286">
   <si>
     <t>Enum 이름</t>
   </si>
@@ -877,6 +877,42 @@
   </si>
   <si>
     <t>원형</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>MonsterAIType</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Monster</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>FSM</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>BehaviourTree</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>행동 트리</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>유한상태기계</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>일반몬스터용</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>엘리트 몬스터, 보스용</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>몬스터 AI 종류</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -993,7 +1029,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -1014,11 +1050,10 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -1303,7 +1338,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G111"/>
+  <dimension ref="A1:G113"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="22.75" style="1" customWidth="1"/>
@@ -1679,7 +1714,7 @@
       <c r="E21" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="F21" s="8" t="s">
+      <c r="F21" t="s">
         <v>49</v>
       </c>
     </row>
@@ -1696,7 +1731,7 @@
       <c r="E22" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="F22" s="8" t="s">
+      <c r="F22" t="s">
         <v>51</v>
       </c>
     </row>
@@ -1713,7 +1748,7 @@
       <c r="E23" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="F23" s="8" t="s">
+      <c r="F23" t="s">
         <v>53</v>
       </c>
     </row>
@@ -1730,7 +1765,7 @@
       <c r="E24" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="F24" s="8" t="s">
+      <c r="F24" t="s">
         <v>55</v>
       </c>
     </row>
@@ -1747,7 +1782,7 @@
       <c r="E25" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="F25" s="8" t="s">
+      <c r="F25" t="s">
         <v>57</v>
       </c>
     </row>
@@ -1937,7 +1972,7 @@
       <c r="F36" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="G36" s="9"/>
+      <c r="G36" s="8"/>
     </row>
     <row r="37" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A37" s="4" t="s">
@@ -2023,7 +2058,7 @@
       <c r="F41" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="G41" s="9"/>
+      <c r="G41" s="8"/>
     </row>
     <row r="42" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A42" s="4" t="s">
@@ -2109,7 +2144,7 @@
       <c r="F46" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="G46" s="9"/>
+      <c r="G46" s="8"/>
     </row>
     <row r="47" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A47" s="4" t="s">
@@ -2195,7 +2230,7 @@
       <c r="F51" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="G51" s="9"/>
+      <c r="G51" s="8"/>
     </row>
     <row r="52" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A52" s="4" t="s">
@@ -2281,7 +2316,7 @@
       <c r="F56" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="G56" s="9"/>
+      <c r="G56" s="8"/>
     </row>
     <row r="57" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A57" s="4" t="s">
@@ -2367,7 +2402,7 @@
       <c r="F61" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="G61" s="9"/>
+      <c r="G61" s="8"/>
     </row>
     <row r="62" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A62" s="4" t="s">
@@ -2453,7 +2488,7 @@
       <c r="F66" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="G66" s="9"/>
+      <c r="G66" s="8"/>
     </row>
     <row r="67" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A67" s="4" t="s">
@@ -2539,7 +2574,7 @@
       <c r="F71" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="G71" s="9"/>
+      <c r="G71" s="8"/>
     </row>
     <row r="72" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A72" s="4" t="s">
@@ -2625,7 +2660,7 @@
       <c r="F76" s="4" t="s">
         <v>160</v>
       </c>
-      <c r="G76" s="9"/>
+      <c r="G76" s="8"/>
     </row>
     <row r="77" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A77" s="4" t="s">
@@ -2739,7 +2774,7 @@
       </c>
     </row>
     <row r="83" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A83" s="8" t="s">
+      <c r="A83" t="s">
         <v>178</v>
       </c>
       <c r="B83" s="4" t="s">
@@ -2751,64 +2786,64 @@
       <c r="D83" s="4">
         <v>1</v>
       </c>
-      <c r="E83" s="8" t="s">
+      <c r="E83" t="s">
         <v>180</v>
       </c>
-      <c r="F83" s="8" t="s">
+      <c r="F83" t="s">
         <v>181</v>
       </c>
     </row>
     <row r="84" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A84" s="8" t="s">
+      <c r="A84" t="s">
         <v>178</v>
       </c>
-      <c r="B84" s="8"/>
+      <c r="B84"/>
       <c r="C84" s="4" t="s">
         <v>168</v>
       </c>
       <c r="D84" s="4">
         <v>2</v>
       </c>
-      <c r="E84" s="8" t="s">
+      <c r="E84" t="s">
         <v>182</v>
       </c>
-      <c r="F84" s="8" t="s">
+      <c r="F84" t="s">
         <v>183</v>
       </c>
     </row>
     <row r="85" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A85" s="8" t="s">
+      <c r="A85" t="s">
         <v>178</v>
       </c>
-      <c r="B85" s="8"/>
+      <c r="B85"/>
       <c r="C85" s="4" t="s">
         <v>168</v>
       </c>
       <c r="D85" s="4">
         <v>3</v>
       </c>
-      <c r="E85" s="8" t="s">
+      <c r="E85" t="s">
         <v>184</v>
       </c>
-      <c r="F85" s="8" t="s">
+      <c r="F85" t="s">
         <v>185</v>
       </c>
     </row>
     <row r="86" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A86" s="8" t="s">
+      <c r="A86" t="s">
         <v>178</v>
       </c>
-      <c r="B86" s="8"/>
+      <c r="B86"/>
       <c r="C86" s="4" t="s">
         <v>168</v>
       </c>
       <c r="D86" s="4">
         <v>4</v>
       </c>
-      <c r="E86" s="8" t="s">
+      <c r="E86" t="s">
         <v>186</v>
       </c>
-      <c r="F86" s="8" t="s">
+      <c r="F86" t="s">
         <v>187</v>
       </c>
     </row>
@@ -2869,10 +2904,10 @@
       </c>
     </row>
     <row r="90" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A90" s="8" t="s">
+      <c r="A90" t="s">
         <v>196</v>
       </c>
-      <c r="B90" s="8" t="s">
+      <c r="B90" t="s">
         <v>197</v>
       </c>
       <c r="C90" s="4" t="s">
@@ -2881,10 +2916,10 @@
       <c r="D90" s="4">
         <v>1</v>
       </c>
-      <c r="E90" s="8" t="s">
+      <c r="E90" t="s">
         <v>198</v>
       </c>
-      <c r="F90" s="8" t="s">
+      <c r="F90" t="s">
         <v>263</v>
       </c>
       <c r="G90" s="4" t="s">
@@ -2892,20 +2927,20 @@
       </c>
     </row>
     <row r="91" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A91" s="8" t="s">
+      <c r="A91" t="s">
         <v>196</v>
       </c>
-      <c r="B91" s="8"/>
+      <c r="B91"/>
       <c r="C91" s="4" t="s">
         <v>168</v>
       </c>
       <c r="D91" s="4">
         <v>2</v>
       </c>
-      <c r="E91" s="8" t="s">
+      <c r="E91" t="s">
         <v>199</v>
       </c>
-      <c r="F91" s="8" t="s">
+      <c r="F91" t="s">
         <v>265</v>
       </c>
       <c r="G91" s="4" t="s">
@@ -2957,10 +2992,10 @@
       </c>
     </row>
     <row r="94" spans="1:7" s="4" customFormat="1" ht="141.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A94" s="10" t="s">
+      <c r="A94" s="9" t="s">
         <v>260</v>
       </c>
-      <c r="B94" s="11" t="s">
+      <c r="B94" s="10" t="s">
         <v>205</v>
       </c>
       <c r="C94" s="4" t="s">
@@ -2969,10 +3004,10 @@
       <c r="D94" s="4">
         <v>1</v>
       </c>
-      <c r="E94" s="8" t="s">
+      <c r="E94" t="s">
         <v>261</v>
       </c>
-      <c r="F94" s="8" t="s">
+      <c r="F94" t="s">
         <v>276</v>
       </c>
       <c r="G94" s="4" t="s">
@@ -2980,20 +3015,20 @@
       </c>
     </row>
     <row r="95" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A95" s="10" t="s">
+      <c r="A95" s="9" t="s">
         <v>204</v>
       </c>
-      <c r="B95" s="10"/>
+      <c r="B95" s="9"/>
       <c r="C95" s="4" t="s">
         <v>168</v>
       </c>
       <c r="D95" s="4">
         <v>2</v>
       </c>
-      <c r="E95" s="8" t="s">
+      <c r="E95" t="s">
         <v>206</v>
       </c>
-      <c r="F95" s="8" t="s">
+      <c r="F95" t="s">
         <v>273</v>
       </c>
       <c r="G95" s="4" t="s">
@@ -3039,7 +3074,7 @@
       </c>
     </row>
     <row r="98" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A98" s="10" t="s">
+      <c r="A98" s="9" t="s">
         <v>213</v>
       </c>
       <c r="B98" s="4" t="s">
@@ -3051,7 +3086,7 @@
       <c r="D98" s="4">
         <v>1</v>
       </c>
-      <c r="E98" s="8" t="s">
+      <c r="E98" t="s">
         <v>215</v>
       </c>
       <c r="F98" s="4" t="s">
@@ -3062,17 +3097,17 @@
       </c>
     </row>
     <row r="99" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A99" s="10" t="s">
+      <c r="A99" s="9" t="s">
         <v>213</v>
       </c>
-      <c r="B99" s="10"/>
+      <c r="B99" s="9"/>
       <c r="C99" s="4" t="s">
         <v>168</v>
       </c>
       <c r="D99" s="4">
         <v>2</v>
       </c>
-      <c r="E99" s="8" t="s">
+      <c r="E99" t="s">
         <v>216</v>
       </c>
       <c r="F99" s="4" t="s">
@@ -3080,17 +3115,17 @@
       </c>
     </row>
     <row r="100" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A100" s="10" t="s">
+      <c r="A100" s="9" t="s">
         <v>213</v>
       </c>
-      <c r="B100" s="10"/>
+      <c r="B100" s="9"/>
       <c r="C100" s="4" t="s">
         <v>168</v>
       </c>
       <c r="D100" s="4">
         <v>3</v>
       </c>
-      <c r="E100" s="8" t="s">
+      <c r="E100" t="s">
         <v>218</v>
       </c>
       <c r="F100" s="4" t="s">
@@ -3238,87 +3273,130 @@
       </c>
     </row>
     <row r="108" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A108" s="8" t="s">
+      <c r="A108" t="s">
         <v>243</v>
       </c>
-      <c r="B108" s="8"/>
-      <c r="C108" s="8" t="s">
+      <c r="B108"/>
+      <c r="C108" t="s">
         <v>26</v>
       </c>
       <c r="D108" s="4">
         <v>1</v>
       </c>
-      <c r="E108" s="8" t="s">
+      <c r="E108" t="s">
         <v>244</v>
       </c>
-      <c r="F108" s="8" t="s">
+      <c r="F108" t="s">
         <v>245</v>
       </c>
-      <c r="G108" s="8" t="s">
+      <c r="G108" t="s">
         <v>246</v>
       </c>
     </row>
     <row r="109" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A109" s="8" t="s">
+      <c r="A109" t="s">
         <v>243</v>
       </c>
-      <c r="B109" s="8"/>
-      <c r="C109" s="8" t="s">
+      <c r="B109"/>
+      <c r="C109" t="s">
         <v>26</v>
       </c>
       <c r="D109" s="4">
         <v>2</v>
       </c>
-      <c r="E109" s="8" t="s">
+      <c r="E109" t="s">
         <v>247</v>
       </c>
-      <c r="F109" s="8" t="s">
+      <c r="F109" t="s">
         <v>248</v>
       </c>
-      <c r="G109" s="8" t="s">
+      <c r="G109" t="s">
         <v>249</v>
       </c>
     </row>
     <row r="110" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A110" s="8" t="s">
+      <c r="A110" t="s">
         <v>243</v>
       </c>
-      <c r="B110" s="8"/>
-      <c r="C110" s="8" t="s">
+      <c r="B110"/>
+      <c r="C110" t="s">
         <v>26</v>
       </c>
       <c r="D110" s="4">
         <v>3</v>
       </c>
-      <c r="E110" s="8" t="s">
+      <c r="E110" t="s">
         <v>250</v>
       </c>
-      <c r="F110" s="8" t="s">
+      <c r="F110" t="s">
         <v>251</v>
       </c>
-      <c r="G110" s="8" t="s">
+      <c r="G110" t="s">
         <v>252</v>
       </c>
     </row>
     <row r="111" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A111" s="8" t="s">
+      <c r="A111" t="s">
         <v>243</v>
       </c>
-      <c r="B111" s="8"/>
-      <c r="C111" s="8" t="s">
+      <c r="B111"/>
+      <c r="C111" t="s">
         <v>26</v>
       </c>
       <c r="D111" s="4">
         <v>4</v>
       </c>
-      <c r="E111" s="8" t="s">
+      <c r="E111" t="s">
         <v>253</v>
       </c>
-      <c r="F111" s="8" t="s">
+      <c r="F111" t="s">
         <v>254</v>
       </c>
-      <c r="G111" s="8" t="s">
+      <c r="G111" t="s">
         <v>255</v>
+      </c>
+    </row>
+    <row r="112" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A112" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="B112" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="C112" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="D112" s="1">
+        <v>1</v>
+      </c>
+      <c r="E112" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="F112" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="G112" s="1" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="113" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A113" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="C113" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="D113" s="1">
+        <v>2</v>
+      </c>
+      <c r="E113" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="F113" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="G113" s="1" t="s">
+        <v>284</v>
       </c>
     </row>
   </sheetData>

--- a/Development/Common/GameData/Enum/GameEnum.xlsx
+++ b/Development/Common/GameData/Enum/GameEnum.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\project\MMOGameServerProject\Development\Common\GameData\Enum\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D949E5D-813E-4DA0-9EE1-7E73EA4D8B0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E727D6E9-16B5-426C-A3E7-B486EDF821A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38280" yWindow="5355" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Enum" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="487" uniqueCount="286">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="503" uniqueCount="298">
   <si>
     <t>Enum 이름</t>
   </si>
@@ -913,6 +913,54 @@
   </si>
   <si>
     <t>몬스터 AI 종류</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SpawnActivation</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>스폰 활성화 모드</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Monster</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Always</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>항상</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>항상 밀도 유지</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>PlayerProximity</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>근접 활성</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>플레이어 근접 시만</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Manual</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>수동</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Stage 스크립트에서 ActivateSpawner 등으로 활성화시킴</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1338,7 +1386,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G113"/>
+  <dimension ref="A1:G116"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="22.75" style="1" customWidth="1"/>
@@ -3399,6 +3447,69 @@
         <v>284</v>
       </c>
     </row>
+    <row r="114" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A114" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="B114" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="C114" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="D114" s="1">
+        <v>1</v>
+      </c>
+      <c r="E114" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="F114" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="G114" s="1" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="115" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A115" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="C115" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="D115" s="1">
+        <v>2</v>
+      </c>
+      <c r="E115" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="F115" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="G115" s="1" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="116" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A116" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="C116" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="D116" s="1">
+        <v>3</v>
+      </c>
+      <c r="E116" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="F116" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="G116" s="1" t="s">
+        <v>297</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="E1:E111" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="2" type="noConversion"/>

--- a/Development/Common/GameData/Enum/GameEnum.xlsx
+++ b/Development/Common/GameData/Enum/GameEnum.xlsx
@@ -8,22 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\project\MMOGameServerProject\Development\Common\GameData\Enum\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E727D6E9-16B5-426C-A3E7-B486EDF821A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91DE8405-31CE-41F4-BAF8-45732242CDE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="5355" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Enum" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Enum!$E$1:$E$111</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Enum!$E$1:$E$112</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="503" uniqueCount="298">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="507" uniqueCount="300">
   <si>
     <t>Enum 이름</t>
   </si>
@@ -796,184 +796,200 @@
   </si>
   <si>
     <t>값 설명</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>Enum 설명</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>Enum 값
 int32 타입이고, 1부터시작 한다.
 값 0은 무조건 None이 자동 생성되고, 마지막값+1 은 Max가 자동으로 생성된다.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>Enum 값 이름</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>SkillEffectShape</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>Circle</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>버프의 주기적 효과</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>고정</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>얼음지대, 화염지대, 전격방출, 메테오 착탄 등</t>
   </si>
   <si>
     <t>직선 등속</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>이동하는 장판 등의 하이브리드</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>투사체 접촉 시 1회</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>투사체 접촉 시 클라이언트가 hit을 보고한다.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>서버 주도 범위 틱</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>서버에서 영역내의 적에게 대미지를 입힌다.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>전격방출, 메테오 착탄, 파이어볼 폭발 등</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>얼음지대, 블레이즈</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>방향이 있는 직사각형, OBB(Oriented Bounding Box)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>캐스터 위치</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>투사체 발사점 / 캐스터 중심 범위</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>원형</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>MonsterAIType</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>Monster</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>FSM</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>BehaviourTree</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>행동 트리</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>유한상태기계</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>일반몬스터용</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>엘리트 몬스터, 보스용</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>몬스터 AI 종류</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>SpawnActivation</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>스폰 활성화 모드</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>Monster</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>Always</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>항상</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>항상 밀도 유지</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>PlayerProximity</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>근접 활성</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>플레이어 근접 시만</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>Manual</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>수동</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>Stage 스크립트에서 ActivateSpawner 등으로 활성화시킴</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>EventArea</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>이벤트영역</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1073,37 +1089,40 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1386,7 +1405,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G116"/>
+  <dimension ref="A1:G117"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="22.75" style="1" customWidth="1"/>
@@ -1717,19 +1736,19 @@
     </row>
     <row r="19" spans="1:6" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A19" s="7" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="C19" s="7" t="s">
         <v>4</v>
       </c>
       <c r="D19" s="7">
-        <v>1</v>
-      </c>
-      <c r="E19" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="F19" s="7" t="s">
-        <v>43</v>
+        <v>5</v>
+      </c>
+      <c r="E19" s="11" t="s">
+        <v>298</v>
+      </c>
+      <c r="F19" s="11" t="s">
+        <v>299</v>
       </c>
     </row>
     <row r="20" spans="1:6" s="7" customFormat="1" x14ac:dyDescent="0.3">
@@ -1740,30 +1759,30 @@
         <v>4</v>
       </c>
       <c r="D20" s="7">
+        <v>1</v>
+      </c>
+      <c r="E20" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="F20" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="D21" s="7">
         <v>2</v>
       </c>
-      <c r="E20" s="7" t="s">
+      <c r="E21" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="F20" s="7" t="s">
+      <c r="F21" s="7" t="s">
         <v>45</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="D21" s="4">
-        <v>1</v>
-      </c>
-      <c r="E21" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="F21" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="22" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.3">
@@ -1774,13 +1793,13 @@
         <v>47</v>
       </c>
       <c r="D22" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F22" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="23" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.3">
@@ -1791,13 +1810,13 @@
         <v>47</v>
       </c>
       <c r="D23" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F23" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="24" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.3">
@@ -1808,13 +1827,13 @@
         <v>47</v>
       </c>
       <c r="D24" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F24" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="25" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.3">
@@ -1825,30 +1844,30 @@
         <v>47</v>
       </c>
       <c r="D25" s="4">
+        <v>4</v>
+      </c>
+      <c r="E25" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="F25" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="D26" s="4">
         <v>5</v>
       </c>
-      <c r="E25" s="4" t="s">
+      <c r="E26" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="F25" t="s">
+      <c r="F26" t="s">
         <v>57</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="C26" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="D26" s="7">
-        <v>1</v>
-      </c>
-      <c r="E26" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="F26" s="7" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="27" spans="1:6" s="7" customFormat="1" x14ac:dyDescent="0.3">
@@ -1859,13 +1878,13 @@
         <v>47</v>
       </c>
       <c r="D27" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E27" s="7" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F27" s="7" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="28" spans="1:6" s="7" customFormat="1" x14ac:dyDescent="0.3">
@@ -1876,13 +1895,13 @@
         <v>47</v>
       </c>
       <c r="D28" s="7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E28" s="7" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="F28" s="7" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="29" spans="1:6" s="7" customFormat="1" x14ac:dyDescent="0.3">
@@ -1893,13 +1912,13 @@
         <v>47</v>
       </c>
       <c r="D29" s="7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E29" s="7" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="F29" s="7" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="30" spans="1:6" s="7" customFormat="1" x14ac:dyDescent="0.3">
@@ -1910,13 +1929,13 @@
         <v>47</v>
       </c>
       <c r="D30" s="7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E30" s="7" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="F30" s="7" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="31" spans="1:6" s="7" customFormat="1" x14ac:dyDescent="0.3">
@@ -1927,13 +1946,13 @@
         <v>47</v>
       </c>
       <c r="D31" s="7">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E31" s="7" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="F31" s="7" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="32" spans="1:6" s="7" customFormat="1" x14ac:dyDescent="0.3">
@@ -1944,13 +1963,13 @@
         <v>47</v>
       </c>
       <c r="D32" s="7">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E32" s="7" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="F32" s="7" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="33" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.3">
@@ -1961,13 +1980,13 @@
         <v>47</v>
       </c>
       <c r="D33" s="7">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E33" s="7" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="F33" s="7" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="34" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.3">
@@ -1978,30 +1997,30 @@
         <v>47</v>
       </c>
       <c r="D34" s="7">
+        <v>8</v>
+      </c>
+      <c r="E34" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="F34" s="7" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="C35" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="D35" s="7">
         <v>9</v>
       </c>
-      <c r="E34" s="7" t="s">
+      <c r="E35" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="F34" s="7" t="s">
+      <c r="F35" s="7" t="s">
         <v>76</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="C35" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="D35" s="4">
-        <v>1</v>
-      </c>
-      <c r="E35" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="F35" s="4" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="36" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
@@ -2012,15 +2031,14 @@
         <v>47</v>
       </c>
       <c r="D36" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="G36" s="8"/>
+        <v>78</v>
+      </c>
     </row>
     <row r="37" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A37" s="4" t="s">
@@ -2030,14 +2048,15 @@
         <v>47</v>
       </c>
       <c r="D37" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>82</v>
-      </c>
+        <v>80</v>
+      </c>
+      <c r="G37" s="8"/>
     </row>
     <row r="38" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A38" s="4" t="s">
@@ -2047,13 +2066,13 @@
         <v>47</v>
       </c>
       <c r="D38" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="39" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
@@ -2064,13 +2083,13 @@
         <v>47</v>
       </c>
       <c r="D39" s="4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="40" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
@@ -2081,13 +2100,13 @@
         <v>47</v>
       </c>
       <c r="D40" s="4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="41" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
@@ -2098,15 +2117,14 @@
         <v>47</v>
       </c>
       <c r="D41" s="4">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="G41" s="8"/>
+        <v>88</v>
+      </c>
     </row>
     <row r="42" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A42" s="4" t="s">
@@ -2116,14 +2134,15 @@
         <v>47</v>
       </c>
       <c r="D42" s="4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>92</v>
-      </c>
+        <v>90</v>
+      </c>
+      <c r="G42" s="8"/>
     </row>
     <row r="43" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A43" s="4" t="s">
@@ -2133,13 +2152,13 @@
         <v>47</v>
       </c>
       <c r="D43" s="4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="44" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
@@ -2150,13 +2169,13 @@
         <v>47</v>
       </c>
       <c r="D44" s="4">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E44" s="4" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="45" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
@@ -2167,13 +2186,13 @@
         <v>47</v>
       </c>
       <c r="D45" s="4">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="46" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
@@ -2184,15 +2203,14 @@
         <v>47</v>
       </c>
       <c r="D46" s="4">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E46" s="4" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="G46" s="8"/>
+        <v>98</v>
+      </c>
     </row>
     <row r="47" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A47" s="4" t="s">
@@ -2202,14 +2220,15 @@
         <v>47</v>
       </c>
       <c r="D47" s="4">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E47" s="4" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>102</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="G47" s="8"/>
     </row>
     <row r="48" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A48" s="4" t="s">
@@ -2219,13 +2238,13 @@
         <v>47</v>
       </c>
       <c r="D48" s="4">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="49" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
@@ -2236,13 +2255,13 @@
         <v>47</v>
       </c>
       <c r="D49" s="4">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="50" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
@@ -2253,13 +2272,13 @@
         <v>47</v>
       </c>
       <c r="D50" s="4">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E50" s="4" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="F50" s="4" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="51" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
@@ -2270,15 +2289,14 @@
         <v>47</v>
       </c>
       <c r="D51" s="4">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E51" s="4" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="G51" s="8"/>
+        <v>108</v>
+      </c>
     </row>
     <row r="52" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A52" s="4" t="s">
@@ -2288,14 +2306,15 @@
         <v>47</v>
       </c>
       <c r="D52" s="4">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E52" s="4" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>112</v>
-      </c>
+        <v>110</v>
+      </c>
+      <c r="G52" s="8"/>
     </row>
     <row r="53" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A53" s="4" t="s">
@@ -2305,13 +2324,13 @@
         <v>47</v>
       </c>
       <c r="D53" s="4">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E53" s="4" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="54" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
@@ -2322,13 +2341,13 @@
         <v>47</v>
       </c>
       <c r="D54" s="4">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E54" s="4" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="F54" s="4" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="55" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
@@ -2339,13 +2358,13 @@
         <v>47</v>
       </c>
       <c r="D55" s="4">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E55" s="4" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="56" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
@@ -2356,15 +2375,14 @@
         <v>47</v>
       </c>
       <c r="D56" s="4">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E56" s="4" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="F56" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="G56" s="8"/>
+        <v>118</v>
+      </c>
     </row>
     <row r="57" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A57" s="4" t="s">
@@ -2374,14 +2392,15 @@
         <v>47</v>
       </c>
       <c r="D57" s="4">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E57" s="4" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="F57" s="4" t="s">
-        <v>122</v>
-      </c>
+        <v>120</v>
+      </c>
+      <c r="G57" s="8"/>
     </row>
     <row r="58" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A58" s="4" t="s">
@@ -2391,13 +2410,13 @@
         <v>47</v>
       </c>
       <c r="D58" s="4">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E58" s="4" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="F58" s="4" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="59" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
@@ -2408,13 +2427,13 @@
         <v>47</v>
       </c>
       <c r="D59" s="4">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E59" s="4" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="F59" s="4" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="60" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
@@ -2425,13 +2444,13 @@
         <v>47</v>
       </c>
       <c r="D60" s="4">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E60" s="4" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="F60" s="4" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="61" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
@@ -2442,15 +2461,14 @@
         <v>47</v>
       </c>
       <c r="D61" s="4">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E61" s="4" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="F61" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="G61" s="8"/>
+        <v>128</v>
+      </c>
     </row>
     <row r="62" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A62" s="4" t="s">
@@ -2460,14 +2478,15 @@
         <v>47</v>
       </c>
       <c r="D62" s="4">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E62" s="4" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="F62" s="4" t="s">
-        <v>132</v>
-      </c>
+        <v>130</v>
+      </c>
+      <c r="G62" s="8"/>
     </row>
     <row r="63" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A63" s="4" t="s">
@@ -2477,13 +2496,13 @@
         <v>47</v>
       </c>
       <c r="D63" s="4">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E63" s="4" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="F63" s="4" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="64" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
@@ -2494,13 +2513,13 @@
         <v>47</v>
       </c>
       <c r="D64" s="4">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E64" s="4" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="F64" s="4" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="65" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
@@ -2511,13 +2530,13 @@
         <v>47</v>
       </c>
       <c r="D65" s="4">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E65" s="4" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="F65" s="4" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="66" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
@@ -2528,15 +2547,14 @@
         <v>47</v>
       </c>
       <c r="D66" s="4">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E66" s="4" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="F66" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="G66" s="8"/>
+        <v>138</v>
+      </c>
     </row>
     <row r="67" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A67" s="4" t="s">
@@ -2546,14 +2564,15 @@
         <v>47</v>
       </c>
       <c r="D67" s="4">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E67" s="4" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="F67" s="4" t="s">
-        <v>142</v>
-      </c>
+        <v>140</v>
+      </c>
+      <c r="G67" s="8"/>
     </row>
     <row r="68" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A68" s="4" t="s">
@@ -2563,13 +2582,13 @@
         <v>47</v>
       </c>
       <c r="D68" s="4">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E68" s="4" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F68" s="4" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="69" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
@@ -2580,13 +2599,13 @@
         <v>47</v>
       </c>
       <c r="D69" s="4">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E69" s="4" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="F69" s="4" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
     <row r="70" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
@@ -2597,13 +2616,13 @@
         <v>47</v>
       </c>
       <c r="D70" s="4">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E70" s="4" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="F70" s="4" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="71" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
@@ -2614,15 +2633,14 @@
         <v>47</v>
       </c>
       <c r="D71" s="4">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E71" s="4" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="F71" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="G71" s="8"/>
+        <v>148</v>
+      </c>
     </row>
     <row r="72" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A72" s="4" t="s">
@@ -2632,14 +2650,15 @@
         <v>47</v>
       </c>
       <c r="D72" s="4">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E72" s="4" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="F72" s="4" t="s">
-        <v>152</v>
-      </c>
+        <v>150</v>
+      </c>
+      <c r="G72" s="8"/>
     </row>
     <row r="73" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A73" s="4" t="s">
@@ -2649,13 +2668,13 @@
         <v>47</v>
       </c>
       <c r="D73" s="4">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E73" s="4" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="F73" s="4" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="74" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
@@ -2666,13 +2685,13 @@
         <v>47</v>
       </c>
       <c r="D74" s="4">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E74" s="4" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="F74" s="4" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="75" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
@@ -2683,13 +2702,13 @@
         <v>47</v>
       </c>
       <c r="D75" s="4">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E75" s="4" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="F75" s="4" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
     <row r="76" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
@@ -2700,15 +2719,14 @@
         <v>47</v>
       </c>
       <c r="D76" s="4">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E76" s="4" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="F76" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="G76" s="8"/>
+        <v>158</v>
+      </c>
     </row>
     <row r="77" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A77" s="4" t="s">
@@ -2718,14 +2736,15 @@
         <v>47</v>
       </c>
       <c r="D77" s="4">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E77" s="4" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="F77" s="4" t="s">
-        <v>162</v>
-      </c>
+        <v>160</v>
+      </c>
+      <c r="G77" s="8"/>
     </row>
     <row r="78" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A78" s="4" t="s">
@@ -2735,13 +2754,13 @@
         <v>47</v>
       </c>
       <c r="D78" s="4">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E78" s="4" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="F78" s="4" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="79" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
@@ -2752,33 +2771,30 @@
         <v>47</v>
       </c>
       <c r="D79" s="4">
+        <v>44</v>
+      </c>
+      <c r="E79" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="F79" s="4" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A80" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C80" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="D80" s="4">
         <v>45</v>
       </c>
-      <c r="E79" s="4" t="s">
+      <c r="E80" s="4" t="s">
         <v>165</v>
       </c>
-      <c r="F79" s="4" t="s">
+      <c r="F80" s="4" t="s">
         <v>166</v>
-      </c>
-    </row>
-    <row r="80" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A80" s="7" t="s">
-        <v>167</v>
-      </c>
-      <c r="C80" s="7" t="s">
-        <v>168</v>
-      </c>
-      <c r="D80" s="7">
-        <v>1</v>
-      </c>
-      <c r="E80" s="5" t="s">
-        <v>169</v>
-      </c>
-      <c r="F80" s="5" t="s">
-        <v>170</v>
-      </c>
-      <c r="G80" s="7" t="s">
-        <v>171</v>
       </c>
     </row>
     <row r="81" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.3">
@@ -2789,16 +2805,16 @@
         <v>168</v>
       </c>
       <c r="D81" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E81" s="5" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="F81" s="5" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="G81" s="7" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
     </row>
     <row r="82" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.3">
@@ -2809,54 +2825,56 @@
         <v>168</v>
       </c>
       <c r="D82" s="7">
+        <v>2</v>
+      </c>
+      <c r="E82" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="F82" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="G82" s="7" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A83" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="C83" s="7" t="s">
+        <v>168</v>
+      </c>
+      <c r="D83" s="7">
         <v>3</v>
       </c>
-      <c r="E82" s="5" t="s">
+      <c r="E83" s="5" t="s">
         <v>175</v>
       </c>
-      <c r="F82" s="5" t="s">
+      <c r="F83" s="5" t="s">
         <v>176</v>
       </c>
-      <c r="G82" s="7" t="s">
+      <c r="G83" s="7" t="s">
         <v>177</v>
-      </c>
-    </row>
-    <row r="83" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A83" t="s">
-        <v>178</v>
-      </c>
-      <c r="B83" s="4" t="s">
-        <v>179</v>
-      </c>
-      <c r="C83" s="4" t="s">
-        <v>168</v>
-      </c>
-      <c r="D83" s="4">
-        <v>1</v>
-      </c>
-      <c r="E83" t="s">
-        <v>180</v>
-      </c>
-      <c r="F83" t="s">
-        <v>181</v>
       </c>
     </row>
     <row r="84" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>178</v>
       </c>
-      <c r="B84"/>
+      <c r="B84" s="4" t="s">
+        <v>179</v>
+      </c>
       <c r="C84" s="4" t="s">
         <v>168</v>
       </c>
       <c r="D84" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E84" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="F84" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="85" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
@@ -2868,13 +2886,13 @@
         <v>168</v>
       </c>
       <c r="D85" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E85" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="F85" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="86" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
@@ -2886,51 +2904,51 @@
         <v>168</v>
       </c>
       <c r="D86" s="4">
+        <v>3</v>
+      </c>
+      <c r="E86" t="s">
+        <v>184</v>
+      </c>
+      <c r="F86" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A87" t="s">
+        <v>178</v>
+      </c>
+      <c r="B87"/>
+      <c r="C87" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="D87" s="4">
         <v>4</v>
       </c>
-      <c r="E86" t="s">
+      <c r="E87" t="s">
         <v>186</v>
       </c>
-      <c r="F86" t="s">
+      <c r="F87" t="s">
         <v>187</v>
-      </c>
-    </row>
-    <row r="87" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A87" s="5" t="s">
-        <v>188</v>
-      </c>
-      <c r="B87" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="C87" s="7" t="s">
-        <v>168</v>
-      </c>
-      <c r="D87" s="7">
-        <v>1</v>
-      </c>
-      <c r="E87" s="5" t="s">
-        <v>190</v>
-      </c>
-      <c r="F87" s="5" t="s">
-        <v>191</v>
       </c>
     </row>
     <row r="88" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A88" s="5" t="s">
         <v>188</v>
       </c>
-      <c r="B88" s="5"/>
+      <c r="B88" s="7" t="s">
+        <v>189</v>
+      </c>
       <c r="C88" s="7" t="s">
         <v>168</v>
       </c>
       <c r="D88" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E88" s="5" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="F88" s="5" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="89" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.3">
@@ -2942,224 +2960,224 @@
         <v>168</v>
       </c>
       <c r="D89" s="7">
+        <v>2</v>
+      </c>
+      <c r="E89" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="F89" s="5" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A90" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="B90" s="5"/>
+      <c r="C90" s="7" t="s">
+        <v>168</v>
+      </c>
+      <c r="D90" s="7">
         <v>3</v>
       </c>
-      <c r="E89" s="5" t="s">
+      <c r="E90" s="5" t="s">
         <v>194</v>
       </c>
-      <c r="F89" s="5" t="s">
+      <c r="F90" s="5" t="s">
         <v>195</v>
-      </c>
-    </row>
-    <row r="90" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A90" t="s">
-        <v>196</v>
-      </c>
-      <c r="B90" t="s">
-        <v>197</v>
-      </c>
-      <c r="C90" s="4" t="s">
-        <v>168</v>
-      </c>
-      <c r="D90" s="4">
-        <v>1</v>
-      </c>
-      <c r="E90" t="s">
-        <v>198</v>
-      </c>
-      <c r="F90" t="s">
-        <v>263</v>
-      </c>
-      <c r="G90" s="4" t="s">
-        <v>264</v>
       </c>
     </row>
     <row r="91" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>196</v>
       </c>
-      <c r="B91"/>
+      <c r="B91" t="s">
+        <v>197</v>
+      </c>
       <c r="C91" s="4" t="s">
         <v>168</v>
       </c>
       <c r="D91" s="4">
+        <v>1</v>
+      </c>
+      <c r="E91" t="s">
+        <v>198</v>
+      </c>
+      <c r="F91" t="s">
+        <v>263</v>
+      </c>
+      <c r="G91" s="4" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A92" t="s">
+        <v>196</v>
+      </c>
+      <c r="B92"/>
+      <c r="C92" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="D92" s="4">
         <v>2</v>
       </c>
-      <c r="E91" t="s">
+      <c r="E92" t="s">
         <v>199</v>
       </c>
-      <c r="F91" t="s">
+      <c r="F92" t="s">
         <v>265</v>
       </c>
-      <c r="G91" s="4" t="s">
+      <c r="G92" s="4" t="s">
         <v>266</v>
-      </c>
-    </row>
-    <row r="92" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A92" s="5" t="s">
-        <v>200</v>
-      </c>
-      <c r="B92" s="7" t="s">
-        <v>201</v>
-      </c>
-      <c r="C92" s="7" t="s">
-        <v>168</v>
-      </c>
-      <c r="D92" s="7">
-        <v>1</v>
-      </c>
-      <c r="E92" s="5" t="s">
-        <v>202</v>
-      </c>
-      <c r="F92" s="5" t="s">
-        <v>267</v>
-      </c>
-      <c r="G92" s="7" t="s">
-        <v>268</v>
       </c>
     </row>
     <row r="93" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A93" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="B93" s="5"/>
+      <c r="B93" s="7" t="s">
+        <v>201</v>
+      </c>
       <c r="C93" s="7" t="s">
         <v>168</v>
       </c>
       <c r="D93" s="7">
+        <v>1</v>
+      </c>
+      <c r="E93" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="F93" s="5" t="s">
+        <v>267</v>
+      </c>
+      <c r="G93" s="7" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A94" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="B94" s="5"/>
+      <c r="C94" s="7" t="s">
+        <v>168</v>
+      </c>
+      <c r="D94" s="7">
         <v>2</v>
       </c>
-      <c r="E93" s="5" t="s">
+      <c r="E94" s="5" t="s">
         <v>203</v>
       </c>
-      <c r="F93" s="5" t="s">
+      <c r="F94" s="5" t="s">
         <v>269</v>
       </c>
-      <c r="G93" s="7" t="s">
+      <c r="G94" s="7" t="s">
         <v>270</v>
       </c>
     </row>
-    <row r="94" spans="1:7" s="4" customFormat="1" ht="141.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A94" s="9" t="s">
+    <row r="95" spans="1:7" s="4" customFormat="1" ht="141.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A95" s="9" t="s">
         <v>260</v>
       </c>
-      <c r="B94" s="10" t="s">
+      <c r="B95" s="10" t="s">
         <v>205</v>
       </c>
-      <c r="C94" s="4" t="s">
-        <v>168</v>
-      </c>
-      <c r="D94" s="4">
-        <v>1</v>
-      </c>
-      <c r="E94" t="s">
-        <v>261</v>
-      </c>
-      <c r="F94" t="s">
-        <v>276</v>
-      </c>
-      <c r="G94" s="4" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="95" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A95" s="9" t="s">
-        <v>204</v>
-      </c>
-      <c r="B95" s="9"/>
       <c r="C95" s="4" t="s">
         <v>168</v>
       </c>
       <c r="D95" s="4">
+        <v>1</v>
+      </c>
+      <c r="E95" t="s">
+        <v>261</v>
+      </c>
+      <c r="F95" t="s">
+        <v>276</v>
+      </c>
+      <c r="G95" s="4" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A96" s="9" t="s">
+        <v>204</v>
+      </c>
+      <c r="B96" s="9"/>
+      <c r="C96" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="D96" s="4">
         <v>2</v>
       </c>
-      <c r="E95" t="s">
+      <c r="E96" t="s">
         <v>206</v>
       </c>
-      <c r="F95" t="s">
+      <c r="F96" t="s">
         <v>273</v>
       </c>
-      <c r="G95" s="4" t="s">
+      <c r="G96" s="4" t="s">
         <v>272</v>
-      </c>
-    </row>
-    <row r="96" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A96" s="5" t="s">
-        <v>207</v>
-      </c>
-      <c r="B96" s="7" t="s">
-        <v>208</v>
-      </c>
-      <c r="C96" s="7" t="s">
-        <v>168</v>
-      </c>
-      <c r="D96" s="7">
-        <v>1</v>
-      </c>
-      <c r="E96" s="5" t="s">
-        <v>209</v>
-      </c>
-      <c r="F96" s="5" t="s">
-        <v>210</v>
       </c>
     </row>
     <row r="97" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A97" s="5" t="s">
         <v>207</v>
       </c>
-      <c r="B97" s="5"/>
+      <c r="B97" s="7" t="s">
+        <v>208</v>
+      </c>
       <c r="C97" s="7" t="s">
         <v>168</v>
       </c>
       <c r="D97" s="7">
+        <v>1</v>
+      </c>
+      <c r="E97" s="5" t="s">
+        <v>209</v>
+      </c>
+      <c r="F97" s="5" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A98" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="B98" s="5"/>
+      <c r="C98" s="7" t="s">
+        <v>168</v>
+      </c>
+      <c r="D98" s="7">
         <v>2</v>
       </c>
-      <c r="E97" s="5" t="s">
+      <c r="E98" s="5" t="s">
         <v>211</v>
       </c>
-      <c r="F97" s="5" t="s">
+      <c r="F98" s="5" t="s">
         <v>212</v>
-      </c>
-    </row>
-    <row r="98" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A98" s="9" t="s">
-        <v>213</v>
-      </c>
-      <c r="B98" s="4" t="s">
-        <v>214</v>
-      </c>
-      <c r="C98" s="4" t="s">
-        <v>168</v>
-      </c>
-      <c r="D98" s="4">
-        <v>1</v>
-      </c>
-      <c r="E98" t="s">
-        <v>215</v>
-      </c>
-      <c r="F98" s="4" t="s">
-        <v>274</v>
-      </c>
-      <c r="G98" s="4" t="s">
-        <v>275</v>
       </c>
     </row>
     <row r="99" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A99" s="9" t="s">
         <v>213</v>
       </c>
-      <c r="B99" s="9"/>
+      <c r="B99" s="4" t="s">
+        <v>214</v>
+      </c>
       <c r="C99" s="4" t="s">
         <v>168</v>
       </c>
       <c r="D99" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E99" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F99" s="4" t="s">
-        <v>217</v>
+        <v>274</v>
+      </c>
+      <c r="G99" s="4" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="100" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
@@ -3171,30 +3189,31 @@
         <v>168</v>
       </c>
       <c r="D100" s="4">
+        <v>2</v>
+      </c>
+      <c r="E100" t="s">
+        <v>216</v>
+      </c>
+      <c r="F100" s="4" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A101" s="9" t="s">
+        <v>213</v>
+      </c>
+      <c r="B101" s="9"/>
+      <c r="C101" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="D101" s="4">
         <v>3</v>
       </c>
-      <c r="E100" t="s">
+      <c r="E101" t="s">
         <v>218</v>
       </c>
-      <c r="F100" s="4" t="s">
+      <c r="F101" s="4" t="s">
         <v>219</v>
-      </c>
-    </row>
-    <row r="101" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A101" s="7" t="s">
-        <v>220</v>
-      </c>
-      <c r="C101" s="7" t="s">
-        <v>221</v>
-      </c>
-      <c r="D101" s="7">
-        <v>1</v>
-      </c>
-      <c r="E101" s="7" t="s">
-        <v>221</v>
-      </c>
-      <c r="F101" s="7" t="s">
-        <v>222</v>
       </c>
     </row>
     <row r="102" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.3">
@@ -3205,36 +3224,33 @@
         <v>221</v>
       </c>
       <c r="D102" s="7">
+        <v>1</v>
+      </c>
+      <c r="E102" s="7" t="s">
+        <v>221</v>
+      </c>
+      <c r="F102" s="7" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A103" s="7" t="s">
+        <v>220</v>
+      </c>
+      <c r="C103" s="7" t="s">
+        <v>221</v>
+      </c>
+      <c r="D103" s="7">
         <v>2</v>
       </c>
-      <c r="E102" s="7" t="s">
+      <c r="E103" s="7" t="s">
         <v>225</v>
       </c>
-      <c r="F102" s="7" t="s">
+      <c r="F103" s="7" t="s">
         <v>223</v>
       </c>
-      <c r="G102" s="7" t="s">
+      <c r="G103" s="7" t="s">
         <v>224</v>
-      </c>
-    </row>
-    <row r="103" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A103" s="4" t="s">
-        <v>226</v>
-      </c>
-      <c r="C103" s="4" t="s">
-        <v>221</v>
-      </c>
-      <c r="D103" s="4">
-        <v>1</v>
-      </c>
-      <c r="E103" s="4" t="s">
-        <v>227</v>
-      </c>
-      <c r="F103" s="4" t="s">
-        <v>228</v>
-      </c>
-      <c r="G103" s="4" t="s">
-        <v>229</v>
       </c>
     </row>
     <row r="104" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
@@ -3245,16 +3261,16 @@
         <v>221</v>
       </c>
       <c r="D104" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E104" s="4" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="F104" s="4" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="G104" s="4" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
     </row>
     <row r="105" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
@@ -3265,80 +3281,79 @@
         <v>221</v>
       </c>
       <c r="D105" s="4">
+        <v>2</v>
+      </c>
+      <c r="E105" s="4" t="s">
+        <v>230</v>
+      </c>
+      <c r="F105" s="4" t="s">
+        <v>231</v>
+      </c>
+      <c r="G105" s="4" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="106" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A106" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="C106" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="D106" s="4">
         <v>3</v>
       </c>
-      <c r="E105" s="4" t="s">
+      <c r="E106" s="4" t="s">
         <v>233</v>
       </c>
-      <c r="F105" s="4" t="s">
+      <c r="F106" s="4" t="s">
         <v>234</v>
       </c>
-      <c r="G105" s="4" t="s">
+      <c r="G106" s="4" t="s">
         <v>235</v>
-      </c>
-    </row>
-    <row r="106" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A106" s="7" t="s">
-        <v>236</v>
-      </c>
-      <c r="B106" s="7" t="s">
-        <v>262</v>
-      </c>
-      <c r="C106" s="7" t="s">
-        <v>221</v>
-      </c>
-      <c r="D106" s="7">
-        <v>1</v>
-      </c>
-      <c r="E106" s="7" t="s">
-        <v>237</v>
-      </c>
-      <c r="F106" s="7" t="s">
-        <v>238</v>
-      </c>
-      <c r="G106" s="7" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="107" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A107" s="7" t="s">
         <v>236</v>
       </c>
+      <c r="B107" s="7" t="s">
+        <v>262</v>
+      </c>
       <c r="C107" s="7" t="s">
         <v>221</v>
       </c>
       <c r="D107" s="7">
+        <v>1</v>
+      </c>
+      <c r="E107" s="7" t="s">
+        <v>237</v>
+      </c>
+      <c r="F107" s="7" t="s">
+        <v>238</v>
+      </c>
+      <c r="G107" s="7" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="108" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A108" s="7" t="s">
+        <v>236</v>
+      </c>
+      <c r="C108" s="7" t="s">
+        <v>221</v>
+      </c>
+      <c r="D108" s="7">
         <v>2</v>
       </c>
-      <c r="E107" s="7" t="s">
+      <c r="E108" s="7" t="s">
         <v>240</v>
       </c>
-      <c r="F107" s="7" t="s">
+      <c r="F108" s="7" t="s">
         <v>241</v>
       </c>
-      <c r="G107" s="7" t="s">
+      <c r="G108" s="7" t="s">
         <v>242</v>
-      </c>
-    </row>
-    <row r="108" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A108" t="s">
-        <v>243</v>
-      </c>
-      <c r="B108"/>
-      <c r="C108" t="s">
-        <v>26</v>
-      </c>
-      <c r="D108" s="4">
-        <v>1</v>
-      </c>
-      <c r="E108" t="s">
-        <v>244</v>
-      </c>
-      <c r="F108" t="s">
-        <v>245</v>
-      </c>
-      <c r="G108" t="s">
-        <v>246</v>
       </c>
     </row>
     <row r="109" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
@@ -3350,16 +3365,16 @@
         <v>26</v>
       </c>
       <c r="D109" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E109" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="F109" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="G109" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="110" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
@@ -3371,16 +3386,16 @@
         <v>26</v>
       </c>
       <c r="D110" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E110" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="F110" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="G110" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
     </row>
     <row r="111" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
@@ -3392,102 +3407,103 @@
         <v>26</v>
       </c>
       <c r="D111" s="4">
+        <v>3</v>
+      </c>
+      <c r="E111" t="s">
+        <v>250</v>
+      </c>
+      <c r="F111" t="s">
+        <v>251</v>
+      </c>
+      <c r="G111" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="112" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A112" t="s">
+        <v>243</v>
+      </c>
+      <c r="B112"/>
+      <c r="C112" t="s">
+        <v>26</v>
+      </c>
+      <c r="D112" s="4">
         <v>4</v>
       </c>
-      <c r="E111" t="s">
+      <c r="E112" t="s">
         <v>253</v>
       </c>
-      <c r="F111" t="s">
+      <c r="F112" t="s">
         <v>254</v>
       </c>
-      <c r="G111" t="s">
+      <c r="G112" t="s">
         <v>255</v>
-      </c>
-    </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A112" s="1" t="s">
-        <v>277</v>
-      </c>
-      <c r="B112" s="1" t="s">
-        <v>285</v>
-      </c>
-      <c r="C112" s="1" t="s">
-        <v>278</v>
-      </c>
-      <c r="D112" s="1">
-        <v>1</v>
-      </c>
-      <c r="E112" s="1" t="s">
-        <v>279</v>
-      </c>
-      <c r="F112" s="1" t="s">
-        <v>282</v>
-      </c>
-      <c r="G112" s="1" t="s">
-        <v>283</v>
       </c>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A113" s="1" t="s">
         <v>277</v>
       </c>
+      <c r="B113" s="1" t="s">
+        <v>285</v>
+      </c>
       <c r="C113" s="1" t="s">
         <v>278</v>
       </c>
       <c r="D113" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="F113" s="1" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="G113" s="1" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A114" s="1" t="s">
-        <v>286</v>
-      </c>
-      <c r="B114" s="1" t="s">
-        <v>287</v>
+        <v>277</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>288</v>
+        <v>278</v>
       </c>
       <c r="D114" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>289</v>
+        <v>280</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>290</v>
+        <v>281</v>
       </c>
       <c r="G114" s="1" t="s">
-        <v>291</v>
+        <v>284</v>
       </c>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A115" s="1" t="s">
         <v>286</v>
       </c>
+      <c r="B115" s="1" t="s">
+        <v>287</v>
+      </c>
       <c r="C115" s="1" t="s">
         <v>288</v>
       </c>
       <c r="D115" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="F115" s="1" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="G115" s="1" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.3">
@@ -3498,21 +3514,41 @@
         <v>288</v>
       </c>
       <c r="D116" s="1">
+        <v>2</v>
+      </c>
+      <c r="E116" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="F116" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="G116" s="1" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="117" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A117" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="C117" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="D117" s="1">
         <v>3</v>
       </c>
-      <c r="E116" s="1" t="s">
+      <c r="E117" s="1" t="s">
         <v>295</v>
       </c>
-      <c r="F116" s="1" t="s">
+      <c r="F117" s="1" t="s">
         <v>296</v>
       </c>
-      <c r="G116" s="1" t="s">
+      <c r="G117" s="1" t="s">
         <v>297</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="E1:E111" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
-  <phoneticPr fontId="2" type="noConversion"/>
+  <autoFilter ref="E1:E112" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Development/Common/GameData/Enum/GameEnum.xlsx
+++ b/Development/Common/GameData/Enum/GameEnum.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\project\MMOGameServerProject\Development\Common\GameData\Enum\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\project\MMOGameServerProject\Development\Common\GameData\Enum\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91DE8405-31CE-41F4-BAF8-45732242CDE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BFC1C08-27D8-4541-BC28-38A489CA0AB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38280" yWindow="5355" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Enum" sheetId="1" r:id="rId1"/>
@@ -23,17 +23,31 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="507" uniqueCount="300">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="524" uniqueCount="310">
   <si>
     <t>Enum 이름</t>
   </si>
   <si>
+    <t>Enum 설명</t>
+  </si>
+  <si>
     <t>파일그룹</t>
   </si>
   <si>
+    <t>Enum 값
+int32 타입이고, 1부터시작 한다.
+값 0은 무조건 None이 자동 생성되고, 마지막값+1 은 Max가 자동으로 생성된다.</t>
+  </si>
+  <si>
+    <t>Enum 값 이름</t>
+  </si>
+  <si>
     <t>Enum 값 한글명</t>
   </si>
   <si>
+    <t>값 설명</t>
+  </si>
+  <si>
     <t>Team</t>
   </si>
   <si>
@@ -148,6 +162,12 @@
     <t>드롭아이템</t>
   </si>
   <si>
+    <t>EventArea</t>
+  </si>
+  <si>
+    <t>이벤트영역</t>
+  </si>
+  <si>
     <t>ResultCode</t>
   </si>
   <si>
@@ -622,9 +642,21 @@
     <t>Static</t>
   </si>
   <si>
+    <t>고정</t>
+  </si>
+  <si>
+    <t>얼음지대, 화염지대, 전격방출, 메테오 착탄 등</t>
+  </si>
+  <si>
     <t>Linear</t>
   </si>
   <si>
+    <t>직선 등속</t>
+  </si>
+  <si>
+    <t>이동하는 장판 등의 하이브리드</t>
+  </si>
+  <si>
     <t>SkillEffectDamage</t>
   </si>
   <si>
@@ -634,7 +666,19 @@
     <t>ContactHit</t>
   </si>
   <si>
+    <t>투사체 접촉 시 1회</t>
+  </si>
+  <si>
+    <t>투사체 접촉 시 클라이언트가 hit을 보고한다.</t>
+  </si>
+  <si>
     <t>Area</t>
+  </si>
+  <si>
+    <t>서버 주도 범위 틱</t>
+  </si>
+  <si>
+    <t>서버에서 영역내의 적에게 대미지를 입힌다.</t>
   </si>
   <si>
     <t>SkillEffectShape</t>
@@ -645,9 +689,24 @@
 중심 좌표(center)는 모양에 넣지 않는다. 이동하는 효과는 매 tick center 가 달라지므로 center 는 판정 시점에 인자로 받고, 모양 자체(반지름/크기/방향)만 보관한다.</t>
   </si>
   <si>
+    <t>Circle</t>
+  </si>
+  <si>
+    <t>원형</t>
+  </si>
+  <si>
+    <t>전격방출, 메테오 착탄, 파이어볼 폭발 등</t>
+  </si>
+  <si>
     <t>Obb</t>
   </si>
   <si>
+    <t>방향이 있는 직사각형, OBB(Oriented Bounding Box)</t>
+  </si>
+  <si>
+    <t>얼음지대, 블레이즈</t>
+  </si>
+  <si>
     <t xml:space="preserve">TargetingMode </t>
   </si>
   <si>
@@ -675,6 +734,12 @@
     <t>Caster</t>
   </si>
   <si>
+    <t>캐스터 위치</t>
+  </si>
+  <si>
+    <t>투사체 발사점 / 캐스터 중심 범위</t>
+  </si>
+  <si>
     <t>Target</t>
   </si>
   <si>
@@ -696,15 +761,15 @@
     <t>이로운효과</t>
   </si>
   <si>
+    <t>Debuff</t>
+  </si>
+  <si>
     <t>해로운효과</t>
   </si>
   <si>
     <t>디스펠 대상</t>
   </si>
   <si>
-    <t>Debuff</t>
-  </si>
-  <si>
     <t>BuffStackPolicy</t>
   </si>
   <si>
@@ -738,6 +803,9 @@
     <t>PeriodicEffect</t>
   </si>
   <si>
+    <t>버프의 주기적 효과</t>
+  </si>
+  <si>
     <t>DamageHp</t>
   </si>
   <si>
@@ -795,181 +863,100 @@
     <t>외부에서 들어오는 세번째 위치</t>
   </si>
   <si>
-    <t>값 설명</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Enum 설명</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Enum 값
-int32 타입이고, 1부터시작 한다.
-값 0은 무조건 None이 자동 생성되고, 마지막값+1 은 Max가 자동으로 생성된다.</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Enum 값 이름</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>SkillEffectShape</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Circle</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>버프의 주기적 효과</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>고정</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>얼음지대, 화염지대, 전격방출, 메테오 착탄 등</t>
-  </si>
-  <si>
-    <t>직선 등속</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>이동하는 장판 등의 하이브리드</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>투사체 접촉 시 1회</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>투사체 접촉 시 클라이언트가 hit을 보고한다.</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>서버 주도 범위 틱</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>서버에서 영역내의 적에게 대미지를 입힌다.</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>전격방출, 메테오 착탄, 파이어볼 폭발 등</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>얼음지대, 블레이즈</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>방향이 있는 직사각형, OBB(Oriented Bounding Box)</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>캐스터 위치</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>투사체 발사점 / 캐스터 중심 범위</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>원형</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>MonsterAIType</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Monster</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>몬스터 AI 종류</t>
   </si>
   <si>
     <t>FSM</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>유한상태기계</t>
+  </si>
+  <si>
+    <t>일반몬스터용</t>
   </si>
   <si>
     <t>BehaviourTree</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>행동 트리</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>유한상태기계</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>일반몬스터용</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>엘리트 몬스터, 보스용</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>몬스터 AI 종류</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>SpawnActivation</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>스폰 활성화 모드</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Monster</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>Always</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>항상</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>항상 밀도 유지</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>PlayerProximity</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>근접 활성</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>플레이어 근접 시만</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>Manual</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>수동</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>Stage 스크립트에서 ActivateSpawner 등으로 활성화시킴</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>EventArea</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>이벤트영역</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>PropStateMode</t>
+  </si>
+  <si>
+    <t>prop 상태머신 모드</t>
+  </si>
+  <si>
+    <t>Toggle</t>
+  </si>
+  <si>
+    <t>토글</t>
+  </si>
+  <si>
+    <t>상호작용마다 상태 순환(StateCount 만큼)</t>
+  </si>
+  <si>
+    <t>OneShot</t>
+  </si>
+  <si>
+    <t>일회성</t>
+  </si>
+  <si>
+    <t>0→1 1회 전이 후 더 이상 상태변화 없음</t>
+  </si>
+  <si>
+    <t>PropBehavior</t>
+  </si>
+  <si>
+    <t>prop 선언형 동작</t>
+  </si>
+  <si>
+    <t>Portal</t>
+  </si>
+  <si>
+    <t>포탈</t>
+  </si>
+  <si>
+    <t>상호작용 시 지정 스테이지/위치로 이동(무스크립트)</t>
   </si>
 </sst>
 </file>
@@ -1089,11 +1076,11 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -1123,6 +1110,12 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1405,7 +1398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G117"/>
+  <dimension ref="A1:G120"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="22.75" style="1" customWidth="1"/>
@@ -1415,8 +1408,8 @@
     <col min="5" max="5" width="29.125" style="1" customWidth="1"/>
     <col min="6" max="6" width="26" style="1" customWidth="1"/>
     <col min="7" max="7" width="36.625" style="1" customWidth="1"/>
-    <col min="8" max="8" width="9" style="1" customWidth="1"/>
-    <col min="9" max="16384" width="9" style="1"/>
+    <col min="8" max="9" width="9" style="1" customWidth="1"/>
+    <col min="10" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" s="3" customFormat="1" ht="72" customHeight="1" x14ac:dyDescent="0.3">
@@ -1424,2063 +1417,2055 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>257</v>
+        <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>258</v>
+        <v>3</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>259</v>
+        <v>4</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>256</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D2" s="4">
         <v>1</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D3" s="4">
         <v>2</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D4" s="4">
         <v>1</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D5" s="4">
         <v>2</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6" spans="1:7" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A6" s="6" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D6" s="6">
         <v>1</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:7" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A7" s="6" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D7" s="6">
         <v>2</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="8" spans="1:7" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A8" s="6" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D8" s="6">
         <v>3</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="9" spans="1:7" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A9" s="6" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D9" s="6">
         <v>4</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="10" spans="1:7" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A10" s="6" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D10" s="6">
         <v>5</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="11" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D11" s="4">
         <v>1</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
     </row>
     <row r="12" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D12" s="4">
         <v>2</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
     </row>
     <row r="13" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D13" s="4">
         <v>3</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
     </row>
     <row r="14" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D14" s="4">
         <v>4</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="15" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A15" s="7" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D15" s="7">
         <v>1</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A16" s="7" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D16" s="7">
         <v>2</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="17" spans="1:6" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A17" s="7" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D17" s="7">
         <v>3</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="18" spans="1:6" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A18" s="7" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D18" s="7">
         <v>4</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
     </row>
     <row r="19" spans="1:6" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A19" s="7" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D19" s="7">
         <v>5</v>
       </c>
       <c r="E19" s="11" t="s">
-        <v>298</v>
+        <v>45</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>299</v>
+        <v>46</v>
       </c>
     </row>
     <row r="20" spans="1:6" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A20" s="7" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D20" s="7">
         <v>1</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
     </row>
     <row r="21" spans="1:6" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A21" s="7" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D21" s="7">
         <v>2</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
     </row>
     <row r="22" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A22" s="4" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D22" s="4">
         <v>1</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="F22" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
     </row>
     <row r="23" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A23" s="4" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D23" s="4">
         <v>2</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="F23" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
     </row>
     <row r="24" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A24" s="4" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D24" s="4">
         <v>3</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="F24" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
     </row>
     <row r="25" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A25" s="4" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D25" s="4">
         <v>4</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="F25" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
     </row>
     <row r="26" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A26" s="4" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D26" s="4">
         <v>5</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="F26" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
     </row>
     <row r="27" spans="1:6" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A27" s="7" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D27" s="7">
         <v>1</v>
       </c>
       <c r="E27" s="7" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="F27" s="7" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
     </row>
     <row r="28" spans="1:6" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A28" s="7" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D28" s="7">
         <v>2</v>
       </c>
       <c r="E28" s="7" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="F28" s="7" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
     </row>
     <row r="29" spans="1:6" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A29" s="7" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D29" s="7">
         <v>3</v>
       </c>
       <c r="E29" s="7" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="F29" s="7" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
     </row>
     <row r="30" spans="1:6" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A30" s="7" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D30" s="7">
         <v>4</v>
       </c>
       <c r="E30" s="7" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="F30" s="7" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
     </row>
     <row r="31" spans="1:6" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A31" s="7" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D31" s="7">
         <v>5</v>
       </c>
       <c r="E31" s="7" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="F31" s="7" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
     </row>
     <row r="32" spans="1:6" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A32" s="7" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D32" s="7">
         <v>6</v>
       </c>
       <c r="E32" s="7" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="F32" s="7" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
     </row>
     <row r="33" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A33" s="7" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D33" s="7">
         <v>7</v>
       </c>
       <c r="E33" s="7" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="F33" s="7" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
     </row>
     <row r="34" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A34" s="7" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D34" s="7">
         <v>8</v>
       </c>
       <c r="E34" s="7" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="F34" s="7" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
     </row>
     <row r="35" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A35" s="7" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D35" s="7">
         <v>9</v>
       </c>
       <c r="E35" s="7" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="F35" s="7" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
     </row>
     <row r="36" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A36" s="4" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D36" s="4">
         <v>1</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
     </row>
     <row r="37" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A37" s="4" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D37" s="4">
         <v>2</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="G37" s="8"/>
     </row>
     <row r="38" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A38" s="4" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D38" s="4">
         <v>3</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
     </row>
     <row r="39" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A39" s="4" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D39" s="4">
         <v>4</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
     </row>
     <row r="40" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A40" s="4" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D40" s="4">
         <v>5</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
     </row>
     <row r="41" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A41" s="4" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D41" s="4">
         <v>6</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
     </row>
     <row r="42" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A42" s="4" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D42" s="4">
         <v>7</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="G42" s="8"/>
     </row>
     <row r="43" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A43" s="4" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D43" s="4">
         <v>8</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
     </row>
     <row r="44" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A44" s="4" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D44" s="4">
         <v>9</v>
       </c>
       <c r="E44" s="4" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
     </row>
     <row r="45" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A45" s="4" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D45" s="4">
         <v>10</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
     </row>
     <row r="46" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A46" s="4" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D46" s="4">
         <v>11</v>
       </c>
       <c r="E46" s="4" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
     </row>
     <row r="47" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A47" s="4" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D47" s="4">
         <v>12</v>
       </c>
       <c r="E47" s="4" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="G47" s="8"/>
     </row>
     <row r="48" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A48" s="4" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D48" s="4">
         <v>13</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
     </row>
     <row r="49" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A49" s="4" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D49" s="4">
         <v>14</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
     </row>
     <row r="50" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A50" s="4" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D50" s="4">
         <v>15</v>
       </c>
       <c r="E50" s="4" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="F50" s="4" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
     </row>
     <row r="51" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A51" s="4" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D51" s="4">
         <v>16</v>
       </c>
       <c r="E51" s="4" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
     </row>
     <row r="52" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A52" s="4" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D52" s="4">
         <v>17</v>
       </c>
       <c r="E52" s="4" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="G52" s="8"/>
     </row>
     <row r="53" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A53" s="4" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D53" s="4">
         <v>18</v>
       </c>
       <c r="E53" s="4" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
     </row>
     <row r="54" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A54" s="4" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D54" s="4">
         <v>19</v>
       </c>
       <c r="E54" s="4" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="F54" s="4" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
     </row>
     <row r="55" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A55" s="4" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D55" s="4">
         <v>20</v>
       </c>
       <c r="E55" s="4" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
     </row>
     <row r="56" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A56" s="4" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D56" s="4">
         <v>21</v>
       </c>
       <c r="E56" s="4" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="F56" s="4" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
     </row>
     <row r="57" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A57" s="4" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D57" s="4">
         <v>22</v>
       </c>
       <c r="E57" s="4" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="F57" s="4" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="G57" s="8"/>
     </row>
     <row r="58" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A58" s="4" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D58" s="4">
         <v>23</v>
       </c>
       <c r="E58" s="4" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="F58" s="4" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
     </row>
     <row r="59" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A59" s="4" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D59" s="4">
         <v>24</v>
       </c>
       <c r="E59" s="4" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="F59" s="4" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
     </row>
     <row r="60" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A60" s="4" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D60" s="4">
         <v>25</v>
       </c>
       <c r="E60" s="4" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="F60" s="4" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
     </row>
     <row r="61" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A61" s="4" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D61" s="4">
         <v>26</v>
       </c>
       <c r="E61" s="4" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="F61" s="4" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
     </row>
     <row r="62" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A62" s="4" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D62" s="4">
         <v>27</v>
       </c>
       <c r="E62" s="4" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="F62" s="4" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="G62" s="8"/>
     </row>
     <row r="63" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A63" s="4" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D63" s="4">
         <v>28</v>
       </c>
       <c r="E63" s="4" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="F63" s="4" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
     </row>
     <row r="64" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A64" s="4" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D64" s="4">
         <v>29</v>
       </c>
       <c r="E64" s="4" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="F64" s="4" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
     </row>
     <row r="65" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A65" s="4" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D65" s="4">
         <v>30</v>
       </c>
       <c r="E65" s="4" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="F65" s="4" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
     </row>
     <row r="66" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A66" s="4" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="C66" s="4" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D66" s="4">
         <v>31</v>
       </c>
       <c r="E66" s="4" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="F66" s="4" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
     </row>
     <row r="67" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A67" s="4" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D67" s="4">
         <v>32</v>
       </c>
       <c r="E67" s="4" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="F67" s="4" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="G67" s="8"/>
     </row>
     <row r="68" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A68" s="4" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="C68" s="4" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D68" s="4">
         <v>33</v>
       </c>
       <c r="E68" s="4" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="F68" s="4" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
     </row>
     <row r="69" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A69" s="4" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D69" s="4">
         <v>34</v>
       </c>
       <c r="E69" s="4" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="F69" s="4" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
     </row>
     <row r="70" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A70" s="4" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D70" s="4">
         <v>35</v>
       </c>
       <c r="E70" s="4" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="F70" s="4" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
     </row>
     <row r="71" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A71" s="4" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D71" s="4">
         <v>36</v>
       </c>
       <c r="E71" s="4" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="F71" s="4" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
     </row>
     <row r="72" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A72" s="4" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D72" s="4">
         <v>37</v>
       </c>
       <c r="E72" s="4" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="F72" s="4" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="G72" s="8"/>
     </row>
     <row r="73" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A73" s="4" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D73" s="4">
         <v>38</v>
       </c>
       <c r="E73" s="4" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="F73" s="4" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
     </row>
     <row r="74" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A74" s="4" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D74" s="4">
         <v>39</v>
       </c>
       <c r="E74" s="4" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="F74" s="4" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
     </row>
     <row r="75" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A75" s="4" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="C75" s="4" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D75" s="4">
         <v>40</v>
       </c>
       <c r="E75" s="4" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="F75" s="4" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
     </row>
     <row r="76" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A76" s="4" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="C76" s="4" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D76" s="4">
         <v>41</v>
       </c>
       <c r="E76" s="4" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="F76" s="4" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
     </row>
     <row r="77" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A77" s="4" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="C77" s="4" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D77" s="4">
         <v>42</v>
       </c>
       <c r="E77" s="4" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="F77" s="4" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="G77" s="8"/>
     </row>
     <row r="78" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A78" s="4" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D78" s="4">
         <v>43</v>
       </c>
       <c r="E78" s="4" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="F78" s="4" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
     </row>
     <row r="79" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A79" s="4" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D79" s="4">
         <v>44</v>
       </c>
       <c r="E79" s="4" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="F79" s="4" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
     </row>
     <row r="80" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A80" s="4" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="C80" s="4" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D80" s="4">
         <v>45</v>
       </c>
       <c r="E80" s="4" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="F80" s="4" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
     </row>
     <row r="81" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A81" s="7" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="C81" s="7" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="D81" s="7">
         <v>1</v>
       </c>
       <c r="E81" s="5" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="F81" s="5" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="G81" s="7" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
     </row>
     <row r="82" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A82" s="7" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="C82" s="7" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="D82" s="7">
         <v>2</v>
       </c>
       <c r="E82" s="5" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="F82" s="5" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="G82" s="7" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
     </row>
     <row r="83" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A83" s="7" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="C83" s="7" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="D83" s="7">
         <v>3</v>
       </c>
       <c r="E83" s="5" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="F83" s="5" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="G83" s="7" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
     </row>
     <row r="84" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="C84" s="4" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="D84" s="4">
         <v>1</v>
       </c>
       <c r="E84" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="F84" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
     </row>
     <row r="85" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>178</v>
-      </c>
-      <c r="B85"/>
+        <v>184</v>
+      </c>
       <c r="C85" s="4" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="D85" s="4">
         <v>2</v>
       </c>
       <c r="E85" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="F85" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
     </row>
     <row r="86" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>178</v>
-      </c>
-      <c r="B86"/>
+        <v>184</v>
+      </c>
       <c r="C86" s="4" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="D86" s="4">
         <v>3</v>
       </c>
       <c r="E86" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="F86" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
     </row>
     <row r="87" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>178</v>
-      </c>
-      <c r="B87"/>
+        <v>184</v>
+      </c>
       <c r="C87" s="4" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="D87" s="4">
         <v>4</v>
       </c>
       <c r="E87" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="F87" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
     </row>
     <row r="88" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A88" s="5" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="B88" s="7" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="C88" s="7" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="D88" s="7">
         <v>1</v>
       </c>
       <c r="E88" s="5" t="s">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="F88" s="5" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
     </row>
     <row r="89" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A89" s="5" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="B89" s="5"/>
       <c r="C89" s="7" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="D89" s="7">
         <v>2</v>
       </c>
       <c r="E89" s="5" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="F89" s="5" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
     </row>
     <row r="90" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A90" s="5" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="B90" s="5"/>
       <c r="C90" s="7" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="D90" s="7">
         <v>3</v>
       </c>
       <c r="E90" s="5" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="F90" s="5" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
     </row>
     <row r="91" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="B91" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="C91" s="4" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="D91" s="4">
         <v>1</v>
       </c>
       <c r="E91" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="F91" t="s">
-        <v>263</v>
+        <v>205</v>
       </c>
       <c r="G91" s="4" t="s">
-        <v>264</v>
+        <v>206</v>
       </c>
     </row>
     <row r="92" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>196</v>
-      </c>
-      <c r="B92"/>
+        <v>202</v>
+      </c>
       <c r="C92" s="4" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="D92" s="4">
         <v>2</v>
       </c>
       <c r="E92" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="F92" t="s">
-        <v>265</v>
+        <v>208</v>
       </c>
       <c r="G92" s="4" t="s">
-        <v>266</v>
+        <v>209</v>
       </c>
     </row>
     <row r="93" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A93" s="5" t="s">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="B93" s="7" t="s">
-        <v>201</v>
+        <v>211</v>
       </c>
       <c r="C93" s="7" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="D93" s="7">
         <v>1</v>
       </c>
       <c r="E93" s="5" t="s">
-        <v>202</v>
+        <v>212</v>
       </c>
       <c r="F93" s="5" t="s">
-        <v>267</v>
+        <v>213</v>
       </c>
       <c r="G93" s="7" t="s">
-        <v>268</v>
+        <v>214</v>
       </c>
     </row>
     <row r="94" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A94" s="5" t="s">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="B94" s="5"/>
       <c r="C94" s="7" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="D94" s="7">
         <v>2</v>
       </c>
       <c r="E94" s="5" t="s">
-        <v>203</v>
+        <v>215</v>
       </c>
       <c r="F94" s="5" t="s">
-        <v>269</v>
+        <v>216</v>
       </c>
       <c r="G94" s="7" t="s">
-        <v>270</v>
+        <v>217</v>
       </c>
     </row>
     <row r="95" spans="1:7" s="4" customFormat="1" ht="141.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A95" s="9" t="s">
-        <v>260</v>
+        <v>218</v>
       </c>
       <c r="B95" s="10" t="s">
-        <v>205</v>
+        <v>219</v>
       </c>
       <c r="C95" s="4" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="D95" s="4">
         <v>1</v>
       </c>
       <c r="E95" t="s">
-        <v>261</v>
+        <v>220</v>
       </c>
       <c r="F95" t="s">
-        <v>276</v>
+        <v>221</v>
       </c>
       <c r="G95" s="4" t="s">
-        <v>271</v>
+        <v>222</v>
       </c>
     </row>
     <row r="96" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A96" s="9" t="s">
-        <v>204</v>
+        <v>218</v>
       </c>
       <c r="B96" s="9"/>
       <c r="C96" s="4" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="D96" s="4">
         <v>2</v>
       </c>
       <c r="E96" t="s">
-        <v>206</v>
+        <v>223</v>
       </c>
       <c r="F96" t="s">
-        <v>273</v>
+        <v>224</v>
       </c>
       <c r="G96" s="4" t="s">
-        <v>272</v>
+        <v>225</v>
       </c>
     </row>
     <row r="97" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A97" s="5" t="s">
-        <v>207</v>
+        <v>226</v>
       </c>
       <c r="B97" s="7" t="s">
-        <v>208</v>
+        <v>227</v>
       </c>
       <c r="C97" s="7" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="D97" s="7">
         <v>1</v>
       </c>
       <c r="E97" s="5" t="s">
-        <v>209</v>
+        <v>228</v>
       </c>
       <c r="F97" s="5" t="s">
-        <v>210</v>
+        <v>229</v>
       </c>
     </row>
     <row r="98" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A98" s="5" t="s">
-        <v>207</v>
+        <v>226</v>
       </c>
       <c r="B98" s="5"/>
       <c r="C98" s="7" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="D98" s="7">
         <v>2</v>
       </c>
       <c r="E98" s="5" t="s">
-        <v>211</v>
+        <v>230</v>
       </c>
       <c r="F98" s="5" t="s">
-        <v>212</v>
+        <v>231</v>
       </c>
     </row>
     <row r="99" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A99" s="9" t="s">
-        <v>213</v>
+        <v>232</v>
       </c>
       <c r="B99" s="4" t="s">
-        <v>214</v>
+        <v>233</v>
       </c>
       <c r="C99" s="4" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="D99" s="4">
         <v>1</v>
       </c>
       <c r="E99" t="s">
-        <v>215</v>
+        <v>234</v>
       </c>
       <c r="F99" s="4" t="s">
-        <v>274</v>
+        <v>235</v>
       </c>
       <c r="G99" s="4" t="s">
-        <v>275</v>
+        <v>236</v>
       </c>
     </row>
     <row r="100" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A100" s="9" t="s">
-        <v>213</v>
+        <v>232</v>
       </c>
       <c r="B100" s="9"/>
       <c r="C100" s="4" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="D100" s="4">
         <v>2</v>
       </c>
       <c r="E100" t="s">
-        <v>216</v>
+        <v>237</v>
       </c>
       <c r="F100" s="4" t="s">
-        <v>217</v>
+        <v>238</v>
       </c>
     </row>
     <row r="101" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A101" s="9" t="s">
-        <v>213</v>
+        <v>232</v>
       </c>
       <c r="B101" s="9"/>
       <c r="C101" s="4" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="D101" s="4">
         <v>3</v>
       </c>
       <c r="E101" t="s">
-        <v>218</v>
+        <v>239</v>
       </c>
       <c r="F101" s="4" t="s">
-        <v>219</v>
+        <v>240</v>
       </c>
     </row>
     <row r="102" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A102" s="7" t="s">
-        <v>220</v>
+        <v>241</v>
       </c>
       <c r="C102" s="7" t="s">
-        <v>221</v>
+        <v>242</v>
       </c>
       <c r="D102" s="7">
         <v>1</v>
       </c>
       <c r="E102" s="7" t="s">
-        <v>221</v>
+        <v>242</v>
       </c>
       <c r="F102" s="7" t="s">
-        <v>222</v>
+        <v>243</v>
       </c>
     </row>
     <row r="103" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A103" s="7" t="s">
-        <v>220</v>
+        <v>241</v>
       </c>
       <c r="C103" s="7" t="s">
-        <v>221</v>
+        <v>242</v>
       </c>
       <c r="D103" s="7">
         <v>2</v>
       </c>
       <c r="E103" s="7" t="s">
-        <v>225</v>
+        <v>244</v>
       </c>
       <c r="F103" s="7" t="s">
-        <v>223</v>
+        <v>245</v>
       </c>
       <c r="G103" s="7" t="s">
-        <v>224</v>
+        <v>246</v>
       </c>
     </row>
     <row r="104" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A104" s="4" t="s">
-        <v>226</v>
+        <v>247</v>
       </c>
       <c r="C104" s="4" t="s">
-        <v>221</v>
+        <v>242</v>
       </c>
       <c r="D104" s="4">
         <v>1</v>
       </c>
       <c r="E104" s="4" t="s">
-        <v>227</v>
+        <v>248</v>
       </c>
       <c r="F104" s="4" t="s">
-        <v>228</v>
+        <v>249</v>
       </c>
       <c r="G104" s="4" t="s">
-        <v>229</v>
+        <v>250</v>
       </c>
     </row>
     <row r="105" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A105" s="4" t="s">
-        <v>226</v>
+        <v>247</v>
       </c>
       <c r="C105" s="4" t="s">
-        <v>221</v>
+        <v>242</v>
       </c>
       <c r="D105" s="4">
         <v>2</v>
       </c>
       <c r="E105" s="4" t="s">
-        <v>230</v>
+        <v>251</v>
       </c>
       <c r="F105" s="4" t="s">
-        <v>231</v>
+        <v>252</v>
       </c>
       <c r="G105" s="4" t="s">
-        <v>232</v>
+        <v>253</v>
       </c>
     </row>
     <row r="106" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A106" s="4" t="s">
-        <v>226</v>
+        <v>247</v>
       </c>
       <c r="C106" s="4" t="s">
-        <v>221</v>
+        <v>242</v>
       </c>
       <c r="D106" s="4">
         <v>3</v>
       </c>
       <c r="E106" s="4" t="s">
-        <v>233</v>
+        <v>254</v>
       </c>
       <c r="F106" s="4" t="s">
-        <v>234</v>
+        <v>255</v>
       </c>
       <c r="G106" s="4" t="s">
-        <v>235</v>
+        <v>256</v>
       </c>
     </row>
     <row r="107" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A107" s="7" t="s">
-        <v>236</v>
+        <v>257</v>
       </c>
       <c r="B107" s="7" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C107" s="7" t="s">
-        <v>221</v>
+        <v>242</v>
       </c>
       <c r="D107" s="7">
         <v>1</v>
       </c>
       <c r="E107" s="7" t="s">
-        <v>237</v>
+        <v>259</v>
       </c>
       <c r="F107" s="7" t="s">
-        <v>238</v>
+        <v>260</v>
       </c>
       <c r="G107" s="7" t="s">
-        <v>239</v>
+        <v>261</v>
       </c>
     </row>
     <row r="108" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A108" s="7" t="s">
-        <v>236</v>
+        <v>257</v>
       </c>
       <c r="C108" s="7" t="s">
-        <v>221</v>
+        <v>242</v>
       </c>
       <c r="D108" s="7">
         <v>2</v>
       </c>
       <c r="E108" s="7" t="s">
-        <v>240</v>
+        <v>262</v>
       </c>
       <c r="F108" s="7" t="s">
-        <v>241</v>
+        <v>263</v>
       </c>
       <c r="G108" s="7" t="s">
-        <v>242</v>
+        <v>264</v>
       </c>
     </row>
     <row r="109" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
-        <v>243</v>
-      </c>
-      <c r="B109"/>
+        <v>265</v>
+      </c>
       <c r="C109" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D109" s="4">
         <v>1</v>
       </c>
       <c r="E109" t="s">
-        <v>244</v>
+        <v>266</v>
       </c>
       <c r="F109" t="s">
-        <v>245</v>
+        <v>267</v>
       </c>
       <c r="G109" t="s">
-        <v>246</v>
+        <v>268</v>
       </c>
     </row>
     <row r="110" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>243</v>
-      </c>
-      <c r="B110"/>
+        <v>265</v>
+      </c>
       <c r="C110" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D110" s="4">
         <v>2</v>
       </c>
       <c r="E110" t="s">
-        <v>247</v>
+        <v>269</v>
       </c>
       <c r="F110" t="s">
-        <v>248</v>
+        <v>270</v>
       </c>
       <c r="G110" t="s">
-        <v>249</v>
+        <v>271</v>
       </c>
     </row>
     <row r="111" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>243</v>
-      </c>
-      <c r="B111"/>
+        <v>265</v>
+      </c>
       <c r="C111" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D111" s="4">
         <v>3</v>
       </c>
       <c r="E111" t="s">
-        <v>250</v>
+        <v>272</v>
       </c>
       <c r="F111" t="s">
-        <v>251</v>
+        <v>273</v>
       </c>
       <c r="G111" t="s">
-        <v>252</v>
+        <v>274</v>
       </c>
     </row>
     <row r="112" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
-        <v>243</v>
-      </c>
-      <c r="B112"/>
+        <v>265</v>
+      </c>
       <c r="C112" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D112" s="4">
         <v>4</v>
       </c>
       <c r="E112" t="s">
-        <v>253</v>
+        <v>275</v>
       </c>
       <c r="F112" t="s">
-        <v>254</v>
+        <v>276</v>
       </c>
       <c r="G112" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A113" s="1" t="s">
         <v>277</v>
       </c>
-      <c r="B113" s="1" t="s">
+    </row>
+    <row r="113" spans="1:7" s="12" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A113" s="12" t="s">
+        <v>278</v>
+      </c>
+      <c r="B113" s="12" t="s">
+        <v>279</v>
+      </c>
+      <c r="C113" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="D113" s="13">
+        <v>1</v>
+      </c>
+      <c r="E113" s="12" t="s">
+        <v>280</v>
+      </c>
+      <c r="F113" s="12" t="s">
+        <v>281</v>
+      </c>
+      <c r="G113" s="12" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="114" spans="1:7" s="12" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A114" s="12" t="s">
+        <v>278</v>
+      </c>
+      <c r="C114" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="D114" s="13">
+        <v>2</v>
+      </c>
+      <c r="E114" s="12" t="s">
+        <v>283</v>
+      </c>
+      <c r="F114" s="12" t="s">
+        <v>284</v>
+      </c>
+      <c r="G114" s="12" t="s">
         <v>285</v>
-      </c>
-      <c r="C113" s="1" t="s">
-        <v>278</v>
-      </c>
-      <c r="D113" s="1">
-        <v>1</v>
-      </c>
-      <c r="E113" s="1" t="s">
-        <v>279</v>
-      </c>
-      <c r="F113" s="1" t="s">
-        <v>282</v>
-      </c>
-      <c r="G113" s="1" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A114" s="1" t="s">
-        <v>277</v>
-      </c>
-      <c r="C114" s="1" t="s">
-        <v>278</v>
-      </c>
-      <c r="D114" s="1">
-        <v>2</v>
-      </c>
-      <c r="E114" s="1" t="s">
-        <v>280</v>
-      </c>
-      <c r="F114" s="1" t="s">
-        <v>281</v>
-      </c>
-      <c r="G114" s="1" t="s">
-        <v>284</v>
       </c>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.3">
@@ -3491,19 +3476,19 @@
         <v>287</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>288</v>
+        <v>11</v>
       </c>
       <c r="D115" s="1">
         <v>1</v>
       </c>
       <c r="E115" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="F115" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="F115" s="1" t="s">
+      <c r="G115" s="1" t="s">
         <v>290</v>
-      </c>
-      <c r="G115" s="1" t="s">
-        <v>291</v>
       </c>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.3">
@@ -3511,19 +3496,19 @@
         <v>286</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>288</v>
+        <v>11</v>
       </c>
       <c r="D116" s="1">
         <v>2</v>
       </c>
       <c r="E116" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="F116" s="1" t="s">
         <v>292</v>
       </c>
-      <c r="F116" s="1" t="s">
+      <c r="G116" s="1" t="s">
         <v>293</v>
-      </c>
-      <c r="G116" s="1" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.3">
@@ -3531,23 +3516,89 @@
         <v>286</v>
       </c>
       <c r="C117" s="1" t="s">
-        <v>288</v>
+        <v>11</v>
       </c>
       <c r="D117" s="1">
         <v>3</v>
       </c>
       <c r="E117" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="F117" s="1" t="s">
         <v>295</v>
       </c>
-      <c r="F117" s="1" t="s">
+      <c r="G117" s="1" t="s">
         <v>296</v>
       </c>
-      <c r="G117" s="1" t="s">
+    </row>
+    <row r="118" spans="1:7" s="12" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A118" s="12" t="s">
         <v>297</v>
       </c>
+      <c r="B118" s="12" t="s">
+        <v>298</v>
+      </c>
+      <c r="C118" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="D118" s="13">
+        <v>1</v>
+      </c>
+      <c r="E118" s="12" t="s">
+        <v>299</v>
+      </c>
+      <c r="F118" s="12" t="s">
+        <v>300</v>
+      </c>
+      <c r="G118" s="12" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="119" spans="1:7" s="12" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A119" s="12" t="s">
+        <v>297</v>
+      </c>
+      <c r="C119" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="D119" s="13">
+        <v>2</v>
+      </c>
+      <c r="E119" s="12" t="s">
+        <v>302</v>
+      </c>
+      <c r="F119" s="12" t="s">
+        <v>303</v>
+      </c>
+      <c r="G119" s="12" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="120" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A120" t="s">
+        <v>305</v>
+      </c>
+      <c r="B120" t="s">
+        <v>306</v>
+      </c>
+      <c r="C120" t="s">
+        <v>41</v>
+      </c>
+      <c r="D120" s="4">
+        <v>1</v>
+      </c>
+      <c r="E120" t="s">
+        <v>307</v>
+      </c>
+      <c r="F120" t="s">
+        <v>308</v>
+      </c>
+      <c r="G120" t="s">
+        <v>309</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="E1:E112" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="E1:E112" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Development/Common/GameData/Enum/GameEnum.xlsx
+++ b/Development/Common/GameData/Enum/GameEnum.xlsx
@@ -1,29 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\project\MMOGameServerProject\Development\Common\GameData\Enum\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BFC1C08-27D8-4541-BC28-38A489CA0AB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC18D725-F76D-41B2-8425-6E31E1C15D04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="5355" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Enum" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Enum!$E$1:$E$112</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Enum!$E$1:$E$113</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="524" uniqueCount="310">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="528" uniqueCount="313">
   <si>
     <t>Enum 이름</t>
   </si>
@@ -957,18 +957,38 @@
   </si>
   <si>
     <t>상호작용 시 지정 스테이지/위치로 이동(무스크립트)</t>
+  </si>
+  <si>
+    <t>Character</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>캐릭터</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>NPC</t>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1076,46 +1096,49 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1398,7 +1421,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G120"/>
+  <dimension ref="A1:G121"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="22.75" style="1" customWidth="1"/>
@@ -1669,11 +1692,11 @@
       <c r="D15" s="7">
         <v>1</v>
       </c>
-      <c r="E15" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="F15" s="7" t="s">
-        <v>10</v>
+      <c r="E15" s="14" t="s">
+        <v>310</v>
+      </c>
+      <c r="F15" s="14" t="s">
+        <v>311</v>
       </c>
     </row>
     <row r="16" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.3">
@@ -1746,19 +1769,19 @@
     </row>
     <row r="20" spans="1:6" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A20" s="7" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="C20" s="7" t="s">
         <v>8</v>
       </c>
       <c r="D20" s="7">
-        <v>1</v>
-      </c>
-      <c r="E20" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="F20" s="7" t="s">
-        <v>49</v>
+        <v>6</v>
+      </c>
+      <c r="E20" s="14" t="s">
+        <v>312</v>
+      </c>
+      <c r="F20" s="14" t="s">
+        <v>312</v>
       </c>
     </row>
     <row r="21" spans="1:6" s="7" customFormat="1" x14ac:dyDescent="0.3">
@@ -1769,30 +1792,30 @@
         <v>8</v>
       </c>
       <c r="D21" s="7">
+        <v>1</v>
+      </c>
+      <c r="E21" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="F21" s="7" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D22" s="7">
         <v>2</v>
       </c>
-      <c r="E21" s="7" t="s">
+      <c r="E22" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="F21" s="7" t="s">
+      <c r="F22" s="7" t="s">
         <v>51</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="D22" s="4">
-        <v>1</v>
-      </c>
-      <c r="E22" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="F22" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="23" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.3">
@@ -1803,13 +1826,13 @@
         <v>53</v>
       </c>
       <c r="D23" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F23" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="24" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.3">
@@ -1820,13 +1843,13 @@
         <v>53</v>
       </c>
       <c r="D24" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F24" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="25" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.3">
@@ -1837,13 +1860,13 @@
         <v>53</v>
       </c>
       <c r="D25" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F25" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="26" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.3">
@@ -1854,30 +1877,30 @@
         <v>53</v>
       </c>
       <c r="D26" s="4">
+        <v>4</v>
+      </c>
+      <c r="E26" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="F26" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="D27" s="4">
         <v>5</v>
       </c>
-      <c r="E26" s="4" t="s">
+      <c r="E27" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="F26" t="s">
+      <c r="F27" t="s">
         <v>63</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="C27" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="D27" s="7">
-        <v>1</v>
-      </c>
-      <c r="E27" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="F27" s="7" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="28" spans="1:6" s="7" customFormat="1" x14ac:dyDescent="0.3">
@@ -1888,13 +1911,13 @@
         <v>53</v>
       </c>
       <c r="D28" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E28" s="7" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="F28" s="7" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="29" spans="1:6" s="7" customFormat="1" x14ac:dyDescent="0.3">
@@ -1905,13 +1928,13 @@
         <v>53</v>
       </c>
       <c r="D29" s="7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E29" s="7" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="F29" s="7" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="30" spans="1:6" s="7" customFormat="1" x14ac:dyDescent="0.3">
@@ -1922,13 +1945,13 @@
         <v>53</v>
       </c>
       <c r="D30" s="7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E30" s="7" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="F30" s="7" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="31" spans="1:6" s="7" customFormat="1" x14ac:dyDescent="0.3">
@@ -1939,13 +1962,13 @@
         <v>53</v>
       </c>
       <c r="D31" s="7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E31" s="7" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="F31" s="7" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="32" spans="1:6" s="7" customFormat="1" x14ac:dyDescent="0.3">
@@ -1956,13 +1979,13 @@
         <v>53</v>
       </c>
       <c r="D32" s="7">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E32" s="7" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F32" s="7" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="33" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.3">
@@ -1973,13 +1996,13 @@
         <v>53</v>
       </c>
       <c r="D33" s="7">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E33" s="7" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F33" s="7" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="34" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.3">
@@ -1990,13 +2013,13 @@
         <v>53</v>
       </c>
       <c r="D34" s="7">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E34" s="7" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="F34" s="7" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="35" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.3">
@@ -2007,30 +2030,30 @@
         <v>53</v>
       </c>
       <c r="D35" s="7">
+        <v>8</v>
+      </c>
+      <c r="E35" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="F35" s="7" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C36" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="D36" s="7">
         <v>9</v>
       </c>
-      <c r="E35" s="7" t="s">
+      <c r="E36" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="F35" s="7" t="s">
+      <c r="F36" s="7" t="s">
         <v>82</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="C36" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="D36" s="4">
-        <v>1</v>
-      </c>
-      <c r="E36" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="F36" s="4" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="37" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
@@ -2041,15 +2064,14 @@
         <v>53</v>
       </c>
       <c r="D37" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="G37" s="8"/>
+        <v>84</v>
+      </c>
     </row>
     <row r="38" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A38" s="4" t="s">
@@ -2059,14 +2081,15 @@
         <v>53</v>
       </c>
       <c r="D38" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>88</v>
-      </c>
+        <v>86</v>
+      </c>
+      <c r="G38" s="8"/>
     </row>
     <row r="39" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A39" s="4" t="s">
@@ -2076,13 +2099,13 @@
         <v>53</v>
       </c>
       <c r="D39" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="40" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
@@ -2093,13 +2116,13 @@
         <v>53</v>
       </c>
       <c r="D40" s="4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="41" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
@@ -2110,13 +2133,13 @@
         <v>53</v>
       </c>
       <c r="D41" s="4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="42" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
@@ -2127,15 +2150,14 @@
         <v>53</v>
       </c>
       <c r="D42" s="4">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="G42" s="8"/>
+        <v>94</v>
+      </c>
     </row>
     <row r="43" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A43" s="4" t="s">
@@ -2145,14 +2167,15 @@
         <v>53</v>
       </c>
       <c r="D43" s="4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>98</v>
-      </c>
+        <v>96</v>
+      </c>
+      <c r="G43" s="8"/>
     </row>
     <row r="44" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A44" s="4" t="s">
@@ -2162,13 +2185,13 @@
         <v>53</v>
       </c>
       <c r="D44" s="4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E44" s="4" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="45" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
@@ -2179,13 +2202,13 @@
         <v>53</v>
       </c>
       <c r="D45" s="4">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="46" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
@@ -2196,13 +2219,13 @@
         <v>53</v>
       </c>
       <c r="D46" s="4">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E46" s="4" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="47" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
@@ -2213,15 +2236,14 @@
         <v>53</v>
       </c>
       <c r="D47" s="4">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E47" s="4" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="G47" s="8"/>
+        <v>104</v>
+      </c>
     </row>
     <row r="48" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A48" s="4" t="s">
@@ -2231,14 +2253,15 @@
         <v>53</v>
       </c>
       <c r="D48" s="4">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>108</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="G48" s="8"/>
     </row>
     <row r="49" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A49" s="4" t="s">
@@ -2248,13 +2271,13 @@
         <v>53</v>
       </c>
       <c r="D49" s="4">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
     <row r="50" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
@@ -2265,13 +2288,13 @@
         <v>53</v>
       </c>
       <c r="D50" s="4">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E50" s="4" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="F50" s="4" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="51" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
@@ -2282,13 +2305,13 @@
         <v>53</v>
       </c>
       <c r="D51" s="4">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E51" s="4" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="52" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
@@ -2299,15 +2322,14 @@
         <v>53</v>
       </c>
       <c r="D52" s="4">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E52" s="4" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="G52" s="8"/>
+        <v>114</v>
+      </c>
     </row>
     <row r="53" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A53" s="4" t="s">
@@ -2317,14 +2339,15 @@
         <v>53</v>
       </c>
       <c r="D53" s="4">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E53" s="4" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>118</v>
-      </c>
+        <v>116</v>
+      </c>
+      <c r="G53" s="8"/>
     </row>
     <row r="54" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A54" s="4" t="s">
@@ -2334,13 +2357,13 @@
         <v>53</v>
       </c>
       <c r="D54" s="4">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E54" s="4" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="F54" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="55" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
@@ -2351,13 +2374,13 @@
         <v>53</v>
       </c>
       <c r="D55" s="4">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E55" s="4" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="56" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
@@ -2368,13 +2391,13 @@
         <v>53</v>
       </c>
       <c r="D56" s="4">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E56" s="4" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="F56" s="4" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="57" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
@@ -2385,15 +2408,14 @@
         <v>53</v>
       </c>
       <c r="D57" s="4">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E57" s="4" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="F57" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="G57" s="8"/>
+        <v>124</v>
+      </c>
     </row>
     <row r="58" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A58" s="4" t="s">
@@ -2403,14 +2425,15 @@
         <v>53</v>
       </c>
       <c r="D58" s="4">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E58" s="4" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="F58" s="4" t="s">
-        <v>128</v>
-      </c>
+        <v>126</v>
+      </c>
+      <c r="G58" s="8"/>
     </row>
     <row r="59" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A59" s="4" t="s">
@@ -2420,13 +2443,13 @@
         <v>53</v>
       </c>
       <c r="D59" s="4">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E59" s="4" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="F59" s="4" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="60" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
@@ -2437,13 +2460,13 @@
         <v>53</v>
       </c>
       <c r="D60" s="4">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E60" s="4" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="F60" s="4" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="61" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
@@ -2454,13 +2477,13 @@
         <v>53</v>
       </c>
       <c r="D61" s="4">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E61" s="4" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="F61" s="4" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="62" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
@@ -2471,15 +2494,14 @@
         <v>53</v>
       </c>
       <c r="D62" s="4">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E62" s="4" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="F62" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="G62" s="8"/>
+        <v>134</v>
+      </c>
     </row>
     <row r="63" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A63" s="4" t="s">
@@ -2489,14 +2511,15 @@
         <v>53</v>
       </c>
       <c r="D63" s="4">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E63" s="4" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="F63" s="4" t="s">
-        <v>138</v>
-      </c>
+        <v>136</v>
+      </c>
+      <c r="G63" s="8"/>
     </row>
     <row r="64" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A64" s="4" t="s">
@@ -2506,13 +2529,13 @@
         <v>53</v>
       </c>
       <c r="D64" s="4">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E64" s="4" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="F64" s="4" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="65" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
@@ -2523,13 +2546,13 @@
         <v>53</v>
       </c>
       <c r="D65" s="4">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E65" s="4" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="F65" s="4" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="66" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
@@ -2540,13 +2563,13 @@
         <v>53</v>
       </c>
       <c r="D66" s="4">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E66" s="4" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F66" s="4" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="67" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
@@ -2557,15 +2580,14 @@
         <v>53</v>
       </c>
       <c r="D67" s="4">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E67" s="4" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="F67" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="G67" s="8"/>
+        <v>144</v>
+      </c>
     </row>
     <row r="68" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A68" s="4" t="s">
@@ -2575,14 +2597,15 @@
         <v>53</v>
       </c>
       <c r="D68" s="4">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E68" s="4" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="F68" s="4" t="s">
-        <v>148</v>
-      </c>
+        <v>146</v>
+      </c>
+      <c r="G68" s="8"/>
     </row>
     <row r="69" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A69" s="4" t="s">
@@ -2592,13 +2615,13 @@
         <v>53</v>
       </c>
       <c r="D69" s="4">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E69" s="4" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="F69" s="4" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
     <row r="70" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
@@ -2609,13 +2632,13 @@
         <v>53</v>
       </c>
       <c r="D70" s="4">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E70" s="4" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="F70" s="4" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="71" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
@@ -2626,13 +2649,13 @@
         <v>53</v>
       </c>
       <c r="D71" s="4">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E71" s="4" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="F71" s="4" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="72" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
@@ -2643,15 +2666,14 @@
         <v>53</v>
       </c>
       <c r="D72" s="4">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E72" s="4" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="F72" s="4" t="s">
-        <v>156</v>
-      </c>
-      <c r="G72" s="8"/>
+        <v>154</v>
+      </c>
     </row>
     <row r="73" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A73" s="4" t="s">
@@ -2661,14 +2683,15 @@
         <v>53</v>
       </c>
       <c r="D73" s="4">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E73" s="4" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="F73" s="4" t="s">
-        <v>158</v>
-      </c>
+        <v>156</v>
+      </c>
+      <c r="G73" s="8"/>
     </row>
     <row r="74" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A74" s="4" t="s">
@@ -2678,13 +2701,13 @@
         <v>53</v>
       </c>
       <c r="D74" s="4">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E74" s="4" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="F74" s="4" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="75" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
@@ -2695,13 +2718,13 @@
         <v>53</v>
       </c>
       <c r="D75" s="4">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E75" s="4" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="F75" s="4" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
     <row r="76" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
@@ -2712,13 +2735,13 @@
         <v>53</v>
       </c>
       <c r="D76" s="4">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E76" s="4" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="F76" s="4" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="77" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
@@ -2729,15 +2752,14 @@
         <v>53</v>
       </c>
       <c r="D77" s="4">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E77" s="4" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="F77" s="4" t="s">
-        <v>166</v>
-      </c>
-      <c r="G77" s="8"/>
+        <v>164</v>
+      </c>
     </row>
     <row r="78" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A78" s="4" t="s">
@@ -2747,14 +2769,15 @@
         <v>53</v>
       </c>
       <c r="D78" s="4">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E78" s="4" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="F78" s="4" t="s">
-        <v>168</v>
-      </c>
+        <v>166</v>
+      </c>
+      <c r="G78" s="8"/>
     </row>
     <row r="79" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A79" s="4" t="s">
@@ -2764,13 +2787,13 @@
         <v>53</v>
       </c>
       <c r="D79" s="4">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E79" s="4" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="F79" s="4" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
     </row>
     <row r="80" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
@@ -2781,33 +2804,30 @@
         <v>53</v>
       </c>
       <c r="D80" s="4">
+        <v>44</v>
+      </c>
+      <c r="E80" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="F80" s="4" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A81" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="C81" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="D81" s="4">
         <v>45</v>
       </c>
-      <c r="E80" s="4" t="s">
+      <c r="E81" s="4" t="s">
         <v>171</v>
       </c>
-      <c r="F80" s="4" t="s">
+      <c r="F81" s="4" t="s">
         <v>172</v>
-      </c>
-    </row>
-    <row r="81" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A81" s="7" t="s">
-        <v>173</v>
-      </c>
-      <c r="C81" s="7" t="s">
-        <v>174</v>
-      </c>
-      <c r="D81" s="7">
-        <v>1</v>
-      </c>
-      <c r="E81" s="5" t="s">
-        <v>175</v>
-      </c>
-      <c r="F81" s="5" t="s">
-        <v>176</v>
-      </c>
-      <c r="G81" s="7" t="s">
-        <v>177</v>
       </c>
     </row>
     <row r="82" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.3">
@@ -2818,16 +2838,16 @@
         <v>174</v>
       </c>
       <c r="D82" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E82" s="5" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="F82" s="5" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="G82" s="7" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
     </row>
     <row r="83" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.3">
@@ -2838,53 +2858,56 @@
         <v>174</v>
       </c>
       <c r="D83" s="7">
+        <v>2</v>
+      </c>
+      <c r="E83" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="F83" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="G83" s="7" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A84" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="C84" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="D84" s="7">
         <v>3</v>
       </c>
-      <c r="E83" s="5" t="s">
+      <c r="E84" s="5" t="s">
         <v>181</v>
       </c>
-      <c r="F83" s="5" t="s">
+      <c r="F84" s="5" t="s">
         <v>182</v>
       </c>
-      <c r="G83" s="7" t="s">
+      <c r="G84" s="7" t="s">
         <v>183</v>
-      </c>
-    </row>
-    <row r="84" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A84" t="s">
-        <v>184</v>
-      </c>
-      <c r="B84" s="4" t="s">
-        <v>185</v>
-      </c>
-      <c r="C84" s="4" t="s">
-        <v>174</v>
-      </c>
-      <c r="D84" s="4">
-        <v>1</v>
-      </c>
-      <c r="E84" t="s">
-        <v>186</v>
-      </c>
-      <c r="F84" t="s">
-        <v>187</v>
       </c>
     </row>
     <row r="85" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>184</v>
       </c>
+      <c r="B85" s="4" t="s">
+        <v>185</v>
+      </c>
       <c r="C85" s="4" t="s">
         <v>174</v>
       </c>
       <c r="D85" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E85" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="F85" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="86" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
@@ -2895,13 +2918,13 @@
         <v>174</v>
       </c>
       <c r="D86" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E86" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="F86" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="87" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
@@ -2912,51 +2935,50 @@
         <v>174</v>
       </c>
       <c r="D87" s="4">
+        <v>3</v>
+      </c>
+      <c r="E87" t="s">
+        <v>190</v>
+      </c>
+      <c r="F87" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A88" t="s">
+        <v>184</v>
+      </c>
+      <c r="C88" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="D88" s="4">
         <v>4</v>
       </c>
-      <c r="E87" t="s">
+      <c r="E88" t="s">
         <v>192</v>
       </c>
-      <c r="F87" t="s">
+      <c r="F88" t="s">
         <v>193</v>
-      </c>
-    </row>
-    <row r="88" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A88" s="5" t="s">
-        <v>194</v>
-      </c>
-      <c r="B88" s="7" t="s">
-        <v>195</v>
-      </c>
-      <c r="C88" s="7" t="s">
-        <v>174</v>
-      </c>
-      <c r="D88" s="7">
-        <v>1</v>
-      </c>
-      <c r="E88" s="5" t="s">
-        <v>196</v>
-      </c>
-      <c r="F88" s="5" t="s">
-        <v>197</v>
       </c>
     </row>
     <row r="89" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A89" s="5" t="s">
         <v>194</v>
       </c>
-      <c r="B89" s="5"/>
+      <c r="B89" s="7" t="s">
+        <v>195</v>
+      </c>
       <c r="C89" s="7" t="s">
         <v>174</v>
       </c>
       <c r="D89" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E89" s="5" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="F89" s="5" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
     </row>
     <row r="90" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.3">
@@ -2968,223 +2990,223 @@
         <v>174</v>
       </c>
       <c r="D90" s="7">
+        <v>2</v>
+      </c>
+      <c r="E90" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="F90" s="5" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A91" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="B91" s="5"/>
+      <c r="C91" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="D91" s="7">
         <v>3</v>
       </c>
-      <c r="E90" s="5" t="s">
+      <c r="E91" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="F90" s="5" t="s">
+      <c r="F91" s="5" t="s">
         <v>201</v>
-      </c>
-    </row>
-    <row r="91" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A91" t="s">
-        <v>202</v>
-      </c>
-      <c r="B91" t="s">
-        <v>203</v>
-      </c>
-      <c r="C91" s="4" t="s">
-        <v>174</v>
-      </c>
-      <c r="D91" s="4">
-        <v>1</v>
-      </c>
-      <c r="E91" t="s">
-        <v>204</v>
-      </c>
-      <c r="F91" t="s">
-        <v>205</v>
-      </c>
-      <c r="G91" s="4" t="s">
-        <v>206</v>
       </c>
     </row>
     <row r="92" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>202</v>
       </c>
+      <c r="B92" t="s">
+        <v>203</v>
+      </c>
       <c r="C92" s="4" t="s">
         <v>174</v>
       </c>
       <c r="D92" s="4">
+        <v>1</v>
+      </c>
+      <c r="E92" t="s">
+        <v>204</v>
+      </c>
+      <c r="F92" t="s">
+        <v>205</v>
+      </c>
+      <c r="G92" s="4" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A93" t="s">
+        <v>202</v>
+      </c>
+      <c r="C93" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="D93" s="4">
         <v>2</v>
       </c>
-      <c r="E92" t="s">
+      <c r="E93" t="s">
         <v>207</v>
       </c>
-      <c r="F92" t="s">
+      <c r="F93" t="s">
         <v>208</v>
       </c>
-      <c r="G92" s="4" t="s">
+      <c r="G93" s="4" t="s">
         <v>209</v>
-      </c>
-    </row>
-    <row r="93" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A93" s="5" t="s">
-        <v>210</v>
-      </c>
-      <c r="B93" s="7" t="s">
-        <v>211</v>
-      </c>
-      <c r="C93" s="7" t="s">
-        <v>174</v>
-      </c>
-      <c r="D93" s="7">
-        <v>1</v>
-      </c>
-      <c r="E93" s="5" t="s">
-        <v>212</v>
-      </c>
-      <c r="F93" s="5" t="s">
-        <v>213</v>
-      </c>
-      <c r="G93" s="7" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="94" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A94" s="5" t="s">
         <v>210</v>
       </c>
-      <c r="B94" s="5"/>
+      <c r="B94" s="7" t="s">
+        <v>211</v>
+      </c>
       <c r="C94" s="7" t="s">
         <v>174</v>
       </c>
       <c r="D94" s="7">
+        <v>1</v>
+      </c>
+      <c r="E94" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="F94" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="G94" s="7" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A95" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="B95" s="5"/>
+      <c r="C95" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="D95" s="7">
         <v>2</v>
       </c>
-      <c r="E94" s="5" t="s">
+      <c r="E95" s="5" t="s">
         <v>215</v>
       </c>
-      <c r="F94" s="5" t="s">
+      <c r="F95" s="5" t="s">
         <v>216</v>
       </c>
-      <c r="G94" s="7" t="s">
+      <c r="G95" s="7" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="95" spans="1:7" s="4" customFormat="1" ht="141.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A95" s="9" t="s">
-        <v>218</v>
-      </c>
-      <c r="B95" s="10" t="s">
-        <v>219</v>
-      </c>
-      <c r="C95" s="4" t="s">
-        <v>174</v>
-      </c>
-      <c r="D95" s="4">
-        <v>1</v>
-      </c>
-      <c r="E95" t="s">
-        <v>220</v>
-      </c>
-      <c r="F95" t="s">
-        <v>221</v>
-      </c>
-      <c r="G95" s="4" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="96" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:7" s="4" customFormat="1" ht="141.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A96" s="9" t="s">
         <v>218</v>
       </c>
-      <c r="B96" s="9"/>
+      <c r="B96" s="10" t="s">
+        <v>219</v>
+      </c>
       <c r="C96" s="4" t="s">
         <v>174</v>
       </c>
       <c r="D96" s="4">
+        <v>1</v>
+      </c>
+      <c r="E96" t="s">
+        <v>220</v>
+      </c>
+      <c r="F96" t="s">
+        <v>221</v>
+      </c>
+      <c r="G96" s="4" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A97" s="9" t="s">
+        <v>218</v>
+      </c>
+      <c r="B97" s="9"/>
+      <c r="C97" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="D97" s="4">
         <v>2</v>
       </c>
-      <c r="E96" t="s">
+      <c r="E97" t="s">
         <v>223</v>
       </c>
-      <c r="F96" t="s">
+      <c r="F97" t="s">
         <v>224</v>
       </c>
-      <c r="G96" s="4" t="s">
+      <c r="G97" s="4" t="s">
         <v>225</v>
-      </c>
-    </row>
-    <row r="97" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A97" s="5" t="s">
-        <v>226</v>
-      </c>
-      <c r="B97" s="7" t="s">
-        <v>227</v>
-      </c>
-      <c r="C97" s="7" t="s">
-        <v>174</v>
-      </c>
-      <c r="D97" s="7">
-        <v>1</v>
-      </c>
-      <c r="E97" s="5" t="s">
-        <v>228</v>
-      </c>
-      <c r="F97" s="5" t="s">
-        <v>229</v>
       </c>
     </row>
     <row r="98" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A98" s="5" t="s">
         <v>226</v>
       </c>
-      <c r="B98" s="5"/>
+      <c r="B98" s="7" t="s">
+        <v>227</v>
+      </c>
       <c r="C98" s="7" t="s">
         <v>174</v>
       </c>
       <c r="D98" s="7">
+        <v>1</v>
+      </c>
+      <c r="E98" s="5" t="s">
+        <v>228</v>
+      </c>
+      <c r="F98" s="5" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A99" s="5" t="s">
+        <v>226</v>
+      </c>
+      <c r="B99" s="5"/>
+      <c r="C99" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="D99" s="7">
         <v>2</v>
       </c>
-      <c r="E98" s="5" t="s">
+      <c r="E99" s="5" t="s">
         <v>230</v>
       </c>
-      <c r="F98" s="5" t="s">
+      <c r="F99" s="5" t="s">
         <v>231</v>
-      </c>
-    </row>
-    <row r="99" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A99" s="9" t="s">
-        <v>232</v>
-      </c>
-      <c r="B99" s="4" t="s">
-        <v>233</v>
-      </c>
-      <c r="C99" s="4" t="s">
-        <v>174</v>
-      </c>
-      <c r="D99" s="4">
-        <v>1</v>
-      </c>
-      <c r="E99" t="s">
-        <v>234</v>
-      </c>
-      <c r="F99" s="4" t="s">
-        <v>235</v>
-      </c>
-      <c r="G99" s="4" t="s">
-        <v>236</v>
       </c>
     </row>
     <row r="100" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A100" s="9" t="s">
         <v>232</v>
       </c>
-      <c r="B100" s="9"/>
+      <c r="B100" s="4" t="s">
+        <v>233</v>
+      </c>
       <c r="C100" s="4" t="s">
         <v>174</v>
       </c>
       <c r="D100" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E100" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="F100" s="4" t="s">
-        <v>238</v>
+        <v>235</v>
+      </c>
+      <c r="G100" s="4" t="s">
+        <v>236</v>
       </c>
     </row>
     <row r="101" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
@@ -3196,30 +3218,31 @@
         <v>174</v>
       </c>
       <c r="D101" s="4">
+        <v>2</v>
+      </c>
+      <c r="E101" t="s">
+        <v>237</v>
+      </c>
+      <c r="F101" s="4" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A102" s="9" t="s">
+        <v>232</v>
+      </c>
+      <c r="B102" s="9"/>
+      <c r="C102" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="D102" s="4">
         <v>3</v>
       </c>
-      <c r="E101" t="s">
+      <c r="E102" t="s">
         <v>239</v>
       </c>
-      <c r="F101" s="4" t="s">
+      <c r="F102" s="4" t="s">
         <v>240</v>
-      </c>
-    </row>
-    <row r="102" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A102" s="7" t="s">
-        <v>241</v>
-      </c>
-      <c r="C102" s="7" t="s">
-        <v>242</v>
-      </c>
-      <c r="D102" s="7">
-        <v>1</v>
-      </c>
-      <c r="E102" s="7" t="s">
-        <v>242</v>
-      </c>
-      <c r="F102" s="7" t="s">
-        <v>243</v>
       </c>
     </row>
     <row r="103" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.3">
@@ -3230,36 +3253,33 @@
         <v>242</v>
       </c>
       <c r="D103" s="7">
+        <v>1</v>
+      </c>
+      <c r="E103" s="7" t="s">
+        <v>242</v>
+      </c>
+      <c r="F103" s="7" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="104" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A104" s="7" t="s">
+        <v>241</v>
+      </c>
+      <c r="C104" s="7" t="s">
+        <v>242</v>
+      </c>
+      <c r="D104" s="7">
         <v>2</v>
       </c>
-      <c r="E103" s="7" t="s">
+      <c r="E104" s="7" t="s">
         <v>244</v>
       </c>
-      <c r="F103" s="7" t="s">
+      <c r="F104" s="7" t="s">
         <v>245</v>
       </c>
-      <c r="G103" s="7" t="s">
+      <c r="G104" s="7" t="s">
         <v>246</v>
-      </c>
-    </row>
-    <row r="104" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A104" s="4" t="s">
-        <v>247</v>
-      </c>
-      <c r="C104" s="4" t="s">
-        <v>242</v>
-      </c>
-      <c r="D104" s="4">
-        <v>1</v>
-      </c>
-      <c r="E104" s="4" t="s">
-        <v>248</v>
-      </c>
-      <c r="F104" s="4" t="s">
-        <v>249</v>
-      </c>
-      <c r="G104" s="4" t="s">
-        <v>250</v>
       </c>
     </row>
     <row r="105" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
@@ -3270,16 +3290,16 @@
         <v>242</v>
       </c>
       <c r="D105" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E105" s="4" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="F105" s="4" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="G105" s="4" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
     </row>
     <row r="106" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
@@ -3290,79 +3310,79 @@
         <v>242</v>
       </c>
       <c r="D106" s="4">
+        <v>2</v>
+      </c>
+      <c r="E106" s="4" t="s">
+        <v>251</v>
+      </c>
+      <c r="F106" s="4" t="s">
+        <v>252</v>
+      </c>
+      <c r="G106" s="4" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A107" s="4" t="s">
+        <v>247</v>
+      </c>
+      <c r="C107" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="D107" s="4">
         <v>3</v>
       </c>
-      <c r="E106" s="4" t="s">
+      <c r="E107" s="4" t="s">
         <v>254</v>
       </c>
-      <c r="F106" s="4" t="s">
+      <c r="F107" s="4" t="s">
         <v>255</v>
       </c>
-      <c r="G106" s="4" t="s">
+      <c r="G107" s="4" t="s">
         <v>256</v>
-      </c>
-    </row>
-    <row r="107" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A107" s="7" t="s">
-        <v>257</v>
-      </c>
-      <c r="B107" s="7" t="s">
-        <v>258</v>
-      </c>
-      <c r="C107" s="7" t="s">
-        <v>242</v>
-      </c>
-      <c r="D107" s="7">
-        <v>1</v>
-      </c>
-      <c r="E107" s="7" t="s">
-        <v>259</v>
-      </c>
-      <c r="F107" s="7" t="s">
-        <v>260</v>
-      </c>
-      <c r="G107" s="7" t="s">
-        <v>261</v>
       </c>
     </row>
     <row r="108" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A108" s="7" t="s">
         <v>257</v>
       </c>
+      <c r="B108" s="7" t="s">
+        <v>258</v>
+      </c>
       <c r="C108" s="7" t="s">
         <v>242</v>
       </c>
       <c r="D108" s="7">
+        <v>1</v>
+      </c>
+      <c r="E108" s="7" t="s">
+        <v>259</v>
+      </c>
+      <c r="F108" s="7" t="s">
+        <v>260</v>
+      </c>
+      <c r="G108" s="7" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="109" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A109" s="7" t="s">
+        <v>257</v>
+      </c>
+      <c r="C109" s="7" t="s">
+        <v>242</v>
+      </c>
+      <c r="D109" s="7">
         <v>2</v>
       </c>
-      <c r="E108" s="7" t="s">
+      <c r="E109" s="7" t="s">
         <v>262</v>
       </c>
-      <c r="F108" s="7" t="s">
+      <c r="F109" s="7" t="s">
         <v>263</v>
       </c>
-      <c r="G108" s="7" t="s">
+      <c r="G109" s="7" t="s">
         <v>264</v>
-      </c>
-    </row>
-    <row r="109" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A109" t="s">
-        <v>265</v>
-      </c>
-      <c r="C109" t="s">
-        <v>30</v>
-      </c>
-      <c r="D109" s="4">
-        <v>1</v>
-      </c>
-      <c r="E109" t="s">
-        <v>266</v>
-      </c>
-      <c r="F109" t="s">
-        <v>267</v>
-      </c>
-      <c r="G109" t="s">
-        <v>268</v>
       </c>
     </row>
     <row r="110" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
@@ -3373,16 +3393,16 @@
         <v>30</v>
       </c>
       <c r="D110" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E110" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="F110" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="G110" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
     </row>
     <row r="111" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
@@ -3393,16 +3413,16 @@
         <v>30</v>
       </c>
       <c r="D111" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E111" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="F111" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="G111" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
     </row>
     <row r="112" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
@@ -3413,102 +3433,102 @@
         <v>30</v>
       </c>
       <c r="D112" s="4">
+        <v>3</v>
+      </c>
+      <c r="E112" t="s">
+        <v>272</v>
+      </c>
+      <c r="F112" t="s">
+        <v>273</v>
+      </c>
+      <c r="G112" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="113" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A113" t="s">
+        <v>265</v>
+      </c>
+      <c r="C113" t="s">
+        <v>30</v>
+      </c>
+      <c r="D113" s="4">
         <v>4</v>
       </c>
-      <c r="E112" t="s">
+      <c r="E113" t="s">
         <v>275</v>
       </c>
-      <c r="F112" t="s">
+      <c r="F113" t="s">
         <v>276</v>
       </c>
-      <c r="G112" t="s">
+      <c r="G113" t="s">
         <v>277</v>
-      </c>
-    </row>
-    <row r="113" spans="1:7" s="12" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A113" s="12" t="s">
-        <v>278</v>
-      </c>
-      <c r="B113" s="12" t="s">
-        <v>279</v>
-      </c>
-      <c r="C113" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="D113" s="13">
-        <v>1</v>
-      </c>
-      <c r="E113" s="12" t="s">
-        <v>280</v>
-      </c>
-      <c r="F113" s="12" t="s">
-        <v>281</v>
-      </c>
-      <c r="G113" s="12" t="s">
-        <v>282</v>
       </c>
     </row>
     <row r="114" spans="1:7" s="12" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A114" s="12" t="s">
         <v>278</v>
       </c>
+      <c r="B114" s="12" t="s">
+        <v>279</v>
+      </c>
       <c r="C114" s="12" t="s">
         <v>11</v>
       </c>
       <c r="D114" s="13">
+        <v>1</v>
+      </c>
+      <c r="E114" s="12" t="s">
+        <v>280</v>
+      </c>
+      <c r="F114" s="12" t="s">
+        <v>281</v>
+      </c>
+      <c r="G114" s="12" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="115" spans="1:7" s="12" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A115" s="12" t="s">
+        <v>278</v>
+      </c>
+      <c r="C115" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="D115" s="13">
         <v>2</v>
       </c>
-      <c r="E114" s="12" t="s">
+      <c r="E115" s="12" t="s">
         <v>283</v>
       </c>
-      <c r="F114" s="12" t="s">
+      <c r="F115" s="12" t="s">
         <v>284</v>
       </c>
-      <c r="G114" s="12" t="s">
+      <c r="G115" s="12" t="s">
         <v>285</v>
-      </c>
-    </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A115" s="1" t="s">
-        <v>286</v>
-      </c>
-      <c r="B115" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="C115" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D115" s="1">
-        <v>1</v>
-      </c>
-      <c r="E115" s="1" t="s">
-        <v>288</v>
-      </c>
-      <c r="F115" s="1" t="s">
-        <v>289</v>
-      </c>
-      <c r="G115" s="1" t="s">
-        <v>290</v>
       </c>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A116" s="1" t="s">
         <v>286</v>
       </c>
+      <c r="B116" s="1" t="s">
+        <v>287</v>
+      </c>
       <c r="C116" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D116" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="F116" s="1" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="G116" s="1" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.3">
@@ -3519,87 +3539,107 @@
         <v>11</v>
       </c>
       <c r="D117" s="1">
+        <v>2</v>
+      </c>
+      <c r="E117" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="F117" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="G117" s="1" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="118" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A118" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="C118" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D118" s="1">
         <v>3</v>
       </c>
-      <c r="E117" s="1" t="s">
+      <c r="E118" s="1" t="s">
         <v>294</v>
       </c>
-      <c r="F117" s="1" t="s">
+      <c r="F118" s="1" t="s">
         <v>295</v>
       </c>
-      <c r="G117" s="1" t="s">
+      <c r="G118" s="1" t="s">
         <v>296</v>
-      </c>
-    </row>
-    <row r="118" spans="1:7" s="12" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A118" s="12" t="s">
-        <v>297</v>
-      </c>
-      <c r="B118" s="12" t="s">
-        <v>298</v>
-      </c>
-      <c r="C118" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="D118" s="13">
-        <v>1</v>
-      </c>
-      <c r="E118" s="12" t="s">
-        <v>299</v>
-      </c>
-      <c r="F118" s="12" t="s">
-        <v>300</v>
-      </c>
-      <c r="G118" s="12" t="s">
-        <v>301</v>
       </c>
     </row>
     <row r="119" spans="1:7" s="12" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A119" s="12" t="s">
         <v>297</v>
       </c>
+      <c r="B119" s="12" t="s">
+        <v>298</v>
+      </c>
       <c r="C119" s="12" t="s">
         <v>41</v>
       </c>
       <c r="D119" s="13">
+        <v>1</v>
+      </c>
+      <c r="E119" s="12" t="s">
+        <v>299</v>
+      </c>
+      <c r="F119" s="12" t="s">
+        <v>300</v>
+      </c>
+      <c r="G119" s="12" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="120" spans="1:7" s="12" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A120" s="12" t="s">
+        <v>297</v>
+      </c>
+      <c r="C120" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="D120" s="13">
         <v>2</v>
       </c>
-      <c r="E119" s="12" t="s">
+      <c r="E120" s="12" t="s">
         <v>302</v>
       </c>
-      <c r="F119" s="12" t="s">
+      <c r="F120" s="12" t="s">
         <v>303</v>
       </c>
-      <c r="G119" s="12" t="s">
+      <c r="G120" s="12" t="s">
         <v>304</v>
       </c>
     </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A120" t="s">
+    <row r="121" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A121" t="s">
         <v>305</v>
       </c>
-      <c r="B120" t="s">
+      <c r="B121" t="s">
         <v>306</v>
       </c>
-      <c r="C120" t="s">
+      <c r="C121" t="s">
         <v>41</v>
       </c>
-      <c r="D120" s="4">
+      <c r="D121" s="4">
         <v>1</v>
       </c>
-      <c r="E120" t="s">
+      <c r="E121" t="s">
         <v>307</v>
       </c>
-      <c r="F120" t="s">
+      <c r="F121" t="s">
         <v>308</v>
       </c>
-      <c r="G120" t="s">
+      <c r="G121" t="s">
         <v>309</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="E1:E112" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
-  <phoneticPr fontId="3" type="noConversion"/>
+  <autoFilter ref="E1:E113" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Development/Common/GameData/Enum/GameEnum.xlsx
+++ b/Development/Common/GameData/Enum/GameEnum.xlsx
@@ -8,22 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\project\MMOGameServerProject\Development\Common\GameData\Enum\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC18D725-F76D-41B2-8425-6E31E1C15D04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A14C8A1-DA15-4890-A3EB-ADF4DA7C4068}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Enum" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Enum!$E$1:$E$113</definedName>
-  </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="528" uniqueCount="313">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="530" uniqueCount="315">
   <si>
     <t>Enum 이름</t>
   </si>
@@ -150,6 +147,12 @@
     <t>ObjectType</t>
   </si>
   <si>
+    <t>Character</t>
+  </si>
+  <si>
+    <t>캐릭터</t>
+  </si>
+  <si>
     <t>Prop</t>
   </si>
   <si>
@@ -166,6 +169,9 @@
   </si>
   <si>
     <t>이벤트영역</t>
+  </si>
+  <si>
+    <t>NPC</t>
   </si>
   <si>
     <t>ResultCode</t>
@@ -728,247 +734,242 @@
     <t>SkillPlacement</t>
   </si>
   <si>
-    <t>스킬 효과의 위치를 어디에 둘지 정한다.</t>
-  </si>
-  <si>
     <t>Caster</t>
   </si>
   <si>
-    <t>캐스터 위치</t>
-  </si>
-  <si>
-    <t>투사체 발사점 / 캐스터 중심 범위</t>
+    <t>BuffCategory</t>
+  </si>
+  <si>
+    <t>Buff</t>
+  </si>
+  <si>
+    <t>이로운효과</t>
+  </si>
+  <si>
+    <t>Debuff</t>
+  </si>
+  <si>
+    <t>해로운효과</t>
+  </si>
+  <si>
+    <t>디스펠 대상</t>
+  </si>
+  <si>
+    <t>BuffStackPolicy</t>
+  </si>
+  <si>
+    <t>Refresh</t>
+  </si>
+  <si>
+    <t>시간갱신</t>
+  </si>
+  <si>
+    <t>재적용 시 지속시간만 리셋</t>
+  </si>
+  <si>
+    <t>Stack</t>
+  </si>
+  <si>
+    <t>스택증가</t>
+  </si>
+  <si>
+    <t>재적용 시 스택+1 (MaxStack까지)</t>
+  </si>
+  <si>
+    <t>Ignore</t>
+  </si>
+  <si>
+    <t>무시</t>
+  </si>
+  <si>
+    <t>이미 있으면 무시</t>
+  </si>
+  <si>
+    <t>PeriodicEffect</t>
+  </si>
+  <si>
+    <t>버프의 주기적 효과</t>
+  </si>
+  <si>
+    <t>DamageHp</t>
+  </si>
+  <si>
+    <t>HP감소</t>
+  </si>
+  <si>
+    <t>DoT</t>
+  </si>
+  <si>
+    <t>HealHp</t>
+  </si>
+  <si>
+    <t>HP회복</t>
+  </si>
+  <si>
+    <t>HoT</t>
+  </si>
+  <si>
+    <t>StagePositionType</t>
+  </si>
+  <si>
+    <t>Default</t>
+  </si>
+  <si>
+    <t>기본 시작위치</t>
+  </si>
+  <si>
+    <t>캐릭터 선택 입장 등 기본 도착 위치</t>
+  </si>
+  <si>
+    <t>Path1</t>
+  </si>
+  <si>
+    <t>경로1</t>
+  </si>
+  <si>
+    <t>외부에서 들어오는 첫번째 위치</t>
+  </si>
+  <si>
+    <t>Path2</t>
+  </si>
+  <si>
+    <t>경로2</t>
+  </si>
+  <si>
+    <t>외부에서 들어오는 두번째 위치</t>
+  </si>
+  <si>
+    <t>Path3</t>
+  </si>
+  <si>
+    <t>경로3</t>
+  </si>
+  <si>
+    <t>외부에서 들어오는 세번째 위치</t>
+  </si>
+  <si>
+    <t>MonsterAIType</t>
+  </si>
+  <si>
+    <t>몬스터 AI 종류</t>
+  </si>
+  <si>
+    <t>FSM</t>
+  </si>
+  <si>
+    <t>유한상태기계</t>
+  </si>
+  <si>
+    <t>일반몬스터용</t>
+  </si>
+  <si>
+    <t>BehaviourTree</t>
+  </si>
+  <si>
+    <t>행동 트리</t>
+  </si>
+  <si>
+    <t>엘리트 몬스터, 보스용</t>
+  </si>
+  <si>
+    <t>SpawnActivation</t>
+  </si>
+  <si>
+    <t>스폰 활성화 모드</t>
+  </si>
+  <si>
+    <t>Always</t>
+  </si>
+  <si>
+    <t>항상</t>
+  </si>
+  <si>
+    <t>항상 밀도 유지</t>
+  </si>
+  <si>
+    <t>PlayerProximity</t>
+  </si>
+  <si>
+    <t>근접 활성</t>
+  </si>
+  <si>
+    <t>플레이어 근접 시만</t>
+  </si>
+  <si>
+    <t>Manual</t>
+  </si>
+  <si>
+    <t>수동</t>
+  </si>
+  <si>
+    <t>Stage 스크립트에서 ActivateSpawner 등으로 활성화시킴</t>
+  </si>
+  <si>
+    <t>PropStateMode</t>
+  </si>
+  <si>
+    <t>prop 상태머신 모드</t>
+  </si>
+  <si>
+    <t>Toggle</t>
+  </si>
+  <si>
+    <t>토글</t>
+  </si>
+  <si>
+    <t>상호작용마다 상태 순환(StateCount 만큼)</t>
+  </si>
+  <si>
+    <t>OneShot</t>
+  </si>
+  <si>
+    <t>일회성</t>
+  </si>
+  <si>
+    <t>0→1 1회 전이 후 더 이상 상태변화 없음</t>
+  </si>
+  <si>
+    <t>PropBehavior</t>
+  </si>
+  <si>
+    <t>prop 선언형 동작</t>
+  </si>
+  <si>
+    <t>Portal</t>
+  </si>
+  <si>
+    <t>포탈</t>
+  </si>
+  <si>
+    <t>상호작용 시 지정 스테이지/위치로 이동(무스크립트)</t>
+  </si>
+  <si>
+    <t>스킬 효과 중심의 기준점을 정한다.</t>
+  </si>
+  <si>
+    <t>캐스터 중심</t>
+  </si>
+  <si>
+    <t>시전자 루트/중심을 효과 중심 기준점으로 사용</t>
+  </si>
+  <si>
+    <t>SkillCastOrigin</t>
+  </si>
+  <si>
+    <t>스킬 시전 앵커</t>
   </si>
   <si>
     <t>Target</t>
   </si>
   <si>
-    <t>타겟 위치에 OBB/Circle 생성</t>
-  </si>
-  <si>
-    <t>Forward</t>
-  </si>
-  <si>
-    <t>캐스터 전방에서 시작해 타겟 방향으로 OBB</t>
-  </si>
-  <si>
-    <t>BuffCategory</t>
-  </si>
-  <si>
-    <t>Buff</t>
-  </si>
-  <si>
-    <t>이로운효과</t>
-  </si>
-  <si>
-    <t>Debuff</t>
-  </si>
-  <si>
-    <t>해로운효과</t>
-  </si>
-  <si>
-    <t>디스펠 대상</t>
-  </si>
-  <si>
-    <t>BuffStackPolicy</t>
-  </si>
-  <si>
-    <t>Refresh</t>
-  </si>
-  <si>
-    <t>시간갱신</t>
-  </si>
-  <si>
-    <t>재적용 시 지속시간만 리셋</t>
-  </si>
-  <si>
-    <t>Stack</t>
-  </si>
-  <si>
-    <t>스택증가</t>
-  </si>
-  <si>
-    <t>재적용 시 스택+1 (MaxStack까지)</t>
-  </si>
-  <si>
-    <t>Ignore</t>
-  </si>
-  <si>
-    <t>무시</t>
-  </si>
-  <si>
-    <t>이미 있으면 무시</t>
-  </si>
-  <si>
-    <t>PeriodicEffect</t>
-  </si>
-  <si>
-    <t>버프의 주기적 효과</t>
-  </si>
-  <si>
-    <t>DamageHp</t>
-  </si>
-  <si>
-    <t>HP감소</t>
-  </si>
-  <si>
-    <t>DoT</t>
-  </si>
-  <si>
-    <t>HealHp</t>
-  </si>
-  <si>
-    <t>HP회복</t>
-  </si>
-  <si>
-    <t>HoT</t>
-  </si>
-  <si>
-    <t>StagePositionType</t>
-  </si>
-  <si>
-    <t>Default</t>
-  </si>
-  <si>
-    <t>기본 시작위치</t>
-  </si>
-  <si>
-    <t>캐릭터 선택 입장 등 기본 도착 위치</t>
-  </si>
-  <si>
-    <t>Path1</t>
-  </si>
-  <si>
-    <t>경로1</t>
-  </si>
-  <si>
-    <t>외부에서 들어오는 첫번째 위치</t>
-  </si>
-  <si>
-    <t>Path2</t>
-  </si>
-  <si>
-    <t>경로2</t>
-  </si>
-  <si>
-    <t>외부에서 들어오는 두번째 위치</t>
-  </si>
-  <si>
-    <t>Path3</t>
-  </si>
-  <si>
-    <t>경로3</t>
-  </si>
-  <si>
-    <t>외부에서 들어오는 세번째 위치</t>
-  </si>
-  <si>
-    <t>MonsterAIType</t>
-  </si>
-  <si>
-    <t>몬스터 AI 종류</t>
-  </si>
-  <si>
-    <t>FSM</t>
-  </si>
-  <si>
-    <t>유한상태기계</t>
-  </si>
-  <si>
-    <t>일반몬스터용</t>
-  </si>
-  <si>
-    <t>BehaviourTree</t>
-  </si>
-  <si>
-    <t>행동 트리</t>
-  </si>
-  <si>
-    <t>엘리트 몬스터, 보스용</t>
-  </si>
-  <si>
-    <t>SpawnActivation</t>
-  </si>
-  <si>
-    <t>스폰 활성화 모드</t>
-  </si>
-  <si>
-    <t>Always</t>
-  </si>
-  <si>
-    <t>항상</t>
-  </si>
-  <si>
-    <t>항상 밀도 유지</t>
-  </si>
-  <si>
-    <t>PlayerProximity</t>
-  </si>
-  <si>
-    <t>근접 활성</t>
-  </si>
-  <si>
-    <t>플레이어 근접 시만</t>
-  </si>
-  <si>
-    <t>Manual</t>
-  </si>
-  <si>
-    <t>수동</t>
-  </si>
-  <si>
-    <t>Stage 스크립트에서 ActivateSpawner 등으로 활성화시킴</t>
-  </si>
-  <si>
-    <t>PropStateMode</t>
-  </si>
-  <si>
-    <t>prop 상태머신 모드</t>
-  </si>
-  <si>
-    <t>Toggle</t>
-  </si>
-  <si>
-    <t>토글</t>
-  </si>
-  <si>
-    <t>상호작용마다 상태 순환(StateCount 만큼)</t>
-  </si>
-  <si>
-    <t>OneShot</t>
-  </si>
-  <si>
-    <t>일회성</t>
-  </si>
-  <si>
-    <t>0→1 1회 전이 후 더 이상 상태변화 없음</t>
-  </si>
-  <si>
-    <t>PropBehavior</t>
-  </si>
-  <si>
-    <t>prop 선언형 동작</t>
-  </si>
-  <si>
-    <t>Portal</t>
-  </si>
-  <si>
-    <t>포탈</t>
-  </si>
-  <si>
-    <t>상호작용 시 지정 스테이지/위치로 이동(무스크립트)</t>
-  </si>
-  <si>
-    <t>Character</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>캐릭터</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>NPC</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <t>타겟 위치</t>
+  </si>
+  <si>
+    <t>타겟 위치를 효과 중심 기준점으로 사용</t>
+  </si>
+  <si>
+    <t>시전자 프리팹의 SkillCastOrigin을 효과 중심 기준점으로 사용</t>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -980,39 +981,27 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="맑은 고딕"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="맑은 고딕"/>
-      <family val="2"/>
+      <family val="3"/>
       <charset val="129"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="맑은 고딕"/>
-      <family val="2"/>
+      <family val="3"/>
       <charset val="129"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="맑은 고딕"/>
-      <family val="2"/>
-      <charset val="129"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <name val="맑은 고딕"/>
       <family val="3"/>
       <charset val="129"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -1021,7 +1010,6 @@
       <name val="맑은 고딕"/>
       <family val="3"/>
       <charset val="129"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -1030,7 +1018,6 @@
       <name val="맑은 고딕"/>
       <family val="3"/>
       <charset val="129"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
@@ -1038,7 +1025,12 @@
       <name val="맑은 고딕"/>
       <family val="3"/>
       <charset val="129"/>
-      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="돋움"/>
+      <family val="3"/>
+      <charset val="129"/>
     </font>
   </fonts>
   <fills count="4">
@@ -1051,12 +1043,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="1" tint="0.249977111117893"/>
-        <bgColor indexed="64"/>
+        <bgColor indexed="65"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.79998168889431442"/>
+        <fgColor theme="4" tint="0.79995117038483843"/>
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
@@ -1105,10 +1097,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1121,10 +1113,7 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -1140,9 +1129,10 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="20% - 강조색1" xfId="1" builtinId="30"/>
+    <cellStyle name="20% - 강조색1" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1201,74 +1191,14 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="Yu Gothic Light"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:latin typeface="Calibri Light"/>
+        <a:ea typeface="Calibri Light"/>
+        <a:cs typeface="Calibri Light"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="Yu Gothic"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface="Calibri"/>
+        <a:cs typeface="Calibri"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -1280,23 +1210,23 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
+                <a:tint val="67000"/>
                 <a:lumMod val="110000"/>
                 <a:satMod val="105000"/>
-                <a:tint val="67000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
+                <a:tint val="73000"/>
                 <a:lumMod val="105000"/>
                 <a:satMod val="103000"/>
-                <a:tint val="73000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
+                <a:tint val="81000"/>
                 <a:lumMod val="105000"/>
                 <a:satMod val="109000"/>
-                <a:tint val="81000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -1306,23 +1236,23 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
+                <a:tint val="94000"/>
+                <a:lumMod val="102000"/>
                 <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
+                <a:shade val="100000"/>
+                <a:lumMod val="100000"/>
                 <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
+                <a:shade val="78000"/>
                 <a:lumMod val="99000"/>
                 <a:satMod val="120000"/>
-                <a:shade val="78000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -1330,26 +1260,23 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="6350">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="12700">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="19050">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
@@ -1384,17 +1311,17 @@
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="93000"/>
-                <a:satMod val="150000"/>
                 <a:shade val="98000"/>
                 <a:lumMod val="102000"/>
+                <a:satMod val="150000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
                 <a:tint val="98000"/>
-                <a:satMod val="130000"/>
                 <a:shade val="90000"/>
                 <a:lumMod val="103000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
@@ -1411,11 +1338,6 @@
   </a:themeElements>
   <a:objectDefaults/>
   <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
@@ -1692,11 +1614,11 @@
       <c r="D15" s="7">
         <v>1</v>
       </c>
-      <c r="E15" s="14" t="s">
-        <v>310</v>
-      </c>
-      <c r="F15" s="14" t="s">
-        <v>311</v>
+      <c r="E15" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="F15" s="13" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="16" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.3">
@@ -1727,10 +1649,10 @@
         <v>3</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="18" spans="1:6" s="7" customFormat="1" x14ac:dyDescent="0.3">
@@ -1744,10 +1666,10 @@
         <v>4</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="19" spans="1:6" s="7" customFormat="1" x14ac:dyDescent="0.3">
@@ -1760,11 +1682,11 @@
       <c r="D19" s="7">
         <v>5</v>
       </c>
-      <c r="E19" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="F19" s="11" t="s">
-        <v>46</v>
+      <c r="E19" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="F19" s="10" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="20" spans="1:6" s="7" customFormat="1" x14ac:dyDescent="0.3">
@@ -1777,16 +1699,16 @@
       <c r="D20" s="7">
         <v>6</v>
       </c>
-      <c r="E20" s="14" t="s">
-        <v>312</v>
-      </c>
-      <c r="F20" s="14" t="s">
-        <v>312</v>
+      <c r="E20" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="F20" s="13" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="21" spans="1:6" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A21" s="7" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="C21" s="7" t="s">
         <v>8</v>
@@ -1795,15 +1717,15 @@
         <v>1</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
     </row>
     <row r="22" spans="1:6" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A22" s="7" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="C22" s="7" t="s">
         <v>8</v>
@@ -1812,1582 +1734,1579 @@
         <v>2</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
     </row>
     <row r="23" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A23" s="4" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D23" s="4">
         <v>1</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="F23" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="24" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A24" s="4" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D24" s="4">
         <v>2</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="F24" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
     <row r="25" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A25" s="4" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D25" s="4">
         <v>3</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="F25" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="26" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A26" s="4" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D26" s="4">
         <v>4</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="F26" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
     </row>
     <row r="27" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A27" s="4" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D27" s="4">
         <v>5</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="F27" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
     </row>
     <row r="28" spans="1:6" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A28" s="7" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D28" s="7">
         <v>1</v>
       </c>
       <c r="E28" s="7" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="F28" s="7" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
     </row>
     <row r="29" spans="1:6" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A29" s="7" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D29" s="7">
         <v>2</v>
       </c>
       <c r="E29" s="7" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="F29" s="7" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
     </row>
     <row r="30" spans="1:6" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A30" s="7" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D30" s="7">
         <v>3</v>
       </c>
       <c r="E30" s="7" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F30" s="7" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
     </row>
     <row r="31" spans="1:6" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A31" s="7" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D31" s="7">
         <v>4</v>
       </c>
       <c r="E31" s="7" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="F31" s="7" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
     </row>
     <row r="32" spans="1:6" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A32" s="7" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D32" s="7">
         <v>5</v>
       </c>
       <c r="E32" s="7" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="F32" s="7" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.3">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A33" s="7" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D33" s="7">
         <v>6</v>
       </c>
       <c r="E33" s="7" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="F33" s="7" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.3">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A34" s="7" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D34" s="7">
         <v>7</v>
       </c>
       <c r="E34" s="7" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="F34" s="7" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.3">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A35" s="7" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D35" s="7">
         <v>8</v>
       </c>
       <c r="E35" s="7" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="F35" s="7" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.3">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A36" s="7" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D36" s="7">
         <v>9</v>
       </c>
       <c r="E36" s="7" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="F36" s="7" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A37" s="4" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D37" s="4">
         <v>1</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A38" s="4" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D38" s="4">
         <v>2</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="G38" s="8"/>
-    </row>
-    <row r="39" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A39" s="4" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D39" s="4">
         <v>3</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A40" s="4" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D40" s="4">
         <v>4</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A41" s="4" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D41" s="4">
         <v>5</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A42" s="4" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D42" s="4">
         <v>6</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A43" s="4" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D43" s="4">
         <v>7</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="G43" s="8"/>
-    </row>
-    <row r="44" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A44" s="4" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D44" s="4">
         <v>8</v>
       </c>
       <c r="E44" s="4" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A45" s="4" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D45" s="4">
         <v>9</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A46" s="4" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D46" s="4">
         <v>10</v>
       </c>
       <c r="E46" s="4" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A47" s="4" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D47" s="4">
         <v>11</v>
       </c>
       <c r="E47" s="4" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A48" s="4" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D48" s="4">
         <v>12</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="G48" s="8"/>
-    </row>
-    <row r="49" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A49" s="4" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D49" s="4">
         <v>13</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A50" s="4" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D50" s="4">
         <v>14</v>
       </c>
       <c r="E50" s="4" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="F50" s="4" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A51" s="4" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D51" s="4">
         <v>15</v>
       </c>
       <c r="E51" s="4" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A52" s="4" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D52" s="4">
         <v>16</v>
       </c>
       <c r="E52" s="4" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A53" s="4" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D53" s="4">
         <v>17</v>
       </c>
       <c r="E53" s="4" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="G53" s="8"/>
-    </row>
-    <row r="54" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A54" s="4" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D54" s="4">
         <v>18</v>
       </c>
       <c r="E54" s="4" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="F54" s="4" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A55" s="4" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D55" s="4">
         <v>19</v>
       </c>
       <c r="E55" s="4" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A56" s="4" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D56" s="4">
         <v>20</v>
       </c>
       <c r="E56" s="4" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="F56" s="4" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A57" s="4" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D57" s="4">
         <v>21</v>
       </c>
       <c r="E57" s="4" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="F57" s="4" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A58" s="4" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D58" s="4">
         <v>22</v>
       </c>
       <c r="E58" s="4" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="F58" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="G58" s="8"/>
-    </row>
-    <row r="59" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A59" s="4" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D59" s="4">
         <v>23</v>
       </c>
       <c r="E59" s="4" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="F59" s="4" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A60" s="4" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D60" s="4">
         <v>24</v>
       </c>
       <c r="E60" s="4" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="F60" s="4" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A61" s="4" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D61" s="4">
         <v>25</v>
       </c>
       <c r="E61" s="4" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="F61" s="4" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A62" s="4" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D62" s="4">
         <v>26</v>
       </c>
       <c r="E62" s="4" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="F62" s="4" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A63" s="4" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D63" s="4">
         <v>27</v>
       </c>
       <c r="E63" s="4" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="F63" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="G63" s="8"/>
-    </row>
-    <row r="64" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A64" s="4" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D64" s="4">
         <v>28</v>
       </c>
       <c r="E64" s="4" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="F64" s="4" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A65" s="4" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D65" s="4">
         <v>29</v>
       </c>
       <c r="E65" s="4" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="F65" s="4" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="66" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A66" s="4" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C66" s="4" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D66" s="4">
         <v>30</v>
       </c>
       <c r="E66" s="4" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="F66" s="4" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="67" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A67" s="4" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D67" s="4">
         <v>31</v>
       </c>
       <c r="E67" s="4" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="F67" s="4" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="68" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A68" s="4" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C68" s="4" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D68" s="4">
         <v>32</v>
       </c>
       <c r="E68" s="4" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="F68" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="G68" s="8"/>
-    </row>
-    <row r="69" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A69" s="4" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D69" s="4">
         <v>33</v>
       </c>
       <c r="E69" s="4" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="F69" s="4" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="70" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A70" s="4" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D70" s="4">
         <v>34</v>
       </c>
       <c r="E70" s="4" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="F70" s="4" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="71" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A71" s="4" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D71" s="4">
         <v>35</v>
       </c>
       <c r="E71" s="4" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="F71" s="4" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="72" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A72" s="4" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D72" s="4">
         <v>36</v>
       </c>
       <c r="E72" s="4" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="F72" s="4" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="73" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A73" s="4" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D73" s="4">
         <v>37</v>
       </c>
       <c r="E73" s="4" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="F73" s="4" t="s">
-        <v>156</v>
-      </c>
-      <c r="G73" s="8"/>
-    </row>
-    <row r="74" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A74" s="4" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D74" s="4">
         <v>38</v>
       </c>
       <c r="E74" s="4" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="F74" s="4" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="75" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A75" s="4" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C75" s="4" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D75" s="4">
         <v>39</v>
       </c>
       <c r="E75" s="4" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="F75" s="4" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="76" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A76" s="4" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C76" s="4" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D76" s="4">
         <v>40</v>
       </c>
       <c r="E76" s="4" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="F76" s="4" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="77" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A77" s="4" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C77" s="4" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D77" s="4">
         <v>41</v>
       </c>
       <c r="E77" s="4" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="F77" s="4" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="78" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A78" s="4" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D78" s="4">
         <v>42</v>
       </c>
       <c r="E78" s="4" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="F78" s="4" t="s">
-        <v>166</v>
-      </c>
-      <c r="G78" s="8"/>
-    </row>
-    <row r="79" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A79" s="4" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D79" s="4">
         <v>43</v>
       </c>
       <c r="E79" s="4" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="F79" s="4" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="80" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A80" s="4" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C80" s="4" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D80" s="4">
         <v>44</v>
       </c>
       <c r="E80" s="4" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="F80" s="4" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
     </row>
     <row r="81" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A81" s="4" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D81" s="4">
         <v>45</v>
       </c>
       <c r="E81" s="4" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="F81" s="4" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
     </row>
     <row r="82" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A82" s="7" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="C82" s="7" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="D82" s="7">
         <v>1</v>
       </c>
       <c r="E82" s="5" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="F82" s="5" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="G82" s="7" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
     </row>
     <row r="83" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A83" s="7" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="C83" s="7" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="D83" s="7">
         <v>2</v>
       </c>
       <c r="E83" s="5" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="F83" s="5" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="G83" s="7" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
     </row>
     <row r="84" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A84" s="7" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="C84" s="7" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="D84" s="7">
         <v>3</v>
       </c>
       <c r="E84" s="5" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="F84" s="5" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="G84" s="7" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
     </row>
     <row r="85" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="C85" s="4" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="D85" s="4">
         <v>1</v>
       </c>
       <c r="E85" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="F85" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
     </row>
     <row r="86" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="C86" s="4" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="D86" s="4">
         <v>2</v>
       </c>
       <c r="E86" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="F86" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
     </row>
     <row r="87" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="C87" s="4" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="D87" s="4">
         <v>3</v>
       </c>
       <c r="E87" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="F87" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
     </row>
     <row r="88" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="D88" s="4">
         <v>4</v>
       </c>
       <c r="E88" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F88" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
     </row>
     <row r="89" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A89" s="5" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="B89" s="7" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="C89" s="7" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="D89" s="7">
         <v>1</v>
       </c>
       <c r="E89" s="5" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="F89" s="5" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
     </row>
     <row r="90" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A90" s="5" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="B90" s="5"/>
       <c r="C90" s="7" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="D90" s="7">
         <v>2</v>
       </c>
       <c r="E90" s="5" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="F90" s="5" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
     </row>
     <row r="91" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A91" s="5" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="B91" s="5"/>
       <c r="C91" s="7" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="D91" s="7">
         <v>3</v>
       </c>
       <c r="E91" s="5" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="F91" s="5" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
     </row>
     <row r="92" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="B92" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="C92" s="4" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="D92" s="4">
         <v>1</v>
       </c>
       <c r="E92" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="F92" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="G92" s="4" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
     </row>
     <row r="93" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="C93" s="4" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="D93" s="4">
         <v>2</v>
       </c>
       <c r="E93" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="F93" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="G93" s="4" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
     </row>
     <row r="94" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A94" s="5" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="B94" s="7" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="C94" s="7" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="D94" s="7">
         <v>1</v>
       </c>
       <c r="E94" s="5" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="F94" s="5" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="G94" s="7" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
     </row>
     <row r="95" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A95" s="5" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="B95" s="5"/>
       <c r="C95" s="7" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="D95" s="7">
         <v>2</v>
       </c>
       <c r="E95" s="5" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="F95" s="5" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="G95" s="7" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
     </row>
     <row r="96" spans="1:7" s="4" customFormat="1" ht="141.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A96" s="9" t="s">
-        <v>218</v>
-      </c>
-      <c r="B96" s="10" t="s">
-        <v>219</v>
+      <c r="A96" s="8" t="s">
+        <v>221</v>
+      </c>
+      <c r="B96" s="9" t="s">
+        <v>222</v>
       </c>
       <c r="C96" s="4" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="D96" s="4">
         <v>1</v>
       </c>
       <c r="E96" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="F96" t="s">
+        <v>224</v>
+      </c>
+      <c r="G96" s="4" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A97" s="8" t="s">
         <v>221</v>
       </c>
-      <c r="G96" s="4" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="97" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A97" s="9" t="s">
-        <v>218</v>
-      </c>
-      <c r="B97" s="9"/>
+      <c r="B97" s="8"/>
       <c r="C97" s="4" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="D97" s="4">
         <v>2</v>
       </c>
       <c r="E97" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="F97" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="G97" s="4" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
     </row>
     <row r="98" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A98" s="5" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="B98" s="7" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="C98" s="7" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="D98" s="7">
         <v>1</v>
       </c>
       <c r="E98" s="5" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="F98" s="5" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
     </row>
     <row r="99" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A99" s="5" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="B99" s="5"/>
       <c r="C99" s="7" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="D99" s="7">
         <v>2</v>
       </c>
       <c r="E99" s="5" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="F99" s="5" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
     </row>
     <row r="100" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A100" s="9" t="s">
-        <v>232</v>
+      <c r="A100" s="8" t="s">
+        <v>235</v>
       </c>
       <c r="B100" s="4" t="s">
-        <v>233</v>
+        <v>306</v>
       </c>
       <c r="C100" s="4" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="D100" s="4">
         <v>1</v>
       </c>
       <c r="E100" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="F100" s="4" t="s">
+        <v>307</v>
+      </c>
+      <c r="G100" s="4" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A101" s="8" t="s">
         <v>235</v>
       </c>
-      <c r="G100" s="4" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="101" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A101" s="9" t="s">
-        <v>232</v>
-      </c>
-      <c r="B101" s="9"/>
+      <c r="B101" s="8"/>
       <c r="C101" s="4" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="D101" s="4">
         <v>2</v>
       </c>
       <c r="E101" t="s">
-        <v>237</v>
+        <v>309</v>
       </c>
       <c r="F101" s="4" t="s">
-        <v>238</v>
+        <v>310</v>
+      </c>
+      <c r="G101" s="14" t="s">
+        <v>314</v>
       </c>
     </row>
     <row r="102" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A102" s="9" t="s">
-        <v>232</v>
-      </c>
-      <c r="B102" s="9"/>
+      <c r="A102" s="8" t="s">
+        <v>235</v>
+      </c>
+      <c r="B102" s="8"/>
       <c r="C102" s="4" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="D102" s="4">
         <v>3</v>
       </c>
       <c r="E102" t="s">
-        <v>239</v>
+        <v>311</v>
       </c>
       <c r="F102" s="4" t="s">
-        <v>240</v>
+        <v>312</v>
+      </c>
+      <c r="G102" t="s">
+        <v>313</v>
       </c>
     </row>
     <row r="103" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A103" s="7" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="C103" s="7" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="D103" s="7">
         <v>1</v>
       </c>
       <c r="E103" s="7" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="F103" s="7" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
     </row>
     <row r="104" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A104" s="7" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="C104" s="7" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="D104" s="7">
         <v>2</v>
       </c>
       <c r="E104" s="7" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="F104" s="7" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="G104" s="7" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
     </row>
     <row r="105" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A105" s="4" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="C105" s="4" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="D105" s="4">
         <v>1</v>
       </c>
       <c r="E105" s="4" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="F105" s="4" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="G105" s="4" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
     </row>
     <row r="106" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A106" s="4" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="C106" s="4" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="D106" s="4">
         <v>2</v>
       </c>
       <c r="E106" s="4" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="F106" s="4" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="G106" s="4" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
     </row>
     <row r="107" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A107" s="4" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="C107" s="4" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="D107" s="4">
         <v>3</v>
       </c>
       <c r="E107" s="4" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="F107" s="4" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="G107" s="4" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
     </row>
     <row r="108" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A108" s="7" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="B108" s="7" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="C108" s="7" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="D108" s="7">
         <v>1</v>
       </c>
       <c r="E108" s="7" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="F108" s="7" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="G108" s="7" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
     </row>
     <row r="109" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A109" s="7" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="C109" s="7" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="D109" s="7">
         <v>2</v>
       </c>
       <c r="E109" s="7" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="F109" s="7" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="G109" s="7" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
     </row>
     <row r="110" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="C110" t="s">
         <v>30</v>
@@ -3396,18 +3315,18 @@
         <v>1</v>
       </c>
       <c r="E110" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="F110" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="G110" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
     </row>
     <row r="111" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="C111" t="s">
         <v>30</v>
@@ -3416,18 +3335,18 @@
         <v>2</v>
       </c>
       <c r="E111" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="F111" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="G111" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
     </row>
     <row r="112" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="C112" t="s">
         <v>30</v>
@@ -3436,18 +3355,18 @@
         <v>3</v>
       </c>
       <c r="E112" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="F112" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="G112" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
     </row>
     <row r="113" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="C113" t="s">
         <v>30</v>
@@ -3456,64 +3375,64 @@
         <v>4</v>
       </c>
       <c r="E113" t="s">
+        <v>271</v>
+      </c>
+      <c r="F113" t="s">
+        <v>272</v>
+      </c>
+      <c r="G113" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="114" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A114" s="11" t="s">
+        <v>274</v>
+      </c>
+      <c r="B114" s="11" t="s">
         <v>275</v>
       </c>
-      <c r="F113" t="s">
+      <c r="C114" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D114" s="12">
+        <v>1</v>
+      </c>
+      <c r="E114" s="11" t="s">
         <v>276</v>
       </c>
-      <c r="G113" t="s">
+      <c r="F114" s="11" t="s">
         <v>277</v>
       </c>
-    </row>
-    <row r="114" spans="1:7" s="12" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A114" s="12" t="s">
+      <c r="G114" s="11" t="s">
         <v>278</v>
       </c>
-      <c r="B114" s="12" t="s">
+    </row>
+    <row r="115" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A115" s="11" t="s">
+        <v>274</v>
+      </c>
+      <c r="C115" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D115" s="12">
+        <v>2</v>
+      </c>
+      <c r="E115" s="11" t="s">
         <v>279</v>
       </c>
-      <c r="C114" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="D114" s="13">
-        <v>1</v>
-      </c>
-      <c r="E114" s="12" t="s">
+      <c r="F115" s="11" t="s">
         <v>280</v>
       </c>
-      <c r="F114" s="12" t="s">
+      <c r="G115" s="11" t="s">
         <v>281</v>
-      </c>
-      <c r="G114" s="12" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="115" spans="1:7" s="12" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A115" s="12" t="s">
-        <v>278</v>
-      </c>
-      <c r="C115" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="D115" s="13">
-        <v>2</v>
-      </c>
-      <c r="E115" s="12" t="s">
-        <v>283</v>
-      </c>
-      <c r="F115" s="12" t="s">
-        <v>284</v>
-      </c>
-      <c r="G115" s="12" t="s">
-        <v>285</v>
       </c>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A116" s="1" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="C116" s="1" t="s">
         <v>11</v>
@@ -3522,18 +3441,18 @@
         <v>1</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="F116" s="1" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="G116" s="1" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A117" s="1" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="C117" s="1" t="s">
         <v>11</v>
@@ -3542,18 +3461,18 @@
         <v>2</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="F117" s="1" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="G117" s="1" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A118" s="1" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="C118" s="1" t="s">
         <v>11</v>
@@ -3562,84 +3481,83 @@
         <v>3</v>
       </c>
       <c r="E118" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="F118" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="G118" s="1" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="119" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A119" s="11" t="s">
+        <v>293</v>
+      </c>
+      <c r="B119" s="11" t="s">
         <v>294</v>
       </c>
-      <c r="F118" s="1" t="s">
+      <c r="C119" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="D119" s="12">
+        <v>1</v>
+      </c>
+      <c r="E119" s="11" t="s">
         <v>295</v>
       </c>
-      <c r="G118" s="1" t="s">
+      <c r="F119" s="11" t="s">
         <v>296</v>
       </c>
-    </row>
-    <row r="119" spans="1:7" s="12" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A119" s="12" t="s">
+      <c r="G119" s="11" t="s">
         <v>297</v>
       </c>
-      <c r="B119" s="12" t="s">
+    </row>
+    <row r="120" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A120" s="11" t="s">
+        <v>293</v>
+      </c>
+      <c r="C120" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="D120" s="12">
+        <v>2</v>
+      </c>
+      <c r="E120" s="11" t="s">
         <v>298</v>
       </c>
-      <c r="C119" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="D119" s="13">
-        <v>1</v>
-      </c>
-      <c r="E119" s="12" t="s">
+      <c r="F120" s="11" t="s">
         <v>299</v>
       </c>
-      <c r="F119" s="12" t="s">
+      <c r="G120" s="11" t="s">
         <v>300</v>
-      </c>
-      <c r="G119" s="12" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="120" spans="1:7" s="12" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A120" s="12" t="s">
-        <v>297</v>
-      </c>
-      <c r="C120" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="D120" s="13">
-        <v>2</v>
-      </c>
-      <c r="E120" s="12" t="s">
-        <v>302</v>
-      </c>
-      <c r="F120" s="12" t="s">
-        <v>303</v>
-      </c>
-      <c r="G120" s="12" t="s">
-        <v>304</v>
       </c>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="B121" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="C121" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D121" s="4">
         <v>1</v>
       </c>
       <c r="E121" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="F121" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="G121" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="E1:E113" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
-  <phoneticPr fontId="4" type="noConversion"/>
+  <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>